--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893972</v>
+        <v>129894024</v>
       </c>
       <c r="B6" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,37 +1082,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447014</v>
+        <v>447139</v>
       </c>
       <c r="R6" t="n">
-        <v>6804654</v>
+        <v>6804619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1150,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1172,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129894024</v>
+        <v>129893972</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,34 +1179,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447139</v>
+        <v>447014</v>
       </c>
       <c r="R7" t="n">
-        <v>6804619</v>
+        <v>6804654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,54 +1269,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893963</v>
+        <v>129893970</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>78838</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447084</v>
+        <v>447006</v>
       </c>
       <c r="R8" t="n">
-        <v>6804507</v>
+        <v>6804685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1376,7 +1366,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893970</v>
+        <v>129893974</v>
       </c>
       <c r="B9" t="n">
         <v>78838</v>
@@ -1411,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447006</v>
+        <v>447014</v>
       </c>
       <c r="R9" t="n">
-        <v>6804685</v>
+        <v>6804644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,45 +1463,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893974</v>
+        <v>129893963</v>
       </c>
       <c r="B10" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447014</v>
+        <v>447084</v>
       </c>
       <c r="R10" t="n">
-        <v>6804644</v>
+        <v>6804507</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,6 +1551,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893955</v>
+        <v>129893920</v>
       </c>
       <c r="B33" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447237</v>
+        <v>447249</v>
       </c>
       <c r="R33" t="n">
-        <v>6804433</v>
+        <v>6804413</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893920</v>
+        <v>129894034</v>
       </c>
       <c r="B34" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3867,21 +3867,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447249</v>
+        <v>447146</v>
       </c>
       <c r="R34" t="n">
-        <v>6804413</v>
+        <v>6804328</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,7 +3953,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894034</v>
+        <v>129894046</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -3982,16 +3982,19 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447146</v>
+        <v>447137</v>
       </c>
       <c r="R35" t="n">
-        <v>6804328</v>
+        <v>6804362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,12 +4029,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4050,7 +4059,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894046</v>
+        <v>129894028</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4079,19 +4088,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447137</v>
+        <v>447038</v>
       </c>
       <c r="R36" t="n">
-        <v>6804362</v>
+        <v>6804585</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4126,18 +4132,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894028</v>
+        <v>129894026</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447038</v>
+        <v>447019</v>
       </c>
       <c r="R37" t="n">
-        <v>6804585</v>
+        <v>6804831</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4227,6 +4227,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4253,7 +4258,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894026</v>
+        <v>129894036</v>
       </c>
       <c r="B38" t="n">
         <v>79081</v>
@@ -4288,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447019</v>
+        <v>447177</v>
       </c>
       <c r="R38" t="n">
-        <v>6804831</v>
+        <v>6804353</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4324,11 +4329,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894036</v>
+        <v>129893955</v>
       </c>
       <c r="B39" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447177</v>
+        <v>447237</v>
       </c>
       <c r="R39" t="n">
-        <v>6804353</v>
+        <v>6804433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894027</v>
+        <v>129893948</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446979</v>
+        <v>446971</v>
       </c>
       <c r="R41" t="n">
-        <v>6804787</v>
+        <v>6804769</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893948</v>
+        <v>129894027</v>
       </c>
       <c r="B44" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,21 +4851,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446971</v>
+        <v>446979</v>
       </c>
       <c r="R44" t="n">
-        <v>6804769</v>
+        <v>6804787</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -7337,6 +7337,6025 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>129893347</v>
+      </c>
+      <c r="B69" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>447114</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6804581</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>129893324</v>
+      </c>
+      <c r="B70" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>447118</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6804529</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>129893402</v>
+      </c>
+      <c r="B71" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>447287</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6804380</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>129893404</v>
+      </c>
+      <c r="B72" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>447286</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6804416</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>129893403</v>
+      </c>
+      <c r="B73" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>447296</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6804411</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129893400</v>
+      </c>
+      <c r="B74" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>447249</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6804333</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129893315</v>
+      </c>
+      <c r="B75" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>447115</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6804531</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129893393</v>
+      </c>
+      <c r="B76" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>447110</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6804630</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 50 m</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129893356</v>
+      </c>
+      <c r="B77" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>447165</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6804365</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129893353</v>
+      </c>
+      <c r="B78" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>447206</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6804417</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129893306</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>447282</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6804440</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129893334</v>
+      </c>
+      <c r="B80" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>447287</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6804433</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129893395</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>447137</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6804440</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129893368</v>
+      </c>
+      <c r="B82" t="n">
+        <v>90981</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>447279</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6804380</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129893303</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>447143</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6804414</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129893305</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>447170</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6804401</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129893397</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>447191</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6804284</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129893348</v>
+      </c>
+      <c r="B86" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>447138</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6804553</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129893392</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>447216</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6804599</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129893405</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>447280</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6804429</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129893360</v>
+      </c>
+      <c r="B89" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>447286</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6804433</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129893399</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>447206</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6804317</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129893307</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>447271</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6804458</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129893351</v>
+      </c>
+      <c r="B92" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>447129</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6804505</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129893316</v>
+      </c>
+      <c r="B93" t="n">
+        <v>56926</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>447102</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6804551</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129893309</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>447247</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6804552</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129893323</v>
+      </c>
+      <c r="B95" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>447139</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6804556</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129893332</v>
+      </c>
+      <c r="B96" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>447086</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6804674</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129893407</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>447258</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6804469</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129893359</v>
+      </c>
+      <c r="B98" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>447276</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6804418</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129893396</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>447170</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6804344</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>129893310</v>
+      </c>
+      <c r="B100" t="n">
+        <v>79671</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>447280</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6804428</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>129893350</v>
+      </c>
+      <c r="B101" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>447120</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6804506</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>129893344</v>
+      </c>
+      <c r="B102" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>447173</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6804600</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>129893357</v>
+      </c>
+      <c r="B103" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>447159</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6804343</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>129893301</v>
+      </c>
+      <c r="B104" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>447134</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6804438</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>129893346</v>
+      </c>
+      <c r="B105" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>447088</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6804609</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>129893299</v>
+      </c>
+      <c r="B106" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>447141</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6804483</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>129893398</v>
+      </c>
+      <c r="B107" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>447189</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6804301</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>129893296</v>
+      </c>
+      <c r="B108" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>447079</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6804660</v>
+      </c>
+      <c r="S108" t="n">
+        <v>10</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>129893358</v>
+      </c>
+      <c r="B109" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>447319</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6804349</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>129893352</v>
+      </c>
+      <c r="B110" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>447146</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6804415</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129893322</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>447105</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6804584</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129893295</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>447085</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6804671</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>129893300</v>
+      </c>
+      <c r="B113" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>447121</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6804435</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129893297</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>447104</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6804519</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129893394</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>447128</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6804516</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129893308</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>447248</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6804484</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129893314</v>
+      </c>
+      <c r="B117" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>447227</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6804586</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129893325</v>
+      </c>
+      <c r="B118" t="n">
+        <v>57733</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>447201</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6804314</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>129893354</v>
+      </c>
+      <c r="B119" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>447193</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6804389</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>129893302</v>
+      </c>
+      <c r="B120" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>447140</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6804436</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>129893408</v>
+      </c>
+      <c r="B121" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>447247</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6804486</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129893355</v>
+      </c>
+      <c r="B122" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>447175</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6804401</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129893333</v>
+      </c>
+      <c r="B123" t="n">
+        <v>78839</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>447284</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6804412</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129893304</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>447208</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6804423</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129893406</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>447282</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6804440</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129893401</v>
+      </c>
+      <c r="B126" t="n">
+        <v>79081</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>447291</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6804354</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129893349</v>
+      </c>
+      <c r="B127" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>447138</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6804511</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>129893298</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79700</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>447137</v>
+      </c>
+      <c r="R128" t="n">
+        <v>6804511</v>
+      </c>
+      <c r="S128" t="n">
+        <v>10</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>129893345</v>
+      </c>
+      <c r="B129" t="n">
+        <v>78838</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Jöllmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>447105</v>
+      </c>
+      <c r="R129" t="n">
+        <v>6804653</v>
+      </c>
+      <c r="S129" t="n">
+        <v>10</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Louise Tegnér</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893971</v>
+        <v>129893939</v>
       </c>
       <c r="B2" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447009</v>
+        <v>447133</v>
       </c>
       <c r="R2" t="n">
-        <v>6804689</v>
+        <v>6804362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894044</v>
+        <v>129893913</v>
       </c>
       <c r="B3" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446959</v>
+        <v>447127</v>
       </c>
       <c r="R3" t="n">
-        <v>6804780</v>
+        <v>6804438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893939</v>
+        <v>129893971</v>
       </c>
       <c r="B4" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +888,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447133</v>
+        <v>447009</v>
       </c>
       <c r="R4" t="n">
-        <v>6804362</v>
+        <v>6804689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893913</v>
+        <v>129894044</v>
       </c>
       <c r="B5" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447127</v>
+        <v>446959</v>
       </c>
       <c r="R5" t="n">
-        <v>6804438</v>
+        <v>6804780</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894024</v>
+        <v>129893972</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,34 +1082,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447139</v>
+        <v>447014</v>
       </c>
       <c r="R6" t="n">
-        <v>6804619</v>
+        <v>6804654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,6 +1153,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893972</v>
+        <v>129894024</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,37 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447014</v>
+        <v>447139</v>
       </c>
       <c r="R7" t="n">
-        <v>6804654</v>
+        <v>6804619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1251,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893920</v>
+        <v>129894034</v>
       </c>
       <c r="B33" t="n">
-        <v>79671</v>
+        <v>79081</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447249</v>
+        <v>447146</v>
       </c>
       <c r="R33" t="n">
-        <v>6804413</v>
+        <v>6804328</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894034</v>
+        <v>129894046</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -3885,16 +3885,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447146</v>
+        <v>447137</v>
       </c>
       <c r="R34" t="n">
-        <v>6804328</v>
+        <v>6804362</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3929,12 +3932,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3953,7 +3962,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894046</v>
+        <v>129894028</v>
       </c>
       <c r="B35" t="n">
         <v>79081</v>
@@ -3982,19 +3991,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447137</v>
+        <v>447038</v>
       </c>
       <c r="R35" t="n">
-        <v>6804362</v>
+        <v>6804585</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4029,18 +4035,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4059,7 +4059,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894028</v>
+        <v>129894026</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4094,10 +4094,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447038</v>
+        <v>447019</v>
       </c>
       <c r="R36" t="n">
-        <v>6804585</v>
+        <v>6804831</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4130,6 +4130,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4156,7 +4161,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894026</v>
+        <v>129894036</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4191,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447019</v>
+        <v>447177</v>
       </c>
       <c r="R37" t="n">
-        <v>6804831</v>
+        <v>6804353</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4227,11 +4232,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894036</v>
+        <v>129893955</v>
       </c>
       <c r="B38" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447177</v>
+        <v>447237</v>
       </c>
       <c r="R38" t="n">
-        <v>6804353</v>
+        <v>6804433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893955</v>
+        <v>129893920</v>
       </c>
       <c r="B39" t="n">
-        <v>78839</v>
+        <v>79671</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447237</v>
+        <v>447249</v>
       </c>
       <c r="R39" t="n">
-        <v>6804433</v>
+        <v>6804413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893948</v>
+        <v>129894027</v>
       </c>
       <c r="B41" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446971</v>
+        <v>446979</v>
       </c>
       <c r="R41" t="n">
-        <v>6804769</v>
+        <v>6804787</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129894027</v>
+        <v>129893948</v>
       </c>
       <c r="B44" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,21 +4851,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446979</v>
+        <v>446971</v>
       </c>
       <c r="R44" t="n">
-        <v>6804787</v>
+        <v>6804769</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893300</v>
+        <v>129893314</v>
       </c>
       <c r="B113" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,34 +11689,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447121</v>
+        <v>447227</v>
       </c>
       <c r="R113" t="n">
-        <v>6804435</v>
+        <v>6804586</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11775,7 +11783,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893297</v>
+        <v>129893300</v>
       </c>
       <c r="B114" t="n">
         <v>79700</v>
@@ -11810,10 +11818,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447104</v>
+        <v>447121</v>
       </c>
       <c r="R114" t="n">
-        <v>6804519</v>
+        <v>6804435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11872,10 +11880,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893394</v>
+        <v>129893297</v>
       </c>
       <c r="B115" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11883,21 +11891,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11907,10 +11915,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447128</v>
+        <v>447104</v>
       </c>
       <c r="R115" t="n">
-        <v>6804516</v>
+        <v>6804519</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11943,11 +11951,6 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11974,10 +11977,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893308</v>
+        <v>129893394</v>
       </c>
       <c r="B116" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11985,21 +11988,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12009,10 +12012,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447248</v>
+        <v>447128</v>
       </c>
       <c r="R116" t="n">
-        <v>6804484</v>
+        <v>6804516</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12045,6 +12048,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12071,10 +12079,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893314</v>
+        <v>129893308</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12082,42 +12090,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447227</v>
+        <v>447248</v>
       </c>
       <c r="R117" t="n">
-        <v>6804586</v>
+        <v>6804484</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893939</v>
+        <v>129894044</v>
       </c>
       <c r="B2" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447133</v>
+        <v>446959</v>
       </c>
       <c r="R2" t="n">
-        <v>6804362</v>
+        <v>6804780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -974,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129894044</v>
+        <v>129893939</v>
       </c>
       <c r="B5" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446959</v>
+        <v>447133</v>
       </c>
       <c r="R5" t="n">
-        <v>6804780</v>
+        <v>6804362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129893972</v>
+        <v>129894024</v>
       </c>
       <c r="B6" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,37 +1082,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447014</v>
+        <v>447139</v>
       </c>
       <c r="R6" t="n">
-        <v>6804654</v>
+        <v>6804619</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1153,7 +1150,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1172,10 +1168,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129894024</v>
+        <v>129893972</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1183,34 +1179,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447139</v>
+        <v>447014</v>
       </c>
       <c r="R7" t="n">
-        <v>6804619</v>
+        <v>6804654</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1251,6 +1250,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R11" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,11 +1641,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1672,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B12" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,21 +1678,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R12" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,6 +1738,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B14" t="n">
-        <v>78839</v>
+        <v>78089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R14" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,6 +1950,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894050</v>
+        <v>129893953</v>
       </c>
       <c r="B15" t="n">
-        <v>78089</v>
+        <v>78839</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447251</v>
+        <v>447186</v>
       </c>
       <c r="R15" t="n">
-        <v>6804480</v>
+        <v>6804347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,7 +2048,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2163,53 +2163,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893923</v>
+        <v>129894043</v>
       </c>
       <c r="B17" t="n">
-        <v>56926</v>
+        <v>79081</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447079</v>
+        <v>447247</v>
       </c>
       <c r="R17" t="n">
-        <v>6804592</v>
+        <v>6804534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,45 +2357,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129894043</v>
+        <v>129893923</v>
       </c>
       <c r="B19" t="n">
-        <v>79081</v>
+        <v>56926</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447247</v>
+        <v>447079</v>
       </c>
       <c r="R19" t="n">
-        <v>6804534</v>
+        <v>6804592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2753,45 +2753,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893956</v>
+        <v>129893945</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>56929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447248</v>
+        <v>447140</v>
       </c>
       <c r="R23" t="n">
-        <v>6804447</v>
+        <v>6804358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894040</v>
+        <v>129893956</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447244</v>
+        <v>447248</v>
       </c>
       <c r="R24" t="n">
-        <v>6804361</v>
+        <v>6804447</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,53 +2955,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893945</v>
+        <v>129894040</v>
       </c>
       <c r="B25" t="n">
-        <v>56929</v>
+        <v>79081</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447140</v>
+        <v>447244</v>
       </c>
       <c r="R25" t="n">
-        <v>6804358</v>
+        <v>6804361</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893919</v>
+        <v>129893935</v>
       </c>
       <c r="B28" t="n">
-        <v>79671</v>
+        <v>57733</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,34 +3267,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447260</v>
+        <v>447017</v>
       </c>
       <c r="R28" t="n">
-        <v>6804349</v>
+        <v>6804662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3353,10 +3361,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893935</v>
+        <v>129893919</v>
       </c>
       <c r="B29" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,42 +3372,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447017</v>
+        <v>447260</v>
       </c>
       <c r="R29" t="n">
-        <v>6804662</v>
+        <v>6804349</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894029</v>
+        <v>129894047</v>
       </c>
       <c r="B30" t="n">
         <v>79081</v>
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447078</v>
+        <v>447264</v>
       </c>
       <c r="R30" t="n">
-        <v>6804574</v>
+        <v>6804394</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3560,7 +3560,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894047</v>
+        <v>129894029</v>
       </c>
       <c r="B31" t="n">
         <v>79081</v>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447264</v>
+        <v>447078</v>
       </c>
       <c r="R31" t="n">
-        <v>6804394</v>
+        <v>6804574</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,7 +3759,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894034</v>
+        <v>129894036</v>
       </c>
       <c r="B33" t="n">
         <v>79081</v>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447146</v>
+        <v>447177</v>
       </c>
       <c r="R33" t="n">
-        <v>6804328</v>
+        <v>6804353</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894046</v>
+        <v>129894026</v>
       </c>
       <c r="B34" t="n">
         <v>79081</v>
@@ -3885,19 +3885,16 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447137</v>
+        <v>447019</v>
       </c>
       <c r="R34" t="n">
-        <v>6804362</v>
+        <v>6804831</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3934,7 +3931,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3943,7 +3940,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4059,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894026</v>
+        <v>129894034</v>
       </c>
       <c r="B36" t="n">
         <v>79081</v>
@@ -4094,10 +4090,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447019</v>
+        <v>447146</v>
       </c>
       <c r="R36" t="n">
-        <v>6804831</v>
+        <v>6804328</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4130,11 +4126,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4161,7 +4152,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894036</v>
+        <v>129894046</v>
       </c>
       <c r="B37" t="n">
         <v>79081</v>
@@ -4190,16 +4181,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447177</v>
+        <v>447137</v>
       </c>
       <c r="R37" t="n">
-        <v>6804353</v>
+        <v>6804362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4234,12 +4228,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4646,7 +4646,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893975</v>
+        <v>129893983</v>
       </c>
       <c r="B42" t="n">
         <v>78838</v>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447017</v>
+        <v>447195</v>
       </c>
       <c r="R42" t="n">
-        <v>6804644</v>
+        <v>6804348</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129893983</v>
+        <v>129893975</v>
       </c>
       <c r="B43" t="n">
         <v>78838</v>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447195</v>
+        <v>447017</v>
       </c>
       <c r="R43" t="n">
-        <v>6804348</v>
+        <v>6804644</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4937,7 +4937,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893969</v>
+        <v>129893980</v>
       </c>
       <c r="B45" t="n">
         <v>78838</v>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447006</v>
+        <v>447136</v>
       </c>
       <c r="R45" t="n">
-        <v>6804728</v>
+        <v>6804407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,7 +5034,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893980</v>
+        <v>129893969</v>
       </c>
       <c r="B46" t="n">
         <v>78838</v>
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447136</v>
+        <v>447006</v>
       </c>
       <c r="R46" t="n">
-        <v>6804407</v>
+        <v>6804728</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,7 +5131,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894035</v>
+        <v>129894041</v>
       </c>
       <c r="B47" t="n">
         <v>79081</v>
@@ -5166,10 +5166,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447155</v>
+        <v>447242</v>
       </c>
       <c r="R47" t="n">
-        <v>6804339</v>
+        <v>6804443</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,7 +5228,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894041</v>
+        <v>129894035</v>
       </c>
       <c r="B48" t="n">
         <v>79081</v>
@@ -5263,10 +5263,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447242</v>
+        <v>447155</v>
       </c>
       <c r="R48" t="n">
-        <v>6804443</v>
+        <v>6804339</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893951</v>
+        <v>129893933</v>
       </c>
       <c r="B49" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,34 +5336,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447014</v>
+        <v>447075</v>
       </c>
       <c r="R49" t="n">
-        <v>6804638</v>
+        <v>6804732</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,7 +5430,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893933</v>
+        <v>129893937</v>
       </c>
       <c r="B50" t="n">
         <v>57733</v>
@@ -5465,10 +5473,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447075</v>
+        <v>447059</v>
       </c>
       <c r="R50" t="n">
-        <v>6804732</v>
+        <v>6804587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5632,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893937</v>
+        <v>129893918</v>
       </c>
       <c r="B52" t="n">
-        <v>57733</v>
+        <v>79671</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5643,42 +5651,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447059</v>
+        <v>447021</v>
       </c>
       <c r="R52" t="n">
-        <v>6804587</v>
+        <v>6804646</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893918</v>
+        <v>129893951</v>
       </c>
       <c r="B53" t="n">
-        <v>79671</v>
+        <v>78839</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447021</v>
+        <v>447014</v>
       </c>
       <c r="R53" t="n">
-        <v>6804646</v>
+        <v>6804638</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129893924</v>
+        <v>129893932</v>
       </c>
       <c r="B54" t="n">
-        <v>56926</v>
+        <v>57733</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,7 +5867,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446997</v>
+        <v>447239</v>
       </c>
       <c r="R54" t="n">
-        <v>6804780</v>
+        <v>6804569</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,11 +5913,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6049,32 +6044,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893932</v>
+        <v>129893924</v>
       </c>
       <c r="B56" t="n">
-        <v>57733</v>
+        <v>56926</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6082,7 +6077,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6092,10 +6087,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447239</v>
+        <v>446997</v>
       </c>
       <c r="R56" t="n">
-        <v>6804569</v>
+        <v>6804780</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6128,6 +6123,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129893967</v>
+        <v>129893950</v>
       </c>
       <c r="B58" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,21 +6267,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447209</v>
+        <v>447015</v>
       </c>
       <c r="R58" t="n">
-        <v>6804576</v>
+        <v>6804655</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893968</v>
+        <v>129893934</v>
       </c>
       <c r="B59" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6364,34 +6364,42 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446972</v>
+        <v>447006</v>
       </c>
       <c r="R59" t="n">
-        <v>6804770</v>
+        <v>6804684</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6547,10 +6555,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893950</v>
+        <v>129893968</v>
       </c>
       <c r="B61" t="n">
-        <v>78839</v>
+        <v>78838</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6558,21 +6566,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6582,10 +6590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447015</v>
+        <v>446972</v>
       </c>
       <c r="R61" t="n">
-        <v>6804655</v>
+        <v>6804770</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6644,10 +6652,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129893934</v>
+        <v>129893967</v>
       </c>
       <c r="B62" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6655,42 +6663,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447006</v>
+        <v>447209</v>
       </c>
       <c r="R62" t="n">
-        <v>6804684</v>
+        <v>6804576</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893982</v>
+        <v>129894038</v>
       </c>
       <c r="B63" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447163</v>
+        <v>447196</v>
       </c>
       <c r="R63" t="n">
-        <v>6804342</v>
+        <v>6804341</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129894038</v>
+        <v>129893914</v>
       </c>
       <c r="B64" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447196</v>
+        <v>447244</v>
       </c>
       <c r="R64" t="n">
-        <v>6804341</v>
+        <v>6804447</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893952</v>
+        <v>129893912</v>
       </c>
       <c r="B65" t="n">
-        <v>78839</v>
+        <v>79700</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447138</v>
+        <v>447082</v>
       </c>
       <c r="R65" t="n">
-        <v>6804405</v>
+        <v>6804551</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893912</v>
+        <v>129893982</v>
       </c>
       <c r="B66" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447082</v>
+        <v>447163</v>
       </c>
       <c r="R66" t="n">
-        <v>6804551</v>
+        <v>6804342</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893914</v>
+        <v>129893952</v>
       </c>
       <c r="B67" t="n">
-        <v>79700</v>
+        <v>78839</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,21 +7148,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447244</v>
+        <v>447138</v>
       </c>
       <c r="R67" t="n">
-        <v>6804447</v>
+        <v>6804405</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129893347</v>
+        <v>129893324</v>
       </c>
       <c r="B69" t="n">
-        <v>78838</v>
+        <v>57733</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7350,34 +7350,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447114</v>
+        <v>447118</v>
       </c>
       <c r="R69" t="n">
-        <v>6804581</v>
+        <v>6804529</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,10 +7444,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893324</v>
+        <v>129893347</v>
       </c>
       <c r="B70" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7447,42 +7455,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447118</v>
+        <v>447114</v>
       </c>
       <c r="R70" t="n">
-        <v>6804529</v>
+        <v>6804581</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893315</v>
+        <v>129893393</v>
       </c>
       <c r="B75" t="n">
-        <v>57736</v>
+        <v>79081</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7945,42 +7945,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447115</v>
+        <v>447110</v>
       </c>
       <c r="R75" t="n">
-        <v>6804531</v>
+        <v>6804630</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8013,6 +8005,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8039,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893393</v>
+        <v>129893356</v>
       </c>
       <c r="B76" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8050,21 +8047,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8074,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447110</v>
+        <v>447165</v>
       </c>
       <c r="R76" t="n">
-        <v>6804630</v>
+        <v>6804365</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8110,11 +8107,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8141,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893356</v>
+        <v>129893315</v>
       </c>
       <c r="B77" t="n">
-        <v>78838</v>
+        <v>57736</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8152,34 +8144,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447165</v>
+        <v>447115</v>
       </c>
       <c r="R77" t="n">
-        <v>6804365</v>
+        <v>6804531</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893353</v>
+        <v>129893395</v>
       </c>
       <c r="B78" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8249,21 +8249,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447206</v>
+        <v>447137</v>
       </c>
       <c r="R78" t="n">
-        <v>6804417</v>
+        <v>6804440</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8309,6 +8309,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8335,32 +8340,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893306</v>
+        <v>129893368</v>
       </c>
       <c r="B79" t="n">
-        <v>79700</v>
+        <v>90981</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8370,10 +8375,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447282</v>
+        <v>447279</v>
       </c>
       <c r="R79" t="n">
-        <v>6804440</v>
+        <v>6804380</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8414,6 +8419,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8529,10 +8535,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893395</v>
+        <v>129893306</v>
       </c>
       <c r="B81" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8540,21 +8546,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8564,7 +8570,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447137</v>
+        <v>447282</v>
       </c>
       <c r="R81" t="n">
         <v>6804440</v>
@@ -8600,11 +8606,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8631,32 +8632,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893368</v>
+        <v>129893353</v>
       </c>
       <c r="B82" t="n">
-        <v>90981</v>
+        <v>78838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5685</v>
+        <v>6446</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8666,10 +8667,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447279</v>
+        <v>447206</v>
       </c>
       <c r="R82" t="n">
-        <v>6804380</v>
+        <v>6804417</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8710,7 +8711,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893303</v>
+        <v>129893397</v>
       </c>
       <c r="B83" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447143</v>
+        <v>447191</v>
       </c>
       <c r="R83" t="n">
-        <v>6804414</v>
+        <v>6804284</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8800,6 +8800,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8826,7 +8831,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893305</v>
+        <v>129893303</v>
       </c>
       <c r="B84" t="n">
         <v>79700</v>
@@ -8861,10 +8866,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447170</v>
+        <v>447143</v>
       </c>
       <c r="R84" t="n">
-        <v>6804401</v>
+        <v>6804414</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8923,10 +8928,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893397</v>
+        <v>129893348</v>
       </c>
       <c r="B85" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8934,21 +8939,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8958,10 +8963,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447191</v>
+        <v>447138</v>
       </c>
       <c r="R85" t="n">
-        <v>6804284</v>
+        <v>6804553</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8994,11 +8999,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9025,10 +9025,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893348</v>
+        <v>129893305</v>
       </c>
       <c r="B86" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9036,21 +9036,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447138</v>
+        <v>447170</v>
       </c>
       <c r="R86" t="n">
-        <v>6804553</v>
+        <v>6804401</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9224,10 +9224,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893405</v>
+        <v>129893307</v>
       </c>
       <c r="B88" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9235,21 +9235,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447280</v>
+        <v>447271</v>
       </c>
       <c r="R88" t="n">
-        <v>6804429</v>
+        <v>6804458</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9418,7 +9418,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893399</v>
+        <v>129893405</v>
       </c>
       <c r="B90" t="n">
         <v>79081</v>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447206</v>
+        <v>447280</v>
       </c>
       <c r="R90" t="n">
-        <v>6804317</v>
+        <v>6804429</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9515,10 +9515,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893307</v>
+        <v>129893399</v>
       </c>
       <c r="B91" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9526,21 +9526,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447271</v>
+        <v>447206</v>
       </c>
       <c r="R91" t="n">
-        <v>6804458</v>
+        <v>6804317</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9612,45 +9612,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893351</v>
+        <v>129893316</v>
       </c>
       <c r="B92" t="n">
-        <v>78838</v>
+        <v>56926</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447129</v>
+        <v>447102</v>
       </c>
       <c r="R92" t="n">
-        <v>6804505</v>
+        <v>6804551</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9709,53 +9717,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893316</v>
+        <v>129893351</v>
       </c>
       <c r="B93" t="n">
-        <v>56926</v>
+        <v>78838</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447102</v>
+        <v>447129</v>
       </c>
       <c r="R93" t="n">
-        <v>6804551</v>
+        <v>6804505</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893323</v>
+        <v>129893407</v>
       </c>
       <c r="B95" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,42 +9922,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447139</v>
+        <v>447258</v>
       </c>
       <c r="R95" t="n">
-        <v>6804556</v>
+        <v>6804469</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10016,10 +10008,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129893332</v>
+        <v>129893323</v>
       </c>
       <c r="B96" t="n">
-        <v>78839</v>
+        <v>57733</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10027,34 +10019,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447086</v>
+        <v>447139</v>
       </c>
       <c r="R96" t="n">
-        <v>6804674</v>
+        <v>6804556</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129893407</v>
+        <v>129893332</v>
       </c>
       <c r="B97" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,21 +10124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10148,10 +10148,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447258</v>
+        <v>447086</v>
       </c>
       <c r="R97" t="n">
-        <v>6804469</v>
+        <v>6804674</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893359</v>
+        <v>129893396</v>
       </c>
       <c r="B98" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447276</v>
+        <v>447170</v>
       </c>
       <c r="R98" t="n">
-        <v>6804418</v>
+        <v>6804344</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10281,6 +10281,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10307,10 +10312,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893396</v>
+        <v>129893359</v>
       </c>
       <c r="B99" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10318,21 +10323,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10342,10 +10347,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447170</v>
+        <v>447276</v>
       </c>
       <c r="R99" t="n">
-        <v>6804344</v>
+        <v>6804418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10378,11 +10383,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10409,10 +10409,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893310</v>
+        <v>129893350</v>
       </c>
       <c r="B100" t="n">
-        <v>79671</v>
+        <v>78838</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10420,21 +10420,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10444,10 +10444,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447280</v>
+        <v>447120</v>
       </c>
       <c r="R100" t="n">
-        <v>6804428</v>
+        <v>6804506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10506,10 +10506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893350</v>
+        <v>129893310</v>
       </c>
       <c r="B101" t="n">
-        <v>78838</v>
+        <v>79671</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10517,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447120</v>
+        <v>447280</v>
       </c>
       <c r="R101" t="n">
-        <v>6804506</v>
+        <v>6804428</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129893346</v>
+        <v>129893398</v>
       </c>
       <c r="B105" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447088</v>
+        <v>447189</v>
       </c>
       <c r="R105" t="n">
-        <v>6804609</v>
+        <v>6804301</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893299</v>
+        <v>129893346</v>
       </c>
       <c r="B106" t="n">
-        <v>79700</v>
+        <v>78838</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447141</v>
+        <v>447088</v>
       </c>
       <c r="R106" t="n">
-        <v>6804483</v>
+        <v>6804609</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893398</v>
+        <v>129893299</v>
       </c>
       <c r="B107" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447189</v>
+        <v>447141</v>
       </c>
       <c r="R107" t="n">
-        <v>6804301</v>
+        <v>6804483</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11185,7 +11185,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129893296</v>
+        <v>129893295</v>
       </c>
       <c r="B108" t="n">
         <v>79700</v>
@@ -11220,10 +11220,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447079</v>
+        <v>447085</v>
       </c>
       <c r="R108" t="n">
-        <v>6804660</v>
+        <v>6804671</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11476,10 +11476,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893322</v>
+        <v>129893296</v>
       </c>
       <c r="B111" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,42 +11487,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447105</v>
+        <v>447079</v>
       </c>
       <c r="R111" t="n">
-        <v>6804584</v>
+        <v>6804660</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11581,10 +11573,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893295</v>
+        <v>129893322</v>
       </c>
       <c r="B112" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11592,34 +11584,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447085</v>
+        <v>447105</v>
       </c>
       <c r="R112" t="n">
-        <v>6804671</v>
+        <v>6804584</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893314</v>
+        <v>129893300</v>
       </c>
       <c r="B113" t="n">
-        <v>57736</v>
+        <v>79700</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,42 +11689,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447227</v>
+        <v>447121</v>
       </c>
       <c r="R113" t="n">
-        <v>6804586</v>
+        <v>6804435</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11783,7 +11775,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893300</v>
+        <v>129893308</v>
       </c>
       <c r="B114" t="n">
         <v>79700</v>
@@ -11818,10 +11810,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447121</v>
+        <v>447248</v>
       </c>
       <c r="R114" t="n">
-        <v>6804435</v>
+        <v>6804484</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12079,10 +12071,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893308</v>
+        <v>129893314</v>
       </c>
       <c r="B117" t="n">
-        <v>79700</v>
+        <v>57736</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12090,34 +12082,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447248</v>
+        <v>447227</v>
       </c>
       <c r="R117" t="n">
-        <v>6804484</v>
+        <v>6804586</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129893325</v>
+        <v>129893302</v>
       </c>
       <c r="B118" t="n">
-        <v>57733</v>
+        <v>79700</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12187,42 +12187,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447201</v>
+        <v>447140</v>
       </c>
       <c r="R118" t="n">
-        <v>6804314</v>
+        <v>6804436</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12378,10 +12370,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893302</v>
+        <v>129893325</v>
       </c>
       <c r="B120" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12389,34 +12381,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447140</v>
+        <v>447201</v>
       </c>
       <c r="R120" t="n">
-        <v>6804436</v>
+        <v>6804314</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129893408</v>
+        <v>129893333</v>
       </c>
       <c r="B121" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,21 +12486,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447247</v>
+        <v>447284</v>
       </c>
       <c r="R121" t="n">
-        <v>6804486</v>
+        <v>6804412</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12572,10 +12572,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893355</v>
+        <v>129893401</v>
       </c>
       <c r="B122" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12583,21 +12583,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12607,10 +12607,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447175</v>
+        <v>447291</v>
       </c>
       <c r="R122" t="n">
-        <v>6804401</v>
+        <v>6804354</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12643,6 +12643,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12669,10 +12674,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893333</v>
+        <v>129893408</v>
       </c>
       <c r="B123" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12680,21 +12685,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12704,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447284</v>
+        <v>447247</v>
       </c>
       <c r="R123" t="n">
-        <v>6804412</v>
+        <v>6804486</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12766,10 +12771,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129893304</v>
+        <v>129893406</v>
       </c>
       <c r="B124" t="n">
-        <v>79700</v>
+        <v>79081</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12777,21 +12782,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12801,10 +12806,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447208</v>
+        <v>447282</v>
       </c>
       <c r="R124" t="n">
-        <v>6804423</v>
+        <v>6804440</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12837,6 +12842,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12863,10 +12873,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893406</v>
+        <v>129893304</v>
       </c>
       <c r="B125" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12874,21 +12884,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12898,10 +12908,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447282</v>
+        <v>447208</v>
       </c>
       <c r="R125" t="n">
-        <v>6804440</v>
+        <v>6804423</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12934,11 +12944,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12965,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893401</v>
+        <v>129893355</v>
       </c>
       <c r="B126" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12976,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13000,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447291</v>
+        <v>447175</v>
       </c>
       <c r="R126" t="n">
-        <v>6804354</v>
+        <v>6804401</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13036,11 +13041,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B11" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R11" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,6 +1641,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1667,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R12" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,11 +1743,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894023</v>
+        <v>129893953</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>78839</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447120</v>
+        <v>447186</v>
       </c>
       <c r="R13" t="n">
-        <v>6804670</v>
+        <v>6804347</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,11 +1840,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1871,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894050</v>
+        <v>129894023</v>
       </c>
       <c r="B14" t="n">
-        <v>78089</v>
+        <v>79081</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,21 +1877,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447251</v>
+        <v>447120</v>
       </c>
       <c r="R14" t="n">
-        <v>6804480</v>
+        <v>6804670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,13 +1939,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B15" t="n">
-        <v>78839</v>
+        <v>78089</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R15" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2753,53 +2753,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893945</v>
+        <v>129893956</v>
       </c>
       <c r="B23" t="n">
-        <v>56929</v>
+        <v>78839</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447140</v>
+        <v>447248</v>
       </c>
       <c r="R23" t="n">
-        <v>6804358</v>
+        <v>6804447</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893956</v>
+        <v>129894040</v>
       </c>
       <c r="B24" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447248</v>
+        <v>447244</v>
       </c>
       <c r="R24" t="n">
-        <v>6804447</v>
+        <v>6804361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,45 +2947,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129894040</v>
+        <v>129893945</v>
       </c>
       <c r="B25" t="n">
-        <v>79081</v>
+        <v>56929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447244</v>
+        <v>447140</v>
       </c>
       <c r="R25" t="n">
-        <v>6804361</v>
+        <v>6804358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -5131,10 +5131,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894041</v>
+        <v>129893933</v>
       </c>
       <c r="B47" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,34 +5142,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447242</v>
+        <v>447075</v>
       </c>
       <c r="R47" t="n">
-        <v>6804443</v>
+        <v>6804732</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894035</v>
+        <v>129893937</v>
       </c>
       <c r="B48" t="n">
-        <v>79081</v>
+        <v>57733</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5239,34 +5247,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447155</v>
+        <v>447059</v>
       </c>
       <c r="R48" t="n">
-        <v>6804339</v>
+        <v>6804587</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,7 +5341,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893933</v>
+        <v>129893936</v>
       </c>
       <c r="B49" t="n">
         <v>57733</v>
@@ -5368,10 +5384,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447075</v>
+        <v>447012</v>
       </c>
       <c r="R49" t="n">
-        <v>6804732</v>
+        <v>6804645</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5430,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893937</v>
+        <v>129894041</v>
       </c>
       <c r="B50" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,42 +5457,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447059</v>
+        <v>447242</v>
       </c>
       <c r="R50" t="n">
-        <v>6804587</v>
+        <v>6804443</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5535,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893936</v>
+        <v>129894035</v>
       </c>
       <c r="B51" t="n">
-        <v>57733</v>
+        <v>79081</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,42 +5554,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447012</v>
+        <v>447155</v>
       </c>
       <c r="R51" t="n">
-        <v>6804645</v>
+        <v>6804339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893395</v>
+        <v>129893306</v>
       </c>
       <c r="B78" t="n">
-        <v>79081</v>
+        <v>79700</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8249,21 +8249,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,7 +8273,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447137</v>
+        <v>447282</v>
       </c>
       <c r="R78" t="n">
         <v>6804440</v>
@@ -8309,11 +8309,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8340,32 +8335,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893368</v>
+        <v>129893353</v>
       </c>
       <c r="B79" t="n">
-        <v>90981</v>
+        <v>78838</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5685</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8375,10 +8370,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447279</v>
+        <v>447206</v>
       </c>
       <c r="R79" t="n">
-        <v>6804380</v>
+        <v>6804417</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8419,7 +8414,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8438,10 +8432,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893334</v>
+        <v>129893395</v>
       </c>
       <c r="B80" t="n">
-        <v>78839</v>
+        <v>79081</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8449,21 +8443,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8473,10 +8467,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447287</v>
+        <v>447137</v>
       </c>
       <c r="R80" t="n">
-        <v>6804433</v>
+        <v>6804440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8509,6 +8503,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8535,32 +8534,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893306</v>
+        <v>129893368</v>
       </c>
       <c r="B81" t="n">
-        <v>79700</v>
+        <v>90981</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8570,10 +8569,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447282</v>
+        <v>447279</v>
       </c>
       <c r="R81" t="n">
-        <v>6804440</v>
+        <v>6804380</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8614,6 +8613,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8632,10 +8632,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893353</v>
+        <v>129893334</v>
       </c>
       <c r="B82" t="n">
-        <v>78838</v>
+        <v>78839</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8643,21 +8643,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8667,10 +8667,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447206</v>
+        <v>447287</v>
       </c>
       <c r="R82" t="n">
-        <v>6804417</v>
+        <v>6804433</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893396</v>
+        <v>129893359</v>
       </c>
       <c r="B98" t="n">
-        <v>79081</v>
+        <v>78838</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447170</v>
+        <v>447276</v>
       </c>
       <c r="R98" t="n">
-        <v>6804344</v>
+        <v>6804418</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10281,11 +10281,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10312,7 +10307,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893359</v>
+        <v>129893350</v>
       </c>
       <c r="B99" t="n">
         <v>78838</v>
@@ -10347,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447276</v>
+        <v>447120</v>
       </c>
       <c r="R99" t="n">
-        <v>6804418</v>
+        <v>6804506</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10409,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893350</v>
+        <v>129893396</v>
       </c>
       <c r="B100" t="n">
-        <v>78838</v>
+        <v>79081</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10420,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10444,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447120</v>
+        <v>447170</v>
       </c>
       <c r="R100" t="n">
-        <v>6804506</v>
+        <v>6804344</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10480,6 +10475,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -12176,10 +12176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129893302</v>
+        <v>129893325</v>
       </c>
       <c r="B118" t="n">
-        <v>79700</v>
+        <v>57733</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12187,34 +12187,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447140</v>
+        <v>447201</v>
       </c>
       <c r="R118" t="n">
-        <v>6804436</v>
+        <v>6804314</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12273,10 +12281,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129893354</v>
+        <v>129893302</v>
       </c>
       <c r="B119" t="n">
-        <v>78838</v>
+        <v>79700</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12284,21 +12292,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12308,10 +12316,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447193</v>
+        <v>447140</v>
       </c>
       <c r="R119" t="n">
-        <v>6804389</v>
+        <v>6804436</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12370,10 +12378,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893325</v>
+        <v>129893354</v>
       </c>
       <c r="B120" t="n">
-        <v>57733</v>
+        <v>78838</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12381,42 +12389,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447201</v>
+        <v>447193</v>
       </c>
       <c r="R120" t="n">
-        <v>6804314</v>
+        <v>6804389</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894044</v>
+        <v>129893939</v>
       </c>
       <c r="B2" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446959</v>
+        <v>447133</v>
       </c>
       <c r="R2" t="n">
-        <v>6804780</v>
+        <v>6804362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129893913</v>
+        <v>129894044</v>
       </c>
       <c r="B3" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447127</v>
+        <v>446959</v>
       </c>
       <c r="R3" t="n">
-        <v>6804438</v>
+        <v>6804780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893971</v>
+        <v>129893913</v>
       </c>
       <c r="B4" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447009</v>
+        <v>447127</v>
       </c>
       <c r="R4" t="n">
-        <v>6804689</v>
+        <v>6804438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893939</v>
+        <v>129893971</v>
       </c>
       <c r="B5" t="n">
-        <v>57733</v>
+        <v>78841</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447133</v>
+        <v>447009</v>
       </c>
       <c r="R5" t="n">
-        <v>6804362</v>
+        <v>6804689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
         <v>129894024</v>
       </c>
       <c r="B6" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
         <v>129893972</v>
       </c>
       <c r="B7" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,45 +1269,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893970</v>
+        <v>129893963</v>
       </c>
       <c r="B8" t="n">
-        <v>78838</v>
+        <v>8450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447006</v>
+        <v>447084</v>
       </c>
       <c r="R8" t="n">
-        <v>6804685</v>
+        <v>6804507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1357,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1366,10 +1376,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893974</v>
+        <v>129893970</v>
       </c>
       <c r="B9" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447014</v>
+        <v>447006</v>
       </c>
       <c r="R9" t="n">
-        <v>6804644</v>
+        <v>6804685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,54 +1473,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893963</v>
+        <v>129893974</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>78841</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447084</v>
+        <v>447014</v>
       </c>
       <c r="R10" t="n">
-        <v>6804507</v>
+        <v>6804644</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1552,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1573,7 +1573,7 @@
         <v>129894030</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>129893949</v>
       </c>
       <c r="B12" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129893953</v>
+        <v>129894023</v>
       </c>
       <c r="B13" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447186</v>
+        <v>447120</v>
       </c>
       <c r="R13" t="n">
-        <v>6804347</v>
+        <v>6804670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,6 +1840,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1866,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894023</v>
+        <v>129894050</v>
       </c>
       <c r="B14" t="n">
-        <v>79081</v>
+        <v>78092</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1877,21 +1882,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1901,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447120</v>
+        <v>447251</v>
       </c>
       <c r="R14" t="n">
-        <v>6804670</v>
+        <v>6804480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,17 +1944,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894050</v>
+        <v>129893953</v>
       </c>
       <c r="B15" t="n">
-        <v>78089</v>
+        <v>78842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447251</v>
+        <v>447186</v>
       </c>
       <c r="R15" t="n">
-        <v>6804480</v>
+        <v>6804347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,7 +2048,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>129894033</v>
       </c>
       <c r="B16" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>129894043</v>
       </c>
       <c r="B17" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2260,45 +2260,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893973</v>
+        <v>129893923</v>
       </c>
       <c r="B18" t="n">
-        <v>78838</v>
+        <v>56927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447018</v>
+        <v>447079</v>
       </c>
       <c r="R18" t="n">
-        <v>6804657</v>
+        <v>6804592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,53 +2365,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893923</v>
+        <v>129893973</v>
       </c>
       <c r="B19" t="n">
-        <v>56926</v>
+        <v>78841</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447079</v>
+        <v>447018</v>
       </c>
       <c r="R19" t="n">
-        <v>6804592</v>
+        <v>6804657</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,10 +2462,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894039</v>
+        <v>129894042</v>
       </c>
       <c r="B20" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447226</v>
+        <v>447262</v>
       </c>
       <c r="R20" t="n">
-        <v>6804354</v>
+        <v>6804466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,10 +2559,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894042</v>
+        <v>129894039</v>
       </c>
       <c r="B21" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447262</v>
+        <v>447226</v>
       </c>
       <c r="R21" t="n">
-        <v>6804466</v>
+        <v>6804354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893976</v>
+        <v>129894040</v>
       </c>
       <c r="B22" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,21 +2667,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447071</v>
+        <v>447244</v>
       </c>
       <c r="R22" t="n">
-        <v>6804595</v>
+        <v>6804361</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,45 +2753,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893956</v>
+        <v>129893945</v>
       </c>
       <c r="B23" t="n">
-        <v>78839</v>
+        <v>56930</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447248</v>
+        <v>447140</v>
       </c>
       <c r="R23" t="n">
-        <v>6804447</v>
+        <v>6804358</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,10 +2858,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894040</v>
+        <v>129893976</v>
       </c>
       <c r="B24" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2861,21 +2869,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2885,10 +2893,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447244</v>
+        <v>447071</v>
       </c>
       <c r="R24" t="n">
-        <v>6804361</v>
+        <v>6804595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,53 +2955,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893945</v>
+        <v>129893956</v>
       </c>
       <c r="B25" t="n">
-        <v>56929</v>
+        <v>78842</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447140</v>
+        <v>447248</v>
       </c>
       <c r="R25" t="n">
-        <v>6804358</v>
+        <v>6804447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3162,7 +3162,7 @@
         <v>129893954</v>
       </c>
       <c r="B27" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893935</v>
+        <v>129894029</v>
       </c>
       <c r="B28" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,42 +3267,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447017</v>
+        <v>447078</v>
       </c>
       <c r="R28" t="n">
-        <v>6804662</v>
+        <v>6804574</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3335,6 +3327,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3361,10 +3358,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893919</v>
+        <v>129893979</v>
       </c>
       <c r="B29" t="n">
-        <v>79671</v>
+        <v>78841</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3372,21 +3369,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3396,10 +3393,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447260</v>
+        <v>447104</v>
       </c>
       <c r="R29" t="n">
-        <v>6804349</v>
+        <v>6804432</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3458,10 +3455,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894047</v>
+        <v>129893935</v>
       </c>
       <c r="B30" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3469,34 +3466,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447264</v>
+        <v>447017</v>
       </c>
       <c r="R30" t="n">
-        <v>6804394</v>
+        <v>6804662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3529,11 +3534,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3560,10 +3560,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894029</v>
+        <v>129894047</v>
       </c>
       <c r="B31" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3595,10 +3595,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447078</v>
+        <v>447264</v>
       </c>
       <c r="R31" t="n">
-        <v>6804574</v>
+        <v>6804394</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3635,7 +3635,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3662,10 +3662,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893979</v>
+        <v>129893919</v>
       </c>
       <c r="B32" t="n">
-        <v>78838</v>
+        <v>79674</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447104</v>
+        <v>447260</v>
       </c>
       <c r="R32" t="n">
-        <v>6804432</v>
+        <v>6804349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894036</v>
+        <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447177</v>
+        <v>447019</v>
       </c>
       <c r="R33" t="n">
-        <v>6804353</v>
+        <v>6804831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,6 +3830,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3856,10 +3861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894026</v>
+        <v>129894028</v>
       </c>
       <c r="B34" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3891,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447019</v>
+        <v>447038</v>
       </c>
       <c r="R34" t="n">
-        <v>6804831</v>
+        <v>6804585</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3927,11 +3932,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,10 +3958,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894028</v>
+        <v>129894036</v>
       </c>
       <c r="B35" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447038</v>
+        <v>447177</v>
       </c>
       <c r="R35" t="n">
-        <v>6804585</v>
+        <v>6804353</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,10 +4055,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894034</v>
+        <v>129894046</v>
       </c>
       <c r="B36" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,16 +4084,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447146</v>
+        <v>447137</v>
       </c>
       <c r="R36" t="n">
-        <v>6804328</v>
+        <v>6804362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,12 +4131,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4152,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894046</v>
+        <v>129894034</v>
       </c>
       <c r="B37" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4181,19 +4190,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447137</v>
+        <v>447146</v>
       </c>
       <c r="R37" t="n">
-        <v>6804362</v>
+        <v>6804328</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,18 +4234,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893955</v>
+        <v>129893920</v>
       </c>
       <c r="B38" t="n">
-        <v>78839</v>
+        <v>79674</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447237</v>
+        <v>447249</v>
       </c>
       <c r="R38" t="n">
-        <v>6804433</v>
+        <v>6804413</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893920</v>
+        <v>129893955</v>
       </c>
       <c r="B39" t="n">
-        <v>79671</v>
+        <v>78842</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447249</v>
+        <v>447237</v>
       </c>
       <c r="R39" t="n">
-        <v>6804413</v>
+        <v>6804433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4455,7 +4455,7 @@
         <v>129893977</v>
       </c>
       <c r="B40" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894027</v>
+        <v>129893948</v>
       </c>
       <c r="B41" t="n">
-        <v>79081</v>
+        <v>78842</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446979</v>
+        <v>446971</v>
       </c>
       <c r="R41" t="n">
-        <v>6804787</v>
+        <v>6804769</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893983</v>
+        <v>129894027</v>
       </c>
       <c r="B42" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447195</v>
+        <v>446979</v>
       </c>
       <c r="R42" t="n">
-        <v>6804348</v>
+        <v>6804787</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129893975</v>
+        <v>129893983</v>
       </c>
       <c r="B43" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447017</v>
+        <v>447195</v>
       </c>
       <c r="R43" t="n">
-        <v>6804644</v>
+        <v>6804348</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893948</v>
+        <v>129893975</v>
       </c>
       <c r="B44" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,21 +4851,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446971</v>
+        <v>447017</v>
       </c>
       <c r="R44" t="n">
-        <v>6804769</v>
+        <v>6804644</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893980</v>
+        <v>129893933</v>
       </c>
       <c r="B45" t="n">
-        <v>78838</v>
+        <v>57734</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,34 +4948,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447136</v>
+        <v>447075</v>
       </c>
       <c r="R45" t="n">
-        <v>6804407</v>
+        <v>6804732</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893969</v>
+        <v>129893937</v>
       </c>
       <c r="B46" t="n">
-        <v>78838</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5045,34 +5053,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447006</v>
+        <v>447059</v>
       </c>
       <c r="R46" t="n">
-        <v>6804728</v>
+        <v>6804587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893933</v>
+        <v>129893936</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5174,10 +5190,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447075</v>
+        <v>447012</v>
       </c>
       <c r="R47" t="n">
-        <v>6804732</v>
+        <v>6804645</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5236,10 +5252,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893937</v>
+        <v>129893918</v>
       </c>
       <c r="B48" t="n">
-        <v>57733</v>
+        <v>79674</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5247,42 +5263,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447059</v>
+        <v>447021</v>
       </c>
       <c r="R48" t="n">
-        <v>6804587</v>
+        <v>6804646</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893936</v>
+        <v>129893951</v>
       </c>
       <c r="B49" t="n">
-        <v>57733</v>
+        <v>78842</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,42 +5360,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447012</v>
+        <v>447014</v>
       </c>
       <c r="R49" t="n">
-        <v>6804645</v>
+        <v>6804638</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5449,7 +5449,7 @@
         <v>129894041</v>
       </c>
       <c r="B50" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5546,7 +5546,7 @@
         <v>129894035</v>
       </c>
       <c r="B51" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893918</v>
+        <v>129893980</v>
       </c>
       <c r="B52" t="n">
-        <v>79671</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447021</v>
+        <v>447136</v>
       </c>
       <c r="R52" t="n">
-        <v>6804646</v>
+        <v>6804407</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893951</v>
+        <v>129893969</v>
       </c>
       <c r="B53" t="n">
-        <v>78839</v>
+        <v>78841</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447014</v>
+        <v>447006</v>
       </c>
       <c r="R53" t="n">
-        <v>6804638</v>
+        <v>6804728</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5837,7 +5837,7 @@
         <v>129893932</v>
       </c>
       <c r="B54" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5942,7 +5942,7 @@
         <v>129893938</v>
       </c>
       <c r="B55" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6047,7 +6047,7 @@
         <v>129893924</v>
       </c>
       <c r="B56" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>129894045</v>
       </c>
       <c r="B57" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129893950</v>
+        <v>129894025</v>
       </c>
       <c r="B58" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,21 +6267,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447015</v>
+        <v>447101</v>
       </c>
       <c r="R58" t="n">
-        <v>6804655</v>
+        <v>6804700</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893934</v>
+        <v>129893950</v>
       </c>
       <c r="B59" t="n">
-        <v>57733</v>
+        <v>78842</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6364,42 +6364,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447006</v>
+        <v>447015</v>
       </c>
       <c r="R59" t="n">
-        <v>6804684</v>
+        <v>6804655</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6458,10 +6450,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129894025</v>
+        <v>129893934</v>
       </c>
       <c r="B60" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6469,34 +6461,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447101</v>
+        <v>447006</v>
       </c>
       <c r="R60" t="n">
-        <v>6804700</v>
+        <v>6804684</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6558,7 +6558,7 @@
         <v>129893968</v>
       </c>
       <c r="B61" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>129893967</v>
       </c>
       <c r="B62" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129894038</v>
+        <v>129893921</v>
       </c>
       <c r="B63" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,34 +6760,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447196</v>
+        <v>447004</v>
       </c>
       <c r="R63" t="n">
-        <v>6804341</v>
+        <v>6804712</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6849,7 +6857,7 @@
         <v>129893914</v>
       </c>
       <c r="B64" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6946,7 +6954,7 @@
         <v>129893912</v>
       </c>
       <c r="B65" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7043,7 +7051,7 @@
         <v>129893982</v>
       </c>
       <c r="B66" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7137,10 +7145,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893952</v>
+        <v>129894038</v>
       </c>
       <c r="B67" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,21 +7156,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7180,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447138</v>
+        <v>447196</v>
       </c>
       <c r="R67" t="n">
-        <v>6804405</v>
+        <v>6804341</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7234,10 +7242,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893921</v>
+        <v>129893952</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>78842</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7245,42 +7253,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447004</v>
+        <v>447138</v>
       </c>
       <c r="R68" t="n">
-        <v>6804712</v>
+        <v>6804405</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,7 +7342,7 @@
         <v>129893324</v>
       </c>
       <c r="B69" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>129893347</v>
       </c>
       <c r="B70" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>129893402</v>
       </c>
       <c r="B71" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129893404</v>
       </c>
       <c r="B72" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>129893403</v>
       </c>
       <c r="B73" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>129893400</v>
       </c>
       <c r="B74" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893393</v>
+        <v>129893315</v>
       </c>
       <c r="B75" t="n">
-        <v>79081</v>
+        <v>57737</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7945,34 +7945,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447110</v>
+        <v>447115</v>
       </c>
       <c r="R75" t="n">
-        <v>6804630</v>
+        <v>6804531</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,11 +8013,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8036,10 +8039,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893356</v>
+        <v>129893393</v>
       </c>
       <c r="B76" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8047,21 +8050,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8071,10 +8074,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447165</v>
+        <v>447110</v>
       </c>
       <c r="R76" t="n">
-        <v>6804365</v>
+        <v>6804630</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8107,6 +8110,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8133,10 +8141,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893315</v>
+        <v>129893356</v>
       </c>
       <c r="B77" t="n">
-        <v>57736</v>
+        <v>78841</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,42 +8152,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447115</v>
+        <v>447165</v>
       </c>
       <c r="R77" t="n">
-        <v>6804531</v>
+        <v>6804365</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8241,7 +8241,7 @@
         <v>129893306</v>
       </c>
       <c r="B78" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8338,7 +8338,7 @@
         <v>129893353</v>
       </c>
       <c r="B79" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8432,32 +8432,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893395</v>
+        <v>129893368</v>
       </c>
       <c r="B80" t="n">
-        <v>79081</v>
+        <v>90984</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5685</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8467,10 +8467,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447137</v>
+        <v>447279</v>
       </c>
       <c r="R80" t="n">
-        <v>6804440</v>
+        <v>6804380</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8505,17 +8505,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8534,32 +8530,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893368</v>
+        <v>129893395</v>
       </c>
       <c r="B81" t="n">
-        <v>90981</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8565,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447279</v>
+        <v>447137</v>
       </c>
       <c r="R81" t="n">
-        <v>6804380</v>
+        <v>6804440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8607,13 +8603,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8635,7 +8635,7 @@
         <v>129893334</v>
       </c>
       <c r="B82" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8729,10 +8729,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893397</v>
+        <v>129893303</v>
       </c>
       <c r="B83" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447191</v>
+        <v>447143</v>
       </c>
       <c r="R83" t="n">
-        <v>6804284</v>
+        <v>6804414</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8800,11 +8800,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8831,10 +8826,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893303</v>
+        <v>129893348</v>
       </c>
       <c r="B84" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8842,21 +8837,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8866,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447143</v>
+        <v>447138</v>
       </c>
       <c r="R84" t="n">
-        <v>6804414</v>
+        <v>6804553</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8928,10 +8923,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893348</v>
+        <v>129893305</v>
       </c>
       <c r="B85" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8939,21 +8934,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8963,10 +8958,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447138</v>
+        <v>447170</v>
       </c>
       <c r="R85" t="n">
-        <v>6804553</v>
+        <v>6804401</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9025,10 +9020,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893305</v>
+        <v>129893397</v>
       </c>
       <c r="B86" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9036,21 +9031,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9060,10 +9055,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447170</v>
+        <v>447191</v>
       </c>
       <c r="R86" t="n">
-        <v>6804401</v>
+        <v>6804284</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9096,6 +9091,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9125,7 +9125,7 @@
         <v>129893392</v>
       </c>
       <c r="B87" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9224,10 +9224,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893307</v>
+        <v>129893405</v>
       </c>
       <c r="B88" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9235,21 +9235,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447271</v>
+        <v>447280</v>
       </c>
       <c r="R88" t="n">
-        <v>6804458</v>
+        <v>6804429</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9321,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893360</v>
+        <v>129893399</v>
       </c>
       <c r="B89" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9332,21 +9332,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447286</v>
+        <v>447206</v>
       </c>
       <c r="R89" t="n">
-        <v>6804433</v>
+        <v>6804317</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893405</v>
+        <v>129893307</v>
       </c>
       <c r="B90" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9429,21 +9429,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447280</v>
+        <v>447271</v>
       </c>
       <c r="R90" t="n">
-        <v>6804429</v>
+        <v>6804458</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9515,10 +9515,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893399</v>
+        <v>129893360</v>
       </c>
       <c r="B91" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9526,21 +9526,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447206</v>
+        <v>447286</v>
       </c>
       <c r="R91" t="n">
-        <v>6804317</v>
+        <v>6804433</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9612,53 +9612,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893316</v>
+        <v>129893351</v>
       </c>
       <c r="B92" t="n">
-        <v>56926</v>
+        <v>78841</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447102</v>
+        <v>447129</v>
       </c>
       <c r="R92" t="n">
-        <v>6804551</v>
+        <v>6804505</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9717,10 +9709,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893351</v>
+        <v>129893309</v>
       </c>
       <c r="B93" t="n">
-        <v>78838</v>
+        <v>79674</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9728,21 +9720,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9752,10 +9744,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447129</v>
+        <v>447247</v>
       </c>
       <c r="R93" t="n">
-        <v>6804505</v>
+        <v>6804552</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9814,45 +9806,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129893309</v>
+        <v>129893316</v>
       </c>
       <c r="B94" t="n">
-        <v>79671</v>
+        <v>56927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447247</v>
+        <v>447102</v>
       </c>
       <c r="R94" t="n">
-        <v>6804552</v>
+        <v>6804551</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893407</v>
+        <v>129893323</v>
       </c>
       <c r="B95" t="n">
-        <v>79081</v>
+        <v>57734</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,34 +9922,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447258</v>
+        <v>447139</v>
       </c>
       <c r="R95" t="n">
-        <v>6804469</v>
+        <v>6804556</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10008,10 +10016,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129893323</v>
+        <v>129893407</v>
       </c>
       <c r="B96" t="n">
-        <v>57733</v>
+        <v>79084</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10019,42 +10027,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447139</v>
+        <v>447258</v>
       </c>
       <c r="R96" t="n">
-        <v>6804556</v>
+        <v>6804469</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10116,7 +10116,7 @@
         <v>129893332</v>
       </c>
       <c r="B97" t="n">
-        <v>78839</v>
+        <v>78842</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893359</v>
+        <v>129893396</v>
       </c>
       <c r="B98" t="n">
-        <v>78838</v>
+        <v>79084</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447276</v>
+        <v>447170</v>
       </c>
       <c r="R98" t="n">
-        <v>6804418</v>
+        <v>6804344</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10281,6 +10281,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10307,10 +10312,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893350</v>
+        <v>129893310</v>
       </c>
       <c r="B99" t="n">
-        <v>78838</v>
+        <v>79674</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10318,21 +10323,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10342,10 +10347,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447120</v>
+        <v>447280</v>
       </c>
       <c r="R99" t="n">
-        <v>6804506</v>
+        <v>6804428</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10409,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893396</v>
+        <v>129893359</v>
       </c>
       <c r="B100" t="n">
-        <v>79081</v>
+        <v>78841</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10420,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10444,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447170</v>
+        <v>447276</v>
       </c>
       <c r="R100" t="n">
-        <v>6804344</v>
+        <v>6804418</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,11 +10480,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10506,10 +10506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893310</v>
+        <v>129893350</v>
       </c>
       <c r="B101" t="n">
-        <v>79671</v>
+        <v>78841</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10517,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447280</v>
+        <v>447120</v>
       </c>
       <c r="R101" t="n">
-        <v>6804428</v>
+        <v>6804506</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10606,7 +10606,7 @@
         <v>129893344</v>
       </c>
       <c r="B102" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>129893357</v>
       </c>
       <c r="B103" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>129893301</v>
       </c>
       <c r="B104" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>129893398</v>
       </c>
       <c r="B105" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>129893346</v>
       </c>
       <c r="B106" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>129893299</v>
       </c>
       <c r="B107" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129893295</v>
+        <v>129893322</v>
       </c>
       <c r="B108" t="n">
-        <v>79700</v>
+        <v>57734</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11196,34 +11196,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447085</v>
+        <v>447105</v>
       </c>
       <c r="R108" t="n">
-        <v>6804671</v>
+        <v>6804584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11282,10 +11290,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893358</v>
+        <v>129893295</v>
       </c>
       <c r="B109" t="n">
-        <v>78838</v>
+        <v>79703</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11293,21 +11301,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11317,10 +11325,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447319</v>
+        <v>447085</v>
       </c>
       <c r="R109" t="n">
-        <v>6804349</v>
+        <v>6804671</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11379,10 +11387,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893352</v>
+        <v>129893358</v>
       </c>
       <c r="B110" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11414,10 +11422,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447146</v>
+        <v>447319</v>
       </c>
       <c r="R110" t="n">
-        <v>6804415</v>
+        <v>6804349</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11476,10 +11484,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893296</v>
+        <v>129893352</v>
       </c>
       <c r="B111" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,21 +11495,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11511,10 +11519,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447079</v>
+        <v>447146</v>
       </c>
       <c r="R111" t="n">
-        <v>6804660</v>
+        <v>6804415</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11573,10 +11581,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893322</v>
+        <v>129893296</v>
       </c>
       <c r="B112" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11584,42 +11592,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447105</v>
+        <v>447079</v>
       </c>
       <c r="R112" t="n">
-        <v>6804584</v>
+        <v>6804660</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893300</v>
+        <v>129893394</v>
       </c>
       <c r="B113" t="n">
-        <v>79700</v>
+        <v>79084</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,21 +11689,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11713,10 +11713,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447121</v>
+        <v>447128</v>
       </c>
       <c r="R113" t="n">
-        <v>6804435</v>
+        <v>6804516</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11749,6 +11749,11 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11775,10 +11780,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893308</v>
+        <v>129893314</v>
       </c>
       <c r="B114" t="n">
-        <v>79700</v>
+        <v>57737</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11786,34 +11791,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447248</v>
+        <v>447227</v>
       </c>
       <c r="R114" t="n">
-        <v>6804484</v>
+        <v>6804586</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11872,10 +11885,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893297</v>
+        <v>129893300</v>
       </c>
       <c r="B115" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11907,10 +11920,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447104</v>
+        <v>447121</v>
       </c>
       <c r="R115" t="n">
-        <v>6804519</v>
+        <v>6804435</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11969,10 +11982,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893394</v>
+        <v>129893308</v>
       </c>
       <c r="B116" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11980,21 +11993,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12004,10 +12017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447128</v>
+        <v>447248</v>
       </c>
       <c r="R116" t="n">
-        <v>6804516</v>
+        <v>6804484</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12040,11 +12053,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12071,10 +12079,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893314</v>
+        <v>129893297</v>
       </c>
       <c r="B117" t="n">
-        <v>57736</v>
+        <v>79703</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12082,42 +12090,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447227</v>
+        <v>447104</v>
       </c>
       <c r="R117" t="n">
-        <v>6804586</v>
+        <v>6804519</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129893325</v>
+        <v>129893302</v>
       </c>
       <c r="B118" t="n">
-        <v>57733</v>
+        <v>79703</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12187,42 +12187,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447201</v>
+        <v>447140</v>
       </c>
       <c r="R118" t="n">
-        <v>6804314</v>
+        <v>6804436</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12281,10 +12273,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129893302</v>
+        <v>129893354</v>
       </c>
       <c r="B119" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12292,21 +12284,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12316,10 +12308,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447140</v>
+        <v>447193</v>
       </c>
       <c r="R119" t="n">
-        <v>6804436</v>
+        <v>6804389</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12378,10 +12370,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893354</v>
+        <v>129893325</v>
       </c>
       <c r="B120" t="n">
-        <v>78838</v>
+        <v>57734</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12389,34 +12381,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447193</v>
+        <v>447201</v>
       </c>
       <c r="R120" t="n">
-        <v>6804389</v>
+        <v>6804314</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129893333</v>
+        <v>129893401</v>
       </c>
       <c r="B121" t="n">
-        <v>78839</v>
+        <v>79084</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,21 +12486,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447284</v>
+        <v>447291</v>
       </c>
       <c r="R121" t="n">
-        <v>6804412</v>
+        <v>6804354</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12546,6 +12546,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12572,10 +12577,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893401</v>
+        <v>129893408</v>
       </c>
       <c r="B122" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12607,10 +12612,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447291</v>
+        <v>447247</v>
       </c>
       <c r="R122" t="n">
-        <v>6804354</v>
+        <v>6804486</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12643,11 +12648,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12674,10 +12674,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893408</v>
+        <v>129893406</v>
       </c>
       <c r="B123" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447247</v>
+        <v>447282</v>
       </c>
       <c r="R123" t="n">
-        <v>6804486</v>
+        <v>6804440</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12745,6 +12745,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12771,10 +12776,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129893406</v>
+        <v>129893304</v>
       </c>
       <c r="B124" t="n">
-        <v>79081</v>
+        <v>79703</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12782,21 +12787,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12806,10 +12811,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447282</v>
+        <v>447208</v>
       </c>
       <c r="R124" t="n">
-        <v>6804440</v>
+        <v>6804423</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12842,11 +12847,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12873,10 +12873,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893304</v>
+        <v>129893355</v>
       </c>
       <c r="B125" t="n">
-        <v>79700</v>
+        <v>78841</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12884,21 +12884,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447208</v>
+        <v>447175</v>
       </c>
       <c r="R125" t="n">
-        <v>6804423</v>
+        <v>6804401</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12970,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893355</v>
+        <v>129893333</v>
       </c>
       <c r="B126" t="n">
-        <v>78838</v>
+        <v>78842</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447175</v>
+        <v>447284</v>
       </c>
       <c r="R126" t="n">
-        <v>6804401</v>
+        <v>6804412</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13070,7 +13070,7 @@
         <v>129893349</v>
       </c>
       <c r="B127" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>129893298</v>
       </c>
       <c r="B128" t="n">
-        <v>79700</v>
+        <v>79703</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>129893345</v>
       </c>
       <c r="B129" t="n">
-        <v>78838</v>
+        <v>78841</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893939</v>
+        <v>129893913</v>
       </c>
       <c r="B2" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447133</v>
+        <v>447127</v>
       </c>
       <c r="R2" t="n">
-        <v>6804362</v>
+        <v>6804438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894044</v>
+        <v>129893971</v>
       </c>
       <c r="B3" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446959</v>
+        <v>447009</v>
       </c>
       <c r="R3" t="n">
-        <v>6804780</v>
+        <v>6804689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893913</v>
+        <v>129893939</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,34 +880,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447127</v>
+        <v>447133</v>
       </c>
       <c r="R4" t="n">
-        <v>6804438</v>
+        <v>6804362</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893971</v>
+        <v>129894044</v>
       </c>
       <c r="B5" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,21 +985,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1009,10 +1009,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447009</v>
+        <v>446959</v>
       </c>
       <c r="R5" t="n">
-        <v>6804689</v>
+        <v>6804780</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894024</v>
+        <v>129893972</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,34 +1082,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447139</v>
+        <v>447014</v>
       </c>
       <c r="R6" t="n">
-        <v>6804619</v>
+        <v>6804654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,6 +1153,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893972</v>
+        <v>129894024</v>
       </c>
       <c r="B7" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,37 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447014</v>
+        <v>447139</v>
       </c>
       <c r="R7" t="n">
-        <v>6804654</v>
+        <v>6804619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1251,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1269,54 +1269,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893963</v>
+        <v>129893970</v>
       </c>
       <c r="B8" t="n">
-        <v>8450</v>
+        <v>78841</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447084</v>
+        <v>447006</v>
       </c>
       <c r="R8" t="n">
-        <v>6804507</v>
+        <v>6804685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1376,7 +1366,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893970</v>
+        <v>129893974</v>
       </c>
       <c r="B9" t="n">
         <v>78841</v>
@@ -1411,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447006</v>
+        <v>447014</v>
       </c>
       <c r="R9" t="n">
-        <v>6804685</v>
+        <v>6804644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,45 +1463,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893974</v>
+        <v>129893963</v>
       </c>
       <c r="B10" t="n">
-        <v>78841</v>
+        <v>8450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447014</v>
+        <v>447084</v>
       </c>
       <c r="R10" t="n">
-        <v>6804644</v>
+        <v>6804507</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,6 +1551,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894023</v>
+        <v>129893953</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447120</v>
+        <v>447186</v>
       </c>
       <c r="R13" t="n">
-        <v>6804670</v>
+        <v>6804347</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,11 +1840,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1964,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893953</v>
+        <v>129894023</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1975,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +1999,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447186</v>
+        <v>447120</v>
       </c>
       <c r="R15" t="n">
-        <v>6804347</v>
+        <v>6804670</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2040,6 +2035,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,45 +2163,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894043</v>
+        <v>129893923</v>
       </c>
       <c r="B17" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447247</v>
+        <v>447079</v>
       </c>
       <c r="R17" t="n">
-        <v>6804534</v>
+        <v>6804592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,53 +2268,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893923</v>
+        <v>129893973</v>
       </c>
       <c r="B18" t="n">
-        <v>56927</v>
+        <v>78841</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447079</v>
+        <v>447018</v>
       </c>
       <c r="R18" t="n">
-        <v>6804592</v>
+        <v>6804657</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,10 +2365,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893973</v>
+        <v>129894043</v>
       </c>
       <c r="B19" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2376,21 +2376,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2400,10 +2400,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447018</v>
+        <v>447247</v>
       </c>
       <c r="R19" t="n">
-        <v>6804657</v>
+        <v>6804534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894042</v>
+        <v>129894039</v>
       </c>
       <c r="B20" t="n">
         <v>79084</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447262</v>
+        <v>447226</v>
       </c>
       <c r="R20" t="n">
-        <v>6804466</v>
+        <v>6804354</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894039</v>
+        <v>129894042</v>
       </c>
       <c r="B21" t="n">
         <v>79084</v>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447226</v>
+        <v>447262</v>
       </c>
       <c r="R21" t="n">
-        <v>6804354</v>
+        <v>6804466</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,53 +2753,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893945</v>
+        <v>129893976</v>
       </c>
       <c r="B23" t="n">
-        <v>56930</v>
+        <v>78841</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447140</v>
+        <v>447071</v>
       </c>
       <c r="R23" t="n">
-        <v>6804358</v>
+        <v>6804595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,45 +2850,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893976</v>
+        <v>129893945</v>
       </c>
       <c r="B24" t="n">
-        <v>78841</v>
+        <v>56930</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447071</v>
+        <v>447140</v>
       </c>
       <c r="R24" t="n">
-        <v>6804595</v>
+        <v>6804358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3052,54 +3052,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R26" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,7 +3131,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3149,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B27" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R27" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,6 +3237,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894029</v>
+        <v>129894047</v>
       </c>
       <c r="B28" t="n">
         <v>79084</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447078</v>
+        <v>447264</v>
       </c>
       <c r="R28" t="n">
-        <v>6804574</v>
+        <v>6804394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3358,10 +3358,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893979</v>
+        <v>129894029</v>
       </c>
       <c r="B29" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3369,21 +3369,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447104</v>
+        <v>447078</v>
       </c>
       <c r="R29" t="n">
-        <v>6804432</v>
+        <v>6804574</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3429,6 +3429,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3560,10 +3565,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894047</v>
+        <v>129893979</v>
       </c>
       <c r="B31" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3571,21 +3576,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3595,10 +3600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447264</v>
+        <v>447104</v>
       </c>
       <c r="R31" t="n">
-        <v>6804394</v>
+        <v>6804432</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3631,11 +3636,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894026</v>
+        <v>129893955</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447019</v>
+        <v>447237</v>
       </c>
       <c r="R33" t="n">
-        <v>6804831</v>
+        <v>6804433</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,11 +3830,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3861,7 +3856,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894028</v>
+        <v>129894026</v>
       </c>
       <c r="B34" t="n">
         <v>79084</v>
@@ -3896,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447038</v>
+        <v>447019</v>
       </c>
       <c r="R34" t="n">
-        <v>6804585</v>
+        <v>6804831</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3932,6 +3927,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,7 +3958,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894036</v>
+        <v>129894028</v>
       </c>
       <c r="B35" t="n">
         <v>79084</v>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447177</v>
+        <v>447038</v>
       </c>
       <c r="R35" t="n">
-        <v>6804353</v>
+        <v>6804585</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894046</v>
+        <v>129894036</v>
       </c>
       <c r="B36" t="n">
         <v>79084</v>
@@ -4084,19 +4084,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447137</v>
+        <v>447177</v>
       </c>
       <c r="R36" t="n">
-        <v>6804362</v>
+        <v>6804353</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4131,18 +4128,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,7 +4152,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894034</v>
+        <v>129894046</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4190,16 +4181,19 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447146</v>
+        <v>447137</v>
       </c>
       <c r="R37" t="n">
-        <v>6804328</v>
+        <v>6804362</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4234,12 +4228,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893920</v>
+        <v>129894034</v>
       </c>
       <c r="B38" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447249</v>
+        <v>447146</v>
       </c>
       <c r="R38" t="n">
-        <v>6804413</v>
+        <v>6804328</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893955</v>
+        <v>129893920</v>
       </c>
       <c r="B39" t="n">
-        <v>78842</v>
+        <v>79674</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447237</v>
+        <v>447249</v>
       </c>
       <c r="R39" t="n">
-        <v>6804433</v>
+        <v>6804413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893948</v>
+        <v>129894027</v>
       </c>
       <c r="B41" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446971</v>
+        <v>446979</v>
       </c>
       <c r="R41" t="n">
-        <v>6804769</v>
+        <v>6804787</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894027</v>
+        <v>129893983</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446979</v>
+        <v>447195</v>
       </c>
       <c r="R42" t="n">
-        <v>6804787</v>
+        <v>6804348</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,7 +4743,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129893983</v>
+        <v>129893975</v>
       </c>
       <c r="B43" t="n">
         <v>78841</v>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447195</v>
+        <v>447017</v>
       </c>
       <c r="R43" t="n">
-        <v>6804348</v>
+        <v>6804644</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893975</v>
+        <v>129893948</v>
       </c>
       <c r="B44" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,21 +4851,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447017</v>
+        <v>446971</v>
       </c>
       <c r="R44" t="n">
-        <v>6804644</v>
+        <v>6804769</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893933</v>
+        <v>129893980</v>
       </c>
       <c r="B45" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,42 +4948,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447075</v>
+        <v>447136</v>
       </c>
       <c r="R45" t="n">
-        <v>6804732</v>
+        <v>6804407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,10 +5034,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893937</v>
+        <v>129893969</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,42 +5045,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447059</v>
+        <v>447006</v>
       </c>
       <c r="R46" t="n">
-        <v>6804587</v>
+        <v>6804728</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5147,7 +5131,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893936</v>
+        <v>129893933</v>
       </c>
       <c r="B47" t="n">
         <v>57734</v>
@@ -5190,10 +5174,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447012</v>
+        <v>447075</v>
       </c>
       <c r="R47" t="n">
-        <v>6804645</v>
+        <v>6804732</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5252,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893918</v>
+        <v>129893937</v>
       </c>
       <c r="B48" t="n">
-        <v>79674</v>
+        <v>57734</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5263,34 +5247,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447021</v>
+        <v>447059</v>
       </c>
       <c r="R48" t="n">
-        <v>6804646</v>
+        <v>6804587</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893951</v>
+        <v>129893936</v>
       </c>
       <c r="B49" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,34 +5352,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447014</v>
+        <v>447012</v>
       </c>
       <c r="R49" t="n">
-        <v>6804638</v>
+        <v>6804645</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894035</v>
+        <v>129893918</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447155</v>
+        <v>447021</v>
       </c>
       <c r="R51" t="n">
-        <v>6804339</v>
+        <v>6804646</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893980</v>
+        <v>129894035</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447136</v>
+        <v>447155</v>
       </c>
       <c r="R52" t="n">
-        <v>6804407</v>
+        <v>6804339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893969</v>
+        <v>129893951</v>
       </c>
       <c r="B53" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447006</v>
+        <v>447014</v>
       </c>
       <c r="R53" t="n">
-        <v>6804728</v>
+        <v>6804638</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129894025</v>
+        <v>129893950</v>
       </c>
       <c r="B58" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,21 +6267,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447101</v>
+        <v>447015</v>
       </c>
       <c r="R58" t="n">
-        <v>6804700</v>
+        <v>6804655</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893950</v>
+        <v>129893968</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>78841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447015</v>
+        <v>446972</v>
       </c>
       <c r="R59" t="n">
-        <v>6804655</v>
+        <v>6804770</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893968</v>
+        <v>129894025</v>
       </c>
       <c r="B61" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446972</v>
+        <v>447101</v>
       </c>
       <c r="R61" t="n">
-        <v>6804770</v>
+        <v>6804700</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893921</v>
+        <v>129893982</v>
       </c>
       <c r="B63" t="n">
-        <v>57737</v>
+        <v>78841</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,42 +6760,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447004</v>
+        <v>447163</v>
       </c>
       <c r="R63" t="n">
-        <v>6804712</v>
+        <v>6804342</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6854,10 +6846,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129893914</v>
+        <v>129894038</v>
       </c>
       <c r="B64" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6865,21 +6857,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6889,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447244</v>
+        <v>447196</v>
       </c>
       <c r="R64" t="n">
-        <v>6804447</v>
+        <v>6804341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6951,10 +6943,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893912</v>
+        <v>129893921</v>
       </c>
       <c r="B65" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6962,34 +6954,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447082</v>
+        <v>447004</v>
       </c>
       <c r="R65" t="n">
-        <v>6804551</v>
+        <v>6804712</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7048,10 +7048,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893982</v>
+        <v>129893914</v>
       </c>
       <c r="B66" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7059,21 +7059,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7083,10 +7083,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447163</v>
+        <v>447244</v>
       </c>
       <c r="R66" t="n">
-        <v>6804342</v>
+        <v>6804447</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7145,10 +7145,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129894038</v>
+        <v>129893912</v>
       </c>
       <c r="B67" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7156,21 +7156,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7180,10 +7180,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447196</v>
+        <v>447082</v>
       </c>
       <c r="R67" t="n">
-        <v>6804341</v>
+        <v>6804551</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129893324</v>
+        <v>129893347</v>
       </c>
       <c r="B69" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7350,42 +7350,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447118</v>
+        <v>447114</v>
       </c>
       <c r="R69" t="n">
-        <v>6804529</v>
+        <v>6804581</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7444,10 +7436,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893347</v>
+        <v>129893324</v>
       </c>
       <c r="B70" t="n">
-        <v>78841</v>
+        <v>57734</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,34 +7447,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447114</v>
+        <v>447118</v>
       </c>
       <c r="R70" t="n">
-        <v>6804581</v>
+        <v>6804529</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893315</v>
+        <v>129893393</v>
       </c>
       <c r="B75" t="n">
-        <v>57737</v>
+        <v>79084</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7945,42 +7945,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447115</v>
+        <v>447110</v>
       </c>
       <c r="R75" t="n">
-        <v>6804531</v>
+        <v>6804630</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8013,6 +8005,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8039,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893393</v>
+        <v>129893356</v>
       </c>
       <c r="B76" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8050,21 +8047,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8074,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447110</v>
+        <v>447165</v>
       </c>
       <c r="R76" t="n">
-        <v>6804630</v>
+        <v>6804365</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8110,11 +8107,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8141,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893356</v>
+        <v>129893315</v>
       </c>
       <c r="B77" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8152,34 +8144,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447165</v>
+        <v>447115</v>
       </c>
       <c r="R77" t="n">
-        <v>6804365</v>
+        <v>6804531</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893306</v>
+        <v>129893334</v>
       </c>
       <c r="B78" t="n">
-        <v>79703</v>
+        <v>78842</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8249,21 +8249,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447282</v>
+        <v>447287</v>
       </c>
       <c r="R78" t="n">
-        <v>6804440</v>
+        <v>6804433</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8335,10 +8335,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893353</v>
+        <v>129893306</v>
       </c>
       <c r="B79" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8346,21 +8346,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447206</v>
+        <v>447282</v>
       </c>
       <c r="R79" t="n">
-        <v>6804417</v>
+        <v>6804440</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8530,10 +8530,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893395</v>
+        <v>129893353</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447137</v>
+        <v>447206</v>
       </c>
       <c r="R81" t="n">
-        <v>6804440</v>
+        <v>6804417</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8601,11 +8601,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8632,10 +8627,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893334</v>
+        <v>129893395</v>
       </c>
       <c r="B82" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8643,21 +8638,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8667,10 +8662,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447287</v>
+        <v>447137</v>
       </c>
       <c r="R82" t="n">
-        <v>6804433</v>
+        <v>6804440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8703,6 +8698,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8826,10 +8826,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893348</v>
+        <v>129893305</v>
       </c>
       <c r="B84" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8837,21 +8837,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447138</v>
+        <v>447170</v>
       </c>
       <c r="R84" t="n">
-        <v>6804553</v>
+        <v>6804401</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8923,10 +8923,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893305</v>
+        <v>129893397</v>
       </c>
       <c r="B85" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8934,21 +8934,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447170</v>
+        <v>447191</v>
       </c>
       <c r="R85" t="n">
-        <v>6804401</v>
+        <v>6804284</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8994,6 +8994,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9020,10 +9025,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893397</v>
+        <v>129893348</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9031,21 +9036,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9055,10 +9060,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447191</v>
+        <v>447138</v>
       </c>
       <c r="R86" t="n">
-        <v>6804284</v>
+        <v>6804553</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9091,11 +9096,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9224,10 +9224,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893405</v>
+        <v>129893307</v>
       </c>
       <c r="B88" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9235,21 +9235,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447280</v>
+        <v>447271</v>
       </c>
       <c r="R88" t="n">
-        <v>6804429</v>
+        <v>6804458</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9321,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893399</v>
+        <v>129893360</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9332,21 +9332,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447206</v>
+        <v>447286</v>
       </c>
       <c r="R89" t="n">
-        <v>6804317</v>
+        <v>6804433</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893307</v>
+        <v>129893405</v>
       </c>
       <c r="B90" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9429,21 +9429,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447271</v>
+        <v>447280</v>
       </c>
       <c r="R90" t="n">
-        <v>6804458</v>
+        <v>6804429</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9515,10 +9515,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893360</v>
+        <v>129893399</v>
       </c>
       <c r="B91" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9526,21 +9526,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447286</v>
+        <v>447206</v>
       </c>
       <c r="R91" t="n">
-        <v>6804433</v>
+        <v>6804317</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893351</v>
+        <v>129893309</v>
       </c>
       <c r="B92" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9623,21 +9623,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9647,10 +9647,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447129</v>
+        <v>447247</v>
       </c>
       <c r="R92" t="n">
-        <v>6804505</v>
+        <v>6804552</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9709,10 +9709,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893309</v>
+        <v>129893351</v>
       </c>
       <c r="B93" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9720,21 +9720,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9744,10 +9744,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447247</v>
+        <v>447129</v>
       </c>
       <c r="R93" t="n">
-        <v>6804552</v>
+        <v>6804505</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893323</v>
+        <v>129893407</v>
       </c>
       <c r="B95" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,42 +9922,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447139</v>
+        <v>447258</v>
       </c>
       <c r="R95" t="n">
-        <v>6804556</v>
+        <v>6804469</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10016,10 +10008,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129893407</v>
+        <v>129893332</v>
       </c>
       <c r="B96" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10027,21 +10019,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10051,10 +10043,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447258</v>
+        <v>447086</v>
       </c>
       <c r="R96" t="n">
-        <v>6804469</v>
+        <v>6804674</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10113,10 +10105,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129893332</v>
+        <v>129893323</v>
       </c>
       <c r="B97" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,34 +10116,42 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447086</v>
+        <v>447139</v>
       </c>
       <c r="R97" t="n">
-        <v>6804674</v>
+        <v>6804556</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893396</v>
+        <v>129893350</v>
       </c>
       <c r="B98" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447170</v>
+        <v>447120</v>
       </c>
       <c r="R98" t="n">
-        <v>6804344</v>
+        <v>6804506</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10281,11 +10281,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10312,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893310</v>
+        <v>129893359</v>
       </c>
       <c r="B99" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10323,21 +10318,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10347,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447280</v>
+        <v>447276</v>
       </c>
       <c r="R99" t="n">
-        <v>6804428</v>
+        <v>6804418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10409,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893359</v>
+        <v>129893396</v>
       </c>
       <c r="B100" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10420,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10444,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447276</v>
+        <v>447170</v>
       </c>
       <c r="R100" t="n">
-        <v>6804418</v>
+        <v>6804344</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10480,6 +10475,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10506,10 +10506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893350</v>
+        <v>129893310</v>
       </c>
       <c r="B101" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10517,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447120</v>
+        <v>447280</v>
       </c>
       <c r="R101" t="n">
-        <v>6804506</v>
+        <v>6804428</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129893398</v>
+        <v>129893346</v>
       </c>
       <c r="B105" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447189</v>
+        <v>447088</v>
       </c>
       <c r="R105" t="n">
-        <v>6804301</v>
+        <v>6804609</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893346</v>
+        <v>129893299</v>
       </c>
       <c r="B106" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447088</v>
+        <v>447141</v>
       </c>
       <c r="R106" t="n">
-        <v>6804609</v>
+        <v>6804483</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893299</v>
+        <v>129893398</v>
       </c>
       <c r="B107" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447141</v>
+        <v>447189</v>
       </c>
       <c r="R107" t="n">
-        <v>6804483</v>
+        <v>6804301</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11185,10 +11185,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129893322</v>
+        <v>129893295</v>
       </c>
       <c r="B108" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11196,42 +11196,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447105</v>
+        <v>447085</v>
       </c>
       <c r="R108" t="n">
-        <v>6804584</v>
+        <v>6804671</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11290,10 +11282,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893295</v>
+        <v>129893352</v>
       </c>
       <c r="B109" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11301,21 +11293,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11325,10 +11317,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447085</v>
+        <v>447146</v>
       </c>
       <c r="R109" t="n">
-        <v>6804671</v>
+        <v>6804415</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11387,10 +11379,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893358</v>
+        <v>129893296</v>
       </c>
       <c r="B110" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11398,21 +11390,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11422,10 +11414,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447319</v>
+        <v>447079</v>
       </c>
       <c r="R110" t="n">
-        <v>6804349</v>
+        <v>6804660</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11484,7 +11476,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893352</v>
+        <v>129893358</v>
       </c>
       <c r="B111" t="n">
         <v>78841</v>
@@ -11519,10 +11511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447146</v>
+        <v>447319</v>
       </c>
       <c r="R111" t="n">
-        <v>6804415</v>
+        <v>6804349</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11581,10 +11573,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893296</v>
+        <v>129893322</v>
       </c>
       <c r="B112" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11592,34 +11584,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447079</v>
+        <v>447105</v>
       </c>
       <c r="R112" t="n">
-        <v>6804660</v>
+        <v>6804584</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11780,10 +11780,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893314</v>
+        <v>129893300</v>
       </c>
       <c r="B114" t="n">
-        <v>57737</v>
+        <v>79703</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11791,42 +11791,34 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447227</v>
+        <v>447121</v>
       </c>
       <c r="R114" t="n">
-        <v>6804586</v>
+        <v>6804435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11885,7 +11877,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893300</v>
+        <v>129893308</v>
       </c>
       <c r="B115" t="n">
         <v>79703</v>
@@ -11920,10 +11912,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447121</v>
+        <v>447248</v>
       </c>
       <c r="R115" t="n">
-        <v>6804435</v>
+        <v>6804484</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11982,7 +11974,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893308</v>
+        <v>129893297</v>
       </c>
       <c r="B116" t="n">
         <v>79703</v>
@@ -12017,10 +12009,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447248</v>
+        <v>447104</v>
       </c>
       <c r="R116" t="n">
-        <v>6804484</v>
+        <v>6804519</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12079,10 +12071,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893297</v>
+        <v>129893314</v>
       </c>
       <c r="B117" t="n">
-        <v>79703</v>
+        <v>57737</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12090,34 +12082,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447104</v>
+        <v>447227</v>
       </c>
       <c r="R117" t="n">
-        <v>6804519</v>
+        <v>6804586</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129893302</v>
+        <v>129893325</v>
       </c>
       <c r="B118" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12187,34 +12187,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447140</v>
+        <v>447201</v>
       </c>
       <c r="R118" t="n">
-        <v>6804436</v>
+        <v>6804314</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12370,10 +12378,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893325</v>
+        <v>129893302</v>
       </c>
       <c r="B120" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12381,42 +12389,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447201</v>
+        <v>447140</v>
       </c>
       <c r="R120" t="n">
-        <v>6804314</v>
+        <v>6804436</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12577,10 +12577,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893408</v>
+        <v>129893333</v>
       </c>
       <c r="B122" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12588,21 +12588,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12612,10 +12612,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447247</v>
+        <v>447284</v>
       </c>
       <c r="R122" t="n">
-        <v>6804486</v>
+        <v>6804412</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12970,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893333</v>
+        <v>129893408</v>
       </c>
       <c r="B126" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447284</v>
+        <v>447247</v>
       </c>
       <c r="R126" t="n">
-        <v>6804412</v>
+        <v>6804486</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13067,10 +13067,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129893349</v>
+        <v>129893298</v>
       </c>
       <c r="B127" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13078,21 +13078,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447138</v>
+        <v>447137</v>
       </c>
       <c r="R127" t="n">
         <v>6804511</v>
@@ -13164,10 +13164,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129893298</v>
+        <v>129893349</v>
       </c>
       <c r="B128" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,21 +13175,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447137</v>
+        <v>447138</v>
       </c>
       <c r="R128" t="n">
         <v>6804511</v>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893913</v>
+        <v>129894044</v>
       </c>
       <c r="B2" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447127</v>
+        <v>446959</v>
       </c>
       <c r="R2" t="n">
-        <v>6804438</v>
+        <v>6804780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893939</v>
+        <v>129893913</v>
       </c>
       <c r="B4" t="n">
-        <v>57734</v>
+        <v>79703</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,42 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447133</v>
+        <v>447127</v>
       </c>
       <c r="R4" t="n">
-        <v>6804362</v>
+        <v>6804438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129894044</v>
+        <v>129893939</v>
       </c>
       <c r="B5" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>446959</v>
+        <v>447133</v>
       </c>
       <c r="R5" t="n">
-        <v>6804780</v>
+        <v>6804362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129893953</v>
+        <v>129894023</v>
       </c>
       <c r="B13" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447186</v>
+        <v>447120</v>
       </c>
       <c r="R13" t="n">
-        <v>6804347</v>
+        <v>6804670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,6 +1840,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1964,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894023</v>
+        <v>129893953</v>
       </c>
       <c r="B15" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1999,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447120</v>
+        <v>447186</v>
       </c>
       <c r="R15" t="n">
-        <v>6804670</v>
+        <v>6804347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2035,11 +2040,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2163,53 +2163,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893923</v>
+        <v>129893973</v>
       </c>
       <c r="B17" t="n">
-        <v>56927</v>
+        <v>78841</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447079</v>
+        <v>447018</v>
       </c>
       <c r="R17" t="n">
-        <v>6804592</v>
+        <v>6804657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,10 +2260,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893973</v>
+        <v>129894043</v>
       </c>
       <c r="B18" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2279,21 +2271,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2303,10 +2295,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447018</v>
+        <v>447247</v>
       </c>
       <c r="R18" t="n">
-        <v>6804657</v>
+        <v>6804534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,45 +2357,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129894043</v>
+        <v>129893923</v>
       </c>
       <c r="B19" t="n">
-        <v>79084</v>
+        <v>56927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447247</v>
+        <v>447079</v>
       </c>
       <c r="R19" t="n">
-        <v>6804534</v>
+        <v>6804592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894039</v>
+        <v>129894042</v>
       </c>
       <c r="B20" t="n">
         <v>79084</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447226</v>
+        <v>447262</v>
       </c>
       <c r="R20" t="n">
-        <v>6804354</v>
+        <v>6804466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894042</v>
+        <v>129894039</v>
       </c>
       <c r="B21" t="n">
         <v>79084</v>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447262</v>
+        <v>447226</v>
       </c>
       <c r="R21" t="n">
-        <v>6804466</v>
+        <v>6804354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129894040</v>
+        <v>129893956</v>
       </c>
       <c r="B22" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,21 +2667,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447244</v>
+        <v>447248</v>
       </c>
       <c r="R22" t="n">
-        <v>6804361</v>
+        <v>6804447</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,53 +2850,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893945</v>
+        <v>129894040</v>
       </c>
       <c r="B24" t="n">
-        <v>56930</v>
+        <v>79084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447140</v>
+        <v>447244</v>
       </c>
       <c r="R24" t="n">
-        <v>6804358</v>
+        <v>6804361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,45 +2947,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893956</v>
+        <v>129893945</v>
       </c>
       <c r="B25" t="n">
-        <v>78842</v>
+        <v>56930</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447248</v>
+        <v>447140</v>
       </c>
       <c r="R25" t="n">
-        <v>6804447</v>
+        <v>6804358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,45 +3052,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B26" t="n">
-        <v>78842</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R26" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,6 +3140,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3149,54 +3159,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>78842</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R27" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,7 +3238,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894047</v>
+        <v>129893919</v>
       </c>
       <c r="B28" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447264</v>
+        <v>447260</v>
       </c>
       <c r="R28" t="n">
-        <v>6804394</v>
+        <v>6804349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,11 +3327,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3358,10 +3353,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894029</v>
+        <v>129893935</v>
       </c>
       <c r="B29" t="n">
-        <v>79084</v>
+        <v>57734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3369,34 +3364,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447078</v>
+        <v>447017</v>
       </c>
       <c r="R29" t="n">
-        <v>6804574</v>
+        <v>6804662</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3429,11 +3432,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3460,10 +3458,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893935</v>
+        <v>129894047</v>
       </c>
       <c r="B30" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3471,42 +3469,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447017</v>
+        <v>447264</v>
       </c>
       <c r="R30" t="n">
-        <v>6804662</v>
+        <v>6804394</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3539,6 +3529,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3662,10 +3657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893919</v>
+        <v>129894029</v>
       </c>
       <c r="B32" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3673,21 +3668,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3697,10 +3692,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447260</v>
+        <v>447078</v>
       </c>
       <c r="R32" t="n">
-        <v>6804349</v>
+        <v>6804574</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3733,6 +3728,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893955</v>
+        <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447237</v>
+        <v>447019</v>
       </c>
       <c r="R33" t="n">
-        <v>6804433</v>
+        <v>6804831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,6 +3830,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3856,7 +3861,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894026</v>
+        <v>129894028</v>
       </c>
       <c r="B34" t="n">
         <v>79084</v>
@@ -3891,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447019</v>
+        <v>447038</v>
       </c>
       <c r="R34" t="n">
-        <v>6804831</v>
+        <v>6804585</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3927,11 +3932,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3958,7 +3958,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894028</v>
+        <v>129894036</v>
       </c>
       <c r="B35" t="n">
         <v>79084</v>
@@ -3993,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447038</v>
+        <v>447177</v>
       </c>
       <c r="R35" t="n">
-        <v>6804585</v>
+        <v>6804353</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894036</v>
+        <v>129894046</v>
       </c>
       <c r="B36" t="n">
         <v>79084</v>
@@ -4084,16 +4084,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447177</v>
+        <v>447137</v>
       </c>
       <c r="R36" t="n">
-        <v>6804353</v>
+        <v>6804362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,12 +4131,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4152,7 +4161,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894046</v>
+        <v>129894034</v>
       </c>
       <c r="B37" t="n">
         <v>79084</v>
@@ -4181,19 +4190,16 @@
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447137</v>
+        <v>447146</v>
       </c>
       <c r="R37" t="n">
-        <v>6804362</v>
+        <v>6804328</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4228,18 +4234,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894034</v>
+        <v>129893920</v>
       </c>
       <c r="B38" t="n">
-        <v>79084</v>
+        <v>79674</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447146</v>
+        <v>447249</v>
       </c>
       <c r="R38" t="n">
-        <v>6804328</v>
+        <v>6804413</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893920</v>
+        <v>129893955</v>
       </c>
       <c r="B39" t="n">
-        <v>79674</v>
+        <v>78842</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447249</v>
+        <v>447237</v>
       </c>
       <c r="R39" t="n">
-        <v>6804413</v>
+        <v>6804433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894027</v>
+        <v>129893983</v>
       </c>
       <c r="B41" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446979</v>
+        <v>447195</v>
       </c>
       <c r="R41" t="n">
-        <v>6804787</v>
+        <v>6804348</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893983</v>
+        <v>129894027</v>
       </c>
       <c r="B42" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447195</v>
+        <v>446979</v>
       </c>
       <c r="R42" t="n">
-        <v>6804348</v>
+        <v>6804787</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893980</v>
+        <v>129893918</v>
       </c>
       <c r="B45" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,21 +4948,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447136</v>
+        <v>447021</v>
       </c>
       <c r="R45" t="n">
-        <v>6804407</v>
+        <v>6804646</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893969</v>
+        <v>129893933</v>
       </c>
       <c r="B46" t="n">
-        <v>78841</v>
+        <v>57734</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5045,34 +5045,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447006</v>
+        <v>447075</v>
       </c>
       <c r="R46" t="n">
-        <v>6804728</v>
+        <v>6804732</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,7 +5139,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893933</v>
+        <v>129893937</v>
       </c>
       <c r="B47" t="n">
         <v>57734</v>
@@ -5174,10 +5182,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447075</v>
+        <v>447059</v>
       </c>
       <c r="R47" t="n">
-        <v>6804732</v>
+        <v>6804587</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5236,7 +5244,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893937</v>
+        <v>129893936</v>
       </c>
       <c r="B48" t="n">
         <v>57734</v>
@@ -5279,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447059</v>
+        <v>447012</v>
       </c>
       <c r="R48" t="n">
-        <v>6804587</v>
+        <v>6804645</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893936</v>
+        <v>129893980</v>
       </c>
       <c r="B49" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5352,42 +5360,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447012</v>
+        <v>447136</v>
       </c>
       <c r="R49" t="n">
-        <v>6804645</v>
+        <v>6804407</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893918</v>
+        <v>129894035</v>
       </c>
       <c r="B51" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447021</v>
+        <v>447155</v>
       </c>
       <c r="R51" t="n">
-        <v>6804646</v>
+        <v>6804339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894035</v>
+        <v>129893969</v>
       </c>
       <c r="B52" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447155</v>
+        <v>447006</v>
       </c>
       <c r="R52" t="n">
-        <v>6804339</v>
+        <v>6804728</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5834,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129893932</v>
+        <v>129893924</v>
       </c>
       <c r="B54" t="n">
-        <v>57734</v>
+        <v>56927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,7 +5867,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447239</v>
+        <v>446997</v>
       </c>
       <c r="R54" t="n">
-        <v>6804569</v>
+        <v>6804780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,6 +5913,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5939,7 +5944,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893938</v>
+        <v>129893932</v>
       </c>
       <c r="B55" t="n">
         <v>57734</v>
@@ -5972,7 +5977,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447064</v>
+        <v>447239</v>
       </c>
       <c r="R55" t="n">
-        <v>6804548</v>
+        <v>6804569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6044,32 +6049,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893924</v>
+        <v>129893938</v>
       </c>
       <c r="B56" t="n">
-        <v>56927</v>
+        <v>57734</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6077,7 +6082,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6087,10 +6092,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446997</v>
+        <v>447064</v>
       </c>
       <c r="R56" t="n">
-        <v>6804780</v>
+        <v>6804548</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6123,11 +6128,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129893950</v>
+        <v>129893934</v>
       </c>
       <c r="B58" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,34 +6267,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447015</v>
+        <v>447006</v>
       </c>
       <c r="R58" t="n">
-        <v>6804655</v>
+        <v>6804684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,10 +6361,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893968</v>
+        <v>129893950</v>
       </c>
       <c r="B59" t="n">
-        <v>78841</v>
+        <v>78842</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6364,21 +6372,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6388,10 +6396,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446972</v>
+        <v>447015</v>
       </c>
       <c r="R59" t="n">
-        <v>6804770</v>
+        <v>6804655</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,10 +6458,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893934</v>
+        <v>129894025</v>
       </c>
       <c r="B60" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6461,42 +6469,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447006</v>
+        <v>447101</v>
       </c>
       <c r="R60" t="n">
-        <v>6804684</v>
+        <v>6804700</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129894025</v>
+        <v>129893968</v>
       </c>
       <c r="B61" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447101</v>
+        <v>446972</v>
       </c>
       <c r="R61" t="n">
-        <v>6804700</v>
+        <v>6804770</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129893347</v>
+        <v>129893324</v>
       </c>
       <c r="B69" t="n">
-        <v>78841</v>
+        <v>57734</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7350,34 +7350,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447114</v>
+        <v>447118</v>
       </c>
       <c r="R69" t="n">
-        <v>6804581</v>
+        <v>6804529</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,10 +7444,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893324</v>
+        <v>129893347</v>
       </c>
       <c r="B70" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7447,42 +7455,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447118</v>
+        <v>447114</v>
       </c>
       <c r="R70" t="n">
-        <v>6804529</v>
+        <v>6804581</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8238,10 +8238,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893334</v>
+        <v>129893306</v>
       </c>
       <c r="B78" t="n">
-        <v>78842</v>
+        <v>79703</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8249,21 +8249,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447287</v>
+        <v>447282</v>
       </c>
       <c r="R78" t="n">
-        <v>6804433</v>
+        <v>6804440</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8335,32 +8335,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893306</v>
+        <v>129893368</v>
       </c>
       <c r="B79" t="n">
-        <v>79703</v>
+        <v>90984</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8370,10 +8370,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447282</v>
+        <v>447279</v>
       </c>
       <c r="R79" t="n">
-        <v>6804440</v>
+        <v>6804380</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8414,6 +8414,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8432,32 +8433,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893368</v>
+        <v>129893353</v>
       </c>
       <c r="B80" t="n">
-        <v>90984</v>
+        <v>78841</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5685</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8467,10 +8468,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447279</v>
+        <v>447206</v>
       </c>
       <c r="R80" t="n">
-        <v>6804380</v>
+        <v>6804417</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8511,7 +8512,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8530,10 +8530,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893353</v>
+        <v>129893395</v>
       </c>
       <c r="B81" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447206</v>
+        <v>447137</v>
       </c>
       <c r="R81" t="n">
-        <v>6804417</v>
+        <v>6804440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8601,6 +8601,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8627,10 +8632,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893395</v>
+        <v>129893334</v>
       </c>
       <c r="B82" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8638,21 +8643,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8662,10 +8667,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447137</v>
+        <v>447287</v>
       </c>
       <c r="R82" t="n">
-        <v>6804440</v>
+        <v>6804433</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8698,11 +8703,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8729,10 +8729,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893303</v>
+        <v>129893348</v>
       </c>
       <c r="B83" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447143</v>
+        <v>447138</v>
       </c>
       <c r="R83" t="n">
-        <v>6804414</v>
+        <v>6804553</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8826,7 +8826,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893305</v>
+        <v>129893303</v>
       </c>
       <c r="B84" t="n">
         <v>79703</v>
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447170</v>
+        <v>447143</v>
       </c>
       <c r="R84" t="n">
-        <v>6804401</v>
+        <v>6804414</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8923,10 +8923,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893397</v>
+        <v>129893305</v>
       </c>
       <c r="B85" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8934,21 +8934,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8958,10 +8958,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447191</v>
+        <v>447170</v>
       </c>
       <c r="R85" t="n">
-        <v>6804284</v>
+        <v>6804401</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8994,11 +8994,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9025,10 +9020,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893348</v>
+        <v>129893397</v>
       </c>
       <c r="B86" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9036,21 +9031,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9060,10 +9055,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447138</v>
+        <v>447191</v>
       </c>
       <c r="R86" t="n">
-        <v>6804553</v>
+        <v>6804284</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9096,6 +9091,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9321,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893360</v>
+        <v>129893405</v>
       </c>
       <c r="B89" t="n">
-        <v>78841</v>
+        <v>79084</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9332,21 +9332,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447286</v>
+        <v>447280</v>
       </c>
       <c r="R89" t="n">
-        <v>6804433</v>
+        <v>6804429</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893405</v>
+        <v>129893360</v>
       </c>
       <c r="B90" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9429,21 +9429,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447280</v>
+        <v>447286</v>
       </c>
       <c r="R90" t="n">
-        <v>6804429</v>
+        <v>6804433</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893309</v>
+        <v>129893351</v>
       </c>
       <c r="B92" t="n">
-        <v>79674</v>
+        <v>78841</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9623,21 +9623,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9647,10 +9647,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447247</v>
+        <v>447129</v>
       </c>
       <c r="R92" t="n">
-        <v>6804552</v>
+        <v>6804505</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9709,45 +9709,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893351</v>
+        <v>129893316</v>
       </c>
       <c r="B93" t="n">
-        <v>78841</v>
+        <v>56927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447129</v>
+        <v>447102</v>
       </c>
       <c r="R93" t="n">
-        <v>6804505</v>
+        <v>6804551</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9806,53 +9814,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129893316</v>
+        <v>129893309</v>
       </c>
       <c r="B94" t="n">
-        <v>56927</v>
+        <v>79674</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447102</v>
+        <v>447247</v>
       </c>
       <c r="R94" t="n">
-        <v>6804551</v>
+        <v>6804552</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893407</v>
+        <v>129893332</v>
       </c>
       <c r="B95" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,21 +9922,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447258</v>
+        <v>447086</v>
       </c>
       <c r="R95" t="n">
-        <v>6804469</v>
+        <v>6804674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10008,10 +10008,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129893332</v>
+        <v>129893323</v>
       </c>
       <c r="B96" t="n">
-        <v>78842</v>
+        <v>57734</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10019,34 +10019,42 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447086</v>
+        <v>447139</v>
       </c>
       <c r="R96" t="n">
-        <v>6804674</v>
+        <v>6804556</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10105,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129893323</v>
+        <v>129893407</v>
       </c>
       <c r="B97" t="n">
-        <v>57734</v>
+        <v>79084</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10116,42 +10124,34 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="K97" t="inlineStr"/>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447139</v>
+        <v>447258</v>
       </c>
       <c r="R97" t="n">
-        <v>6804556</v>
+        <v>6804469</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893350</v>
+        <v>129893310</v>
       </c>
       <c r="B98" t="n">
-        <v>78841</v>
+        <v>79674</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447120</v>
+        <v>447280</v>
       </c>
       <c r="R98" t="n">
-        <v>6804506</v>
+        <v>6804428</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893396</v>
+        <v>129893350</v>
       </c>
       <c r="B100" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447170</v>
+        <v>447120</v>
       </c>
       <c r="R100" t="n">
-        <v>6804344</v>
+        <v>6804506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,11 +10475,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10506,10 +10501,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893310</v>
+        <v>129893396</v>
       </c>
       <c r="B101" t="n">
-        <v>79674</v>
+        <v>79084</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10512,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10536,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447280</v>
+        <v>447170</v>
       </c>
       <c r="R101" t="n">
-        <v>6804428</v>
+        <v>6804344</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10577,6 +10572,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10603,10 +10603,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129893344</v>
+        <v>129893301</v>
       </c>
       <c r="B102" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10614,21 +10614,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10638,10 +10638,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447173</v>
+        <v>447134</v>
       </c>
       <c r="R102" t="n">
-        <v>6804600</v>
+        <v>6804438</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10700,7 +10700,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129893357</v>
+        <v>129893344</v>
       </c>
       <c r="B103" t="n">
         <v>78841</v>
@@ -10735,10 +10735,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447159</v>
+        <v>447173</v>
       </c>
       <c r="R103" t="n">
-        <v>6804343</v>
+        <v>6804600</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10797,10 +10797,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129893301</v>
+        <v>129893357</v>
       </c>
       <c r="B104" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10808,21 +10808,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10832,10 +10832,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447134</v>
+        <v>447159</v>
       </c>
       <c r="R104" t="n">
-        <v>6804438</v>
+        <v>6804343</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129893346</v>
+        <v>129893299</v>
       </c>
       <c r="B105" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447088</v>
+        <v>447141</v>
       </c>
       <c r="R105" t="n">
-        <v>6804609</v>
+        <v>6804483</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893299</v>
+        <v>129893398</v>
       </c>
       <c r="B106" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447141</v>
+        <v>447189</v>
       </c>
       <c r="R106" t="n">
-        <v>6804483</v>
+        <v>6804301</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893398</v>
+        <v>129893346</v>
       </c>
       <c r="B107" t="n">
-        <v>79084</v>
+        <v>78841</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447189</v>
+        <v>447088</v>
       </c>
       <c r="R107" t="n">
-        <v>6804301</v>
+        <v>6804609</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11282,10 +11282,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893352</v>
+        <v>129893296</v>
       </c>
       <c r="B109" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11293,21 +11293,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447146</v>
+        <v>447079</v>
       </c>
       <c r="R109" t="n">
-        <v>6804415</v>
+        <v>6804660</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11379,10 +11379,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893296</v>
+        <v>129893322</v>
       </c>
       <c r="B110" t="n">
-        <v>79703</v>
+        <v>57734</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11390,34 +11390,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447079</v>
+        <v>447105</v>
       </c>
       <c r="R110" t="n">
-        <v>6804660</v>
+        <v>6804584</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11573,10 +11581,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893322</v>
+        <v>129893352</v>
       </c>
       <c r="B112" t="n">
-        <v>57734</v>
+        <v>78841</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11584,42 +11592,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447105</v>
+        <v>447146</v>
       </c>
       <c r="R112" t="n">
-        <v>6804584</v>
+        <v>6804415</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893394</v>
+        <v>129893300</v>
       </c>
       <c r="B113" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,21 +11689,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11713,10 +11713,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447128</v>
+        <v>447121</v>
       </c>
       <c r="R113" t="n">
-        <v>6804516</v>
+        <v>6804435</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11749,11 +11749,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -11780,7 +11775,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893300</v>
+        <v>129893308</v>
       </c>
       <c r="B114" t="n">
         <v>79703</v>
@@ -11815,10 +11810,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447121</v>
+        <v>447248</v>
       </c>
       <c r="R114" t="n">
-        <v>6804435</v>
+        <v>6804484</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11877,7 +11872,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893308</v>
+        <v>129893297</v>
       </c>
       <c r="B115" t="n">
         <v>79703</v>
@@ -11912,10 +11907,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447248</v>
+        <v>447104</v>
       </c>
       <c r="R115" t="n">
-        <v>6804484</v>
+        <v>6804519</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11974,10 +11969,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893297</v>
+        <v>129893394</v>
       </c>
       <c r="B116" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11985,21 +11980,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12009,10 +12004,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447104</v>
+        <v>447128</v>
       </c>
       <c r="R116" t="n">
-        <v>6804519</v>
+        <v>6804516</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12045,6 +12040,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12281,10 +12281,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129893354</v>
+        <v>129893302</v>
       </c>
       <c r="B119" t="n">
-        <v>78841</v>
+        <v>79703</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12292,21 +12292,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12316,10 +12316,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447193</v>
+        <v>447140</v>
       </c>
       <c r="R119" t="n">
-        <v>6804389</v>
+        <v>6804436</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12378,10 +12378,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893302</v>
+        <v>129893354</v>
       </c>
       <c r="B120" t="n">
-        <v>79703</v>
+        <v>78841</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12389,21 +12389,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12413,10 +12413,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447140</v>
+        <v>447193</v>
       </c>
       <c r="R120" t="n">
-        <v>6804436</v>
+        <v>6804389</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129893401</v>
+        <v>129893304</v>
       </c>
       <c r="B121" t="n">
-        <v>79084</v>
+        <v>79703</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,21 +12486,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447291</v>
+        <v>447208</v>
       </c>
       <c r="R121" t="n">
-        <v>6804354</v>
+        <v>6804423</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12546,11 +12546,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12577,10 +12572,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893333</v>
+        <v>129893401</v>
       </c>
       <c r="B122" t="n">
-        <v>78842</v>
+        <v>79084</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12588,21 +12583,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12612,10 +12607,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447284</v>
+        <v>447291</v>
       </c>
       <c r="R122" t="n">
-        <v>6804412</v>
+        <v>6804354</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12648,6 +12643,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12674,7 +12674,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893406</v>
+        <v>129893408</v>
       </c>
       <c r="B123" t="n">
         <v>79084</v>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447282</v>
+        <v>447247</v>
       </c>
       <c r="R123" t="n">
-        <v>6804440</v>
+        <v>6804486</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12745,11 +12745,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12776,10 +12771,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129893304</v>
+        <v>129893406</v>
       </c>
       <c r="B124" t="n">
-        <v>79703</v>
+        <v>79084</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12787,21 +12782,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12811,10 +12806,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447208</v>
+        <v>447282</v>
       </c>
       <c r="R124" t="n">
-        <v>6804423</v>
+        <v>6804440</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12847,6 +12842,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12970,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893408</v>
+        <v>129893333</v>
       </c>
       <c r="B126" t="n">
-        <v>79084</v>
+        <v>78842</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447247</v>
+        <v>447284</v>
       </c>
       <c r="R126" t="n">
-        <v>6804486</v>
+        <v>6804412</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894044</v>
+        <v>129893939</v>
       </c>
       <c r="B2" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446959</v>
+        <v>447133</v>
       </c>
       <c r="R2" t="n">
-        <v>6804780</v>
+        <v>6804362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129893971</v>
+        <v>129894044</v>
       </c>
       <c r="B3" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447009</v>
+        <v>446959</v>
       </c>
       <c r="R3" t="n">
-        <v>6804689</v>
+        <v>6804780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +880,7 @@
         <v>129893913</v>
       </c>
       <c r="B4" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893939</v>
+        <v>129893971</v>
       </c>
       <c r="B5" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447133</v>
+        <v>447009</v>
       </c>
       <c r="R5" t="n">
-        <v>6804362</v>
+        <v>6804689</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
         <v>129893972</v>
       </c>
       <c r="B6" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129894024</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893970</v>
+        <v>129893974</v>
       </c>
       <c r="B8" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447006</v>
+        <v>447014</v>
       </c>
       <c r="R8" t="n">
-        <v>6804685</v>
+        <v>6804644</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893974</v>
+        <v>129893970</v>
       </c>
       <c r="B9" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447014</v>
+        <v>447006</v>
       </c>
       <c r="R9" t="n">
-        <v>6804644</v>
+        <v>6804685</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1466,7 +1466,7 @@
         <v>129893963</v>
       </c>
       <c r="B10" t="n">
-        <v>8450</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         <v>129894030</v>
       </c>
       <c r="B11" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1675,7 +1675,7 @@
         <v>129893949</v>
       </c>
       <c r="B12" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>129894023</v>
       </c>
       <c r="B13" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1871,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894050</v>
+        <v>129893953</v>
       </c>
       <c r="B14" t="n">
-        <v>78092</v>
+        <v>78845</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447251</v>
+        <v>447186</v>
       </c>
       <c r="R14" t="n">
-        <v>6804480</v>
+        <v>6804347</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,7 +1950,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B15" t="n">
-        <v>78842</v>
+        <v>78095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R15" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>129894033</v>
       </c>
       <c r="B16" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2166,7 +2166,7 @@
         <v>129893973</v>
       </c>
       <c r="B17" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>129894043</v>
       </c>
       <c r="B18" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
         <v>129893923</v>
       </c>
       <c r="B19" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>129894042</v>
       </c>
       <c r="B20" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129894039</v>
       </c>
       <c r="B21" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893956</v>
+        <v>129893976</v>
       </c>
       <c r="B22" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2667,21 +2667,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447248</v>
+        <v>447071</v>
       </c>
       <c r="R22" t="n">
-        <v>6804447</v>
+        <v>6804595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,10 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893976</v>
+        <v>129894040</v>
       </c>
       <c r="B23" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,21 +2764,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2788,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447071</v>
+        <v>447244</v>
       </c>
       <c r="R23" t="n">
-        <v>6804595</v>
+        <v>6804361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,45 +2850,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894040</v>
+        <v>129893945</v>
       </c>
       <c r="B24" t="n">
-        <v>79084</v>
+        <v>56933</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447244</v>
+        <v>447140</v>
       </c>
       <c r="R24" t="n">
-        <v>6804361</v>
+        <v>6804358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2947,53 +2955,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893945</v>
+        <v>129893956</v>
       </c>
       <c r="B25" t="n">
-        <v>56930</v>
+        <v>78845</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447140</v>
+        <v>447248</v>
       </c>
       <c r="R25" t="n">
-        <v>6804358</v>
+        <v>6804447</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,54 +3052,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>78845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R26" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,7 +3131,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3149,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B27" t="n">
-        <v>78842</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R27" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,6 +3237,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893919</v>
+        <v>129894047</v>
       </c>
       <c r="B28" t="n">
-        <v>79674</v>
+        <v>79087</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447260</v>
+        <v>447264</v>
       </c>
       <c r="R28" t="n">
-        <v>6804349</v>
+        <v>6804394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,6 +3327,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3353,10 +3358,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893935</v>
+        <v>129893979</v>
       </c>
       <c r="B29" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,42 +3369,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447017</v>
+        <v>447104</v>
       </c>
       <c r="R29" t="n">
-        <v>6804662</v>
+        <v>6804432</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3458,10 +3455,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894047</v>
+        <v>129894029</v>
       </c>
       <c r="B30" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3493,10 +3490,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447264</v>
+        <v>447078</v>
       </c>
       <c r="R30" t="n">
-        <v>6804394</v>
+        <v>6804574</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3533,7 +3530,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3560,10 +3557,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893979</v>
+        <v>129893935</v>
       </c>
       <c r="B31" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3571,34 +3568,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447104</v>
+        <v>447017</v>
       </c>
       <c r="R31" t="n">
-        <v>6804432</v>
+        <v>6804662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3657,10 +3662,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894029</v>
+        <v>129893919</v>
       </c>
       <c r="B32" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3668,21 +3673,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3692,10 +3697,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447078</v>
+        <v>447260</v>
       </c>
       <c r="R32" t="n">
-        <v>6804574</v>
+        <v>6804349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,11 +3733,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,7 +3762,7 @@
         <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>129894028</v>
       </c>
       <c r="B34" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129894036</v>
       </c>
       <c r="B35" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>129894046</v>
       </c>
       <c r="B36" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>129894034</v>
       </c>
       <c r="B37" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>129893920</v>
       </c>
       <c r="B38" t="n">
-        <v>79674</v>
+        <v>79677</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>129893955</v>
       </c>
       <c r="B39" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>129893977</v>
       </c>
       <c r="B40" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>129893983</v>
       </c>
       <c r="B41" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>129894027</v>
       </c>
       <c r="B42" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>129893975</v>
       </c>
       <c r="B43" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>129893948</v>
       </c>
       <c r="B44" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893918</v>
+        <v>129893980</v>
       </c>
       <c r="B45" t="n">
-        <v>79674</v>
+        <v>78844</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,21 +4948,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447021</v>
+        <v>447136</v>
       </c>
       <c r="R45" t="n">
-        <v>6804646</v>
+        <v>6804407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893933</v>
+        <v>129894041</v>
       </c>
       <c r="B46" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5045,42 +5045,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447075</v>
+        <v>447242</v>
       </c>
       <c r="R46" t="n">
-        <v>6804732</v>
+        <v>6804443</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5139,10 +5131,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893937</v>
+        <v>129894035</v>
       </c>
       <c r="B47" t="n">
-        <v>57734</v>
+        <v>79087</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5150,42 +5142,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447059</v>
+        <v>447155</v>
       </c>
       <c r="R47" t="n">
-        <v>6804587</v>
+        <v>6804339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5244,10 +5228,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893936</v>
+        <v>129893969</v>
       </c>
       <c r="B48" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5255,42 +5239,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447012</v>
+        <v>447006</v>
       </c>
       <c r="R48" t="n">
-        <v>6804645</v>
+        <v>6804728</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893980</v>
+        <v>129893933</v>
       </c>
       <c r="B49" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,34 +5336,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447136</v>
+        <v>447075</v>
       </c>
       <c r="R49" t="n">
-        <v>6804407</v>
+        <v>6804732</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5430,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129894041</v>
+        <v>129893937</v>
       </c>
       <c r="B50" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,34 +5441,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447242</v>
+        <v>447059</v>
       </c>
       <c r="R50" t="n">
-        <v>6804443</v>
+        <v>6804587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5535,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894035</v>
+        <v>129893936</v>
       </c>
       <c r="B51" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,34 +5546,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447155</v>
+        <v>447012</v>
       </c>
       <c r="R51" t="n">
-        <v>6804339</v>
+        <v>6804645</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893969</v>
+        <v>129893918</v>
       </c>
       <c r="B52" t="n">
-        <v>78841</v>
+        <v>79677</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447006</v>
+        <v>447021</v>
       </c>
       <c r="R52" t="n">
-        <v>6804728</v>
+        <v>6804646</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5740,7 +5740,7 @@
         <v>129893951</v>
       </c>
       <c r="B53" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>129893924</v>
       </c>
       <c r="B54" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
         <v>129893932</v>
       </c>
       <c r="B55" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>129893938</v>
       </c>
       <c r="B56" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         <v>129894045</v>
       </c>
       <c r="B57" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129893934</v>
+        <v>129893968</v>
       </c>
       <c r="B58" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,42 +6267,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447006</v>
+        <v>446972</v>
       </c>
       <c r="R58" t="n">
-        <v>6804684</v>
+        <v>6804770</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6361,10 +6353,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893950</v>
+        <v>129893967</v>
       </c>
       <c r="B59" t="n">
-        <v>78842</v>
+        <v>78844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6372,21 +6364,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6396,10 +6388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447015</v>
+        <v>447209</v>
       </c>
       <c r="R59" t="n">
-        <v>6804655</v>
+        <v>6804576</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6458,10 +6450,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129894025</v>
+        <v>129893934</v>
       </c>
       <c r="B60" t="n">
-        <v>79084</v>
+        <v>57737</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6469,34 +6461,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447101</v>
+        <v>447006</v>
       </c>
       <c r="R60" t="n">
-        <v>6804700</v>
+        <v>6804684</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6555,10 +6555,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893968</v>
+        <v>129893950</v>
       </c>
       <c r="B61" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6566,21 +6566,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>446972</v>
+        <v>447015</v>
       </c>
       <c r="R61" t="n">
-        <v>6804770</v>
+        <v>6804655</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129893967</v>
+        <v>129894025</v>
       </c>
       <c r="B62" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447209</v>
+        <v>447101</v>
       </c>
       <c r="R62" t="n">
-        <v>6804576</v>
+        <v>6804700</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893982</v>
+        <v>129893952</v>
       </c>
       <c r="B63" t="n">
-        <v>78841</v>
+        <v>78845</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447163</v>
+        <v>447138</v>
       </c>
       <c r="R63" t="n">
-        <v>6804342</v>
+        <v>6804405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129894038</v>
+        <v>129893914</v>
       </c>
       <c r="B64" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447196</v>
+        <v>447244</v>
       </c>
       <c r="R64" t="n">
-        <v>6804341</v>
+        <v>6804447</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893921</v>
+        <v>129893912</v>
       </c>
       <c r="B65" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6954,42 +6954,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447004</v>
+        <v>447082</v>
       </c>
       <c r="R65" t="n">
-        <v>6804712</v>
+        <v>6804551</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7048,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893914</v>
+        <v>129893982</v>
       </c>
       <c r="B66" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7059,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7083,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447244</v>
+        <v>447163</v>
       </c>
       <c r="R66" t="n">
-        <v>6804447</v>
+        <v>6804342</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7145,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893912</v>
+        <v>129894038</v>
       </c>
       <c r="B67" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7156,21 +7148,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7180,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447082</v>
+        <v>447196</v>
       </c>
       <c r="R67" t="n">
-        <v>6804551</v>
+        <v>6804341</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7242,10 +7234,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893952</v>
+        <v>129893921</v>
       </c>
       <c r="B68" t="n">
-        <v>78842</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7253,34 +7245,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447138</v>
+        <v>447004</v>
       </c>
       <c r="R68" t="n">
-        <v>6804405</v>
+        <v>6804712</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7342,7 +7342,7 @@
         <v>129893324</v>
       </c>
       <c r="B69" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7447,7 +7447,7 @@
         <v>129893347</v>
       </c>
       <c r="B70" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7544,7 +7544,7 @@
         <v>129893402</v>
       </c>
       <c r="B71" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129893404</v>
       </c>
       <c r="B72" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>129893403</v>
       </c>
       <c r="B73" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>129893400</v>
       </c>
       <c r="B74" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>129893393</v>
       </c>
       <c r="B75" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>129893356</v>
       </c>
       <c r="B76" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>129893315</v>
       </c>
       <c r="B77" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8238,32 +8238,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893306</v>
+        <v>129893368</v>
       </c>
       <c r="B78" t="n">
-        <v>79703</v>
+        <v>90987</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447282</v>
+        <v>447279</v>
       </c>
       <c r="R78" t="n">
-        <v>6804440</v>
+        <v>6804380</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8317,6 +8317,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8335,32 +8336,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893368</v>
+        <v>129893334</v>
       </c>
       <c r="B79" t="n">
-        <v>90984</v>
+        <v>78845</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8370,10 +8371,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447279</v>
+        <v>447287</v>
       </c>
       <c r="R79" t="n">
-        <v>6804380</v>
+        <v>6804433</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8414,7 +8415,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893353</v>
+        <v>129893306</v>
       </c>
       <c r="B80" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8444,21 +8444,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447206</v>
+        <v>447282</v>
       </c>
       <c r="R80" t="n">
-        <v>6804417</v>
+        <v>6804440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8530,10 +8530,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893395</v>
+        <v>129893353</v>
       </c>
       <c r="B81" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447137</v>
+        <v>447206</v>
       </c>
       <c r="R81" t="n">
-        <v>6804440</v>
+        <v>6804417</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8601,11 +8601,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8632,10 +8627,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893334</v>
+        <v>129893395</v>
       </c>
       <c r="B82" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8643,21 +8638,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8667,10 +8662,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447287</v>
+        <v>447137</v>
       </c>
       <c r="R82" t="n">
-        <v>6804433</v>
+        <v>6804440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8703,6 +8698,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8729,10 +8729,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893348</v>
+        <v>129893303</v>
       </c>
       <c r="B83" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447138</v>
+        <v>447143</v>
       </c>
       <c r="R83" t="n">
-        <v>6804553</v>
+        <v>6804414</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8826,10 +8826,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893303</v>
+        <v>129893397</v>
       </c>
       <c r="B84" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8837,21 +8837,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447143</v>
+        <v>447191</v>
       </c>
       <c r="R84" t="n">
-        <v>6804414</v>
+        <v>6804284</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8897,6 +8897,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8923,10 +8928,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893305</v>
+        <v>129893348</v>
       </c>
       <c r="B85" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8934,21 +8939,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8958,10 +8963,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447170</v>
+        <v>447138</v>
       </c>
       <c r="R85" t="n">
-        <v>6804401</v>
+        <v>6804553</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9020,10 +9025,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893397</v>
+        <v>129893305</v>
       </c>
       <c r="B86" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9031,21 +9036,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9055,10 +9060,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447191</v>
+        <v>447170</v>
       </c>
       <c r="R86" t="n">
-        <v>6804284</v>
+        <v>6804401</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9091,11 +9096,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9125,7 +9125,7 @@
         <v>129893392</v>
       </c>
       <c r="B87" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9224,10 +9224,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893307</v>
+        <v>129893405</v>
       </c>
       <c r="B88" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9235,21 +9235,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447271</v>
+        <v>447280</v>
       </c>
       <c r="R88" t="n">
-        <v>6804458</v>
+        <v>6804429</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9321,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893405</v>
+        <v>129893307</v>
       </c>
       <c r="B89" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9332,21 +9332,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447280</v>
+        <v>447271</v>
       </c>
       <c r="R89" t="n">
-        <v>6804429</v>
+        <v>6804458</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9421,7 +9421,7 @@
         <v>129893360</v>
       </c>
       <c r="B90" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>129893399</v>
       </c>
       <c r="B91" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>129893351</v>
       </c>
       <c r="B92" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,53 +9709,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893316</v>
+        <v>129893309</v>
       </c>
       <c r="B93" t="n">
-        <v>56927</v>
+        <v>79677</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447102</v>
+        <v>447247</v>
       </c>
       <c r="R93" t="n">
-        <v>6804551</v>
+        <v>6804552</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9814,45 +9806,53 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129893309</v>
+        <v>129893316</v>
       </c>
       <c r="B94" t="n">
-        <v>79674</v>
+        <v>56930</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447247</v>
+        <v>447102</v>
       </c>
       <c r="R94" t="n">
-        <v>6804552</v>
+        <v>6804551</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893332</v>
+        <v>129893407</v>
       </c>
       <c r="B95" t="n">
-        <v>78842</v>
+        <v>79087</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,21 +9922,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447086</v>
+        <v>447258</v>
       </c>
       <c r="R95" t="n">
-        <v>6804674</v>
+        <v>6804469</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10011,7 +10011,7 @@
         <v>129893323</v>
       </c>
       <c r="B96" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129893407</v>
+        <v>129893332</v>
       </c>
       <c r="B97" t="n">
-        <v>79084</v>
+        <v>78845</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,21 +10124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10148,10 +10148,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447258</v>
+        <v>447086</v>
       </c>
       <c r="R97" t="n">
-        <v>6804469</v>
+        <v>6804674</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893310</v>
+        <v>129893359</v>
       </c>
       <c r="B98" t="n">
-        <v>79674</v>
+        <v>78844</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447280</v>
+        <v>447276</v>
       </c>
       <c r="R98" t="n">
-        <v>6804428</v>
+        <v>6804418</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893359</v>
+        <v>129893350</v>
       </c>
       <c r="B99" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447276</v>
+        <v>447120</v>
       </c>
       <c r="R99" t="n">
-        <v>6804418</v>
+        <v>6804506</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893350</v>
+        <v>129893396</v>
       </c>
       <c r="B100" t="n">
-        <v>78841</v>
+        <v>79087</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447120</v>
+        <v>447170</v>
       </c>
       <c r="R100" t="n">
-        <v>6804506</v>
+        <v>6804344</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,6 +10475,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10501,10 +10506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893396</v>
+        <v>129893310</v>
       </c>
       <c r="B101" t="n">
-        <v>79084</v>
+        <v>79677</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10512,21 +10517,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10536,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447170</v>
+        <v>447280</v>
       </c>
       <c r="R101" t="n">
-        <v>6804344</v>
+        <v>6804428</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10572,11 +10577,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10603,10 +10603,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129893301</v>
+        <v>129893344</v>
       </c>
       <c r="B102" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10614,21 +10614,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10638,10 +10638,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447134</v>
+        <v>447173</v>
       </c>
       <c r="R102" t="n">
-        <v>6804438</v>
+        <v>6804600</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10700,10 +10700,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>129893344</v>
+        <v>129893357</v>
       </c>
       <c r="B103" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10735,10 +10735,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>447173</v>
+        <v>447159</v>
       </c>
       <c r="R103" t="n">
-        <v>6804600</v>
+        <v>6804343</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -10797,10 +10797,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129893357</v>
+        <v>129893301</v>
       </c>
       <c r="B104" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10808,21 +10808,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10832,10 +10832,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447159</v>
+        <v>447134</v>
       </c>
       <c r="R104" t="n">
-        <v>6804343</v>
+        <v>6804438</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129893299</v>
+        <v>129893398</v>
       </c>
       <c r="B105" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447141</v>
+        <v>447189</v>
       </c>
       <c r="R105" t="n">
-        <v>6804483</v>
+        <v>6804301</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893398</v>
+        <v>129893346</v>
       </c>
       <c r="B106" t="n">
-        <v>79084</v>
+        <v>78844</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447189</v>
+        <v>447088</v>
       </c>
       <c r="R106" t="n">
-        <v>6804301</v>
+        <v>6804609</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893346</v>
+        <v>129893299</v>
       </c>
       <c r="B107" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447088</v>
+        <v>447141</v>
       </c>
       <c r="R107" t="n">
-        <v>6804609</v>
+        <v>6804483</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11188,7 +11188,7 @@
         <v>129893295</v>
       </c>
       <c r="B108" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11282,10 +11282,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893296</v>
+        <v>129893358</v>
       </c>
       <c r="B109" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11293,21 +11293,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447079</v>
+        <v>447319</v>
       </c>
       <c r="R109" t="n">
-        <v>6804660</v>
+        <v>6804349</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11379,10 +11379,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893322</v>
+        <v>129893352</v>
       </c>
       <c r="B110" t="n">
-        <v>57734</v>
+        <v>78844</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11390,42 +11390,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447105</v>
+        <v>447146</v>
       </c>
       <c r="R110" t="n">
-        <v>6804584</v>
+        <v>6804415</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11484,10 +11476,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893358</v>
+        <v>129893296</v>
       </c>
       <c r="B111" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11495,21 +11487,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11519,10 +11511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447319</v>
+        <v>447079</v>
       </c>
       <c r="R111" t="n">
-        <v>6804349</v>
+        <v>6804660</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11581,10 +11573,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893352</v>
+        <v>129893322</v>
       </c>
       <c r="B112" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11592,34 +11584,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447146</v>
+        <v>447105</v>
       </c>
       <c r="R112" t="n">
-        <v>6804415</v>
+        <v>6804584</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11681,7 +11681,7 @@
         <v>129893300</v>
       </c>
       <c r="B113" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11775,10 +11775,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893308</v>
+        <v>129893394</v>
       </c>
       <c r="B114" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11786,21 +11786,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11810,10 +11810,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447248</v>
+        <v>447128</v>
       </c>
       <c r="R114" t="n">
-        <v>6804484</v>
+        <v>6804516</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11846,6 +11846,11 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11872,10 +11877,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893297</v>
+        <v>129893308</v>
       </c>
       <c r="B115" t="n">
-        <v>79703</v>
+        <v>79706</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11907,10 +11912,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447104</v>
+        <v>447248</v>
       </c>
       <c r="R115" t="n">
-        <v>6804519</v>
+        <v>6804484</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11969,10 +11974,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893394</v>
+        <v>129893314</v>
       </c>
       <c r="B116" t="n">
-        <v>79084</v>
+        <v>57740</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11980,34 +11985,42 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447128</v>
+        <v>447227</v>
       </c>
       <c r="R116" t="n">
-        <v>6804516</v>
+        <v>6804586</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12040,11 +12053,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12071,10 +12079,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893314</v>
+        <v>129893297</v>
       </c>
       <c r="B117" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12082,42 +12090,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447227</v>
+        <v>447104</v>
       </c>
       <c r="R117" t="n">
-        <v>6804586</v>
+        <v>6804519</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129893325</v>
+        <v>129893302</v>
       </c>
       <c r="B118" t="n">
-        <v>57734</v>
+        <v>79706</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12187,42 +12187,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447201</v>
+        <v>447140</v>
       </c>
       <c r="R118" t="n">
-        <v>6804314</v>
+        <v>6804436</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12281,10 +12273,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129893302</v>
+        <v>129893354</v>
       </c>
       <c r="B119" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12292,21 +12284,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12316,10 +12308,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447140</v>
+        <v>447193</v>
       </c>
       <c r="R119" t="n">
-        <v>6804436</v>
+        <v>6804389</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12378,10 +12370,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893354</v>
+        <v>129893325</v>
       </c>
       <c r="B120" t="n">
-        <v>78841</v>
+        <v>57737</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12389,34 +12381,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447193</v>
+        <v>447201</v>
       </c>
       <c r="R120" t="n">
-        <v>6804389</v>
+        <v>6804314</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129893304</v>
+        <v>129893401</v>
       </c>
       <c r="B121" t="n">
-        <v>79703</v>
+        <v>79087</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,21 +12486,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447208</v>
+        <v>447291</v>
       </c>
       <c r="R121" t="n">
-        <v>6804423</v>
+        <v>6804354</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12546,6 +12546,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12572,10 +12577,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893401</v>
+        <v>129893408</v>
       </c>
       <c r="B122" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12607,10 +12612,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447291</v>
+        <v>447247</v>
       </c>
       <c r="R122" t="n">
-        <v>6804354</v>
+        <v>6804486</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12643,11 +12648,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12674,10 +12674,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893408</v>
+        <v>129893304</v>
       </c>
       <c r="B123" t="n">
-        <v>79084</v>
+        <v>79706</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12685,21 +12685,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447247</v>
+        <v>447208</v>
       </c>
       <c r="R123" t="n">
-        <v>6804486</v>
+        <v>6804423</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12774,7 +12774,7 @@
         <v>129893406</v>
       </c>
       <c r="B124" t="n">
-        <v>79084</v>
+        <v>79087</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12876,7 +12876,7 @@
         <v>129893355</v>
       </c>
       <c r="B125" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12973,7 +12973,7 @@
         <v>129893333</v>
       </c>
       <c r="B126" t="n">
-        <v>78842</v>
+        <v>78845</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13067,10 +13067,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129893298</v>
+        <v>129893349</v>
       </c>
       <c r="B127" t="n">
-        <v>79703</v>
+        <v>78844</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13078,21 +13078,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447137</v>
+        <v>447138</v>
       </c>
       <c r="R127" t="n">
         <v>6804511</v>
@@ -13164,10 +13164,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129893349</v>
+        <v>129893298</v>
       </c>
       <c r="B128" t="n">
-        <v>78841</v>
+        <v>79706</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,21 +13175,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447138</v>
+        <v>447137</v>
       </c>
       <c r="R128" t="n">
         <v>6804511</v>
@@ -13264,7 +13264,7 @@
         <v>129893345</v>
       </c>
       <c r="B129" t="n">
-        <v>78841</v>
+        <v>78844</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -2656,45 +2656,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893976</v>
+        <v>129893945</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>56933</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447071</v>
+        <v>447140</v>
       </c>
       <c r="R22" t="n">
-        <v>6804595</v>
+        <v>6804358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,10 +2761,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894040</v>
+        <v>129893976</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,21 +2772,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2788,10 +2796,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447244</v>
+        <v>447071</v>
       </c>
       <c r="R23" t="n">
-        <v>6804361</v>
+        <v>6804595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,53 +2858,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893945</v>
+        <v>129894040</v>
       </c>
       <c r="B24" t="n">
-        <v>56933</v>
+        <v>79087</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447140</v>
+        <v>447244</v>
       </c>
       <c r="R24" t="n">
-        <v>6804358</v>
+        <v>6804361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129893968</v>
+        <v>129894025</v>
       </c>
       <c r="B58" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,21 +6267,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446972</v>
+        <v>447101</v>
       </c>
       <c r="R58" t="n">
-        <v>6804770</v>
+        <v>6804700</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893967</v>
+        <v>129893968</v>
       </c>
       <c r="B59" t="n">
         <v>78844</v>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447209</v>
+        <v>446972</v>
       </c>
       <c r="R59" t="n">
-        <v>6804576</v>
+        <v>6804770</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893934</v>
+        <v>129893967</v>
       </c>
       <c r="B60" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6461,42 +6461,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447006</v>
+        <v>447209</v>
       </c>
       <c r="R60" t="n">
-        <v>6804684</v>
+        <v>6804576</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6555,10 +6547,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893950</v>
+        <v>129893934</v>
       </c>
       <c r="B61" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6566,34 +6558,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447015</v>
+        <v>447006</v>
       </c>
       <c r="R61" t="n">
-        <v>6804655</v>
+        <v>6804684</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129894025</v>
+        <v>129893950</v>
       </c>
       <c r="B62" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447101</v>
+        <v>447015</v>
       </c>
       <c r="R62" t="n">
-        <v>6804700</v>
+        <v>6804655</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893359</v>
+        <v>129893310</v>
       </c>
       <c r="B98" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447276</v>
+        <v>447280</v>
       </c>
       <c r="R98" t="n">
-        <v>6804418</v>
+        <v>6804428</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,7 +10307,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893350</v>
+        <v>129893359</v>
       </c>
       <c r="B99" t="n">
         <v>78844</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447120</v>
+        <v>447276</v>
       </c>
       <c r="R99" t="n">
-        <v>6804506</v>
+        <v>6804418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893396</v>
+        <v>129893350</v>
       </c>
       <c r="B100" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447170</v>
+        <v>447120</v>
       </c>
       <c r="R100" t="n">
-        <v>6804344</v>
+        <v>6804506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,11 +10475,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10506,10 +10501,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893310</v>
+        <v>129893396</v>
       </c>
       <c r="B101" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10512,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10536,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447280</v>
+        <v>447170</v>
       </c>
       <c r="R101" t="n">
-        <v>6804428</v>
+        <v>6804344</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10577,6 +10572,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -1871,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B14" t="n">
-        <v>78845</v>
+        <v>78095</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,21 +1882,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R14" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1950,6 +1950,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894050</v>
+        <v>129893953</v>
       </c>
       <c r="B15" t="n">
-        <v>78095</v>
+        <v>78845</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447251</v>
+        <v>447186</v>
       </c>
       <c r="R15" t="n">
-        <v>6804480</v>
+        <v>6804347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,7 +2048,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2656,53 +2656,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893945</v>
+        <v>129893976</v>
       </c>
       <c r="B22" t="n">
-        <v>56933</v>
+        <v>78844</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447140</v>
+        <v>447071</v>
       </c>
       <c r="R22" t="n">
-        <v>6804358</v>
+        <v>6804595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,10 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129893976</v>
+        <v>129894040</v>
       </c>
       <c r="B23" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,21 +2764,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2796,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447071</v>
+        <v>447244</v>
       </c>
       <c r="R23" t="n">
-        <v>6804595</v>
+        <v>6804361</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,45 +2850,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129894040</v>
+        <v>129893945</v>
       </c>
       <c r="B24" t="n">
-        <v>79087</v>
+        <v>56933</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>102613</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447244</v>
+        <v>447140</v>
       </c>
       <c r="R24" t="n">
-        <v>6804361</v>
+        <v>6804358</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894047</v>
+        <v>129893919</v>
       </c>
       <c r="B28" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447264</v>
+        <v>447260</v>
       </c>
       <c r="R28" t="n">
-        <v>6804394</v>
+        <v>6804349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,11 +3327,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3358,10 +3353,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893979</v>
+        <v>129894047</v>
       </c>
       <c r="B29" t="n">
-        <v>78844</v>
+        <v>79087</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3369,21 +3364,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3393,10 +3388,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447104</v>
+        <v>447264</v>
       </c>
       <c r="R29" t="n">
-        <v>6804432</v>
+        <v>6804394</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3429,6 +3424,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3455,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894029</v>
+        <v>129893979</v>
       </c>
       <c r="B30" t="n">
-        <v>79087</v>
+        <v>78844</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3490,10 +3490,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447078</v>
+        <v>447104</v>
       </c>
       <c r="R30" t="n">
-        <v>6804574</v>
+        <v>6804432</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3526,11 +3526,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3557,10 +3552,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893935</v>
+        <v>129894029</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3568,42 +3563,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447017</v>
+        <v>447078</v>
       </c>
       <c r="R31" t="n">
-        <v>6804662</v>
+        <v>6804574</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3636,6 +3623,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3662,10 +3654,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893919</v>
+        <v>129893935</v>
       </c>
       <c r="B32" t="n">
-        <v>79677</v>
+        <v>57737</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3673,34 +3665,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447260</v>
+        <v>447017</v>
       </c>
       <c r="R32" t="n">
-        <v>6804349</v>
+        <v>6804662</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894026</v>
+        <v>129893920</v>
       </c>
       <c r="B33" t="n">
-        <v>79087</v>
+        <v>79677</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447019</v>
+        <v>447249</v>
       </c>
       <c r="R33" t="n">
-        <v>6804831</v>
+        <v>6804413</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,11 +3830,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3861,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894028</v>
+        <v>129893955</v>
       </c>
       <c r="B34" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3872,21 +3867,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3896,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447038</v>
+        <v>447237</v>
       </c>
       <c r="R34" t="n">
-        <v>6804585</v>
+        <v>6804433</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3958,7 +3953,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894036</v>
+        <v>129894026</v>
       </c>
       <c r="B35" t="n">
         <v>79087</v>
@@ -3993,10 +3988,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447177</v>
+        <v>447019</v>
       </c>
       <c r="R35" t="n">
-        <v>6804353</v>
+        <v>6804831</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4029,6 +4024,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894046</v>
+        <v>129894028</v>
       </c>
       <c r="B36" t="n">
         <v>79087</v>
@@ -4084,19 +4084,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447137</v>
+        <v>447038</v>
       </c>
       <c r="R36" t="n">
-        <v>6804362</v>
+        <v>6804585</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4131,18 +4128,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,7 +4152,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894034</v>
+        <v>129894036</v>
       </c>
       <c r="B37" t="n">
         <v>79087</v>
@@ -4196,10 +4187,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447146</v>
+        <v>447177</v>
       </c>
       <c r="R37" t="n">
-        <v>6804328</v>
+        <v>6804353</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4258,10 +4249,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893920</v>
+        <v>129894046</v>
       </c>
       <c r="B38" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,34 +4260,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447249</v>
+        <v>447137</v>
       </c>
       <c r="R38" t="n">
-        <v>6804413</v>
+        <v>6804362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4331,12 +4325,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893955</v>
+        <v>129894034</v>
       </c>
       <c r="B39" t="n">
-        <v>78845</v>
+        <v>79087</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447237</v>
+        <v>447146</v>
       </c>
       <c r="R39" t="n">
-        <v>6804433</v>
+        <v>6804328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893980</v>
+        <v>129893933</v>
       </c>
       <c r="B45" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,34 +4948,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447136</v>
+        <v>447075</v>
       </c>
       <c r="R45" t="n">
-        <v>6804407</v>
+        <v>6804732</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894041</v>
+        <v>129893937</v>
       </c>
       <c r="B46" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5045,34 +5053,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447242</v>
+        <v>447059</v>
       </c>
       <c r="R46" t="n">
-        <v>6804443</v>
+        <v>6804587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894035</v>
+        <v>129893936</v>
       </c>
       <c r="B47" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,34 +5158,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447155</v>
+        <v>447012</v>
       </c>
       <c r="R47" t="n">
-        <v>6804339</v>
+        <v>6804645</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,10 +5252,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893969</v>
+        <v>129893918</v>
       </c>
       <c r="B48" t="n">
-        <v>78844</v>
+        <v>79677</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5239,21 +5263,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5263,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447006</v>
+        <v>447021</v>
       </c>
       <c r="R48" t="n">
-        <v>6804728</v>
+        <v>6804646</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893933</v>
+        <v>129893951</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,42 +5360,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447075</v>
+        <v>447014</v>
       </c>
       <c r="R49" t="n">
-        <v>6804732</v>
+        <v>6804638</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5430,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893937</v>
+        <v>129893980</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>78844</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,42 +5457,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447059</v>
+        <v>447136</v>
       </c>
       <c r="R50" t="n">
-        <v>6804587</v>
+        <v>6804407</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5535,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893936</v>
+        <v>129894041</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>79087</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,42 +5554,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447012</v>
+        <v>447242</v>
       </c>
       <c r="R51" t="n">
-        <v>6804645</v>
+        <v>6804443</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893918</v>
+        <v>129894035</v>
       </c>
       <c r="B52" t="n">
-        <v>79677</v>
+        <v>79087</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447021</v>
+        <v>447155</v>
       </c>
       <c r="R52" t="n">
-        <v>6804646</v>
+        <v>6804339</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893951</v>
+        <v>129893969</v>
       </c>
       <c r="B53" t="n">
-        <v>78845</v>
+        <v>78844</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447014</v>
+        <v>447006</v>
       </c>
       <c r="R53" t="n">
-        <v>6804638</v>
+        <v>6804728</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -11185,10 +11185,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129893295</v>
+        <v>129893322</v>
       </c>
       <c r="B108" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11196,34 +11196,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447085</v>
+        <v>447105</v>
       </c>
       <c r="R108" t="n">
-        <v>6804671</v>
+        <v>6804584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11282,10 +11290,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893358</v>
+        <v>129893295</v>
       </c>
       <c r="B109" t="n">
-        <v>78844</v>
+        <v>79706</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11293,21 +11301,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11317,10 +11325,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447319</v>
+        <v>447085</v>
       </c>
       <c r="R109" t="n">
-        <v>6804349</v>
+        <v>6804671</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11379,7 +11387,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893352</v>
+        <v>129893358</v>
       </c>
       <c r="B110" t="n">
         <v>78844</v>
@@ -11414,10 +11422,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447146</v>
+        <v>447319</v>
       </c>
       <c r="R110" t="n">
-        <v>6804415</v>
+        <v>6804349</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11476,10 +11484,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893296</v>
+        <v>129893352</v>
       </c>
       <c r="B111" t="n">
-        <v>79706</v>
+        <v>78844</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,21 +11495,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11511,10 +11519,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447079</v>
+        <v>447146</v>
       </c>
       <c r="R111" t="n">
-        <v>6804660</v>
+        <v>6804415</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11573,10 +11581,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893322</v>
+        <v>129893296</v>
       </c>
       <c r="B112" t="n">
-        <v>57737</v>
+        <v>79706</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11584,42 +11592,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447105</v>
+        <v>447079</v>
       </c>
       <c r="R112" t="n">
-        <v>6804584</v>
+        <v>6804660</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11974,10 +11974,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893314</v>
+        <v>129893297</v>
       </c>
       <c r="B116" t="n">
-        <v>57740</v>
+        <v>79706</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11985,42 +11985,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447227</v>
+        <v>447104</v>
       </c>
       <c r="R116" t="n">
-        <v>6804586</v>
+        <v>6804519</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12079,10 +12071,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893297</v>
+        <v>129893314</v>
       </c>
       <c r="B117" t="n">
-        <v>79706</v>
+        <v>57740</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12090,34 +12082,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447104</v>
+        <v>447227</v>
       </c>
       <c r="R117" t="n">
-        <v>6804519</v>
+        <v>6804586</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893939</v>
+        <v>129894044</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447133</v>
+        <v>446959</v>
       </c>
       <c r="R2" t="n">
-        <v>6804362</v>
+        <v>6804780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894044</v>
+        <v>129893913</v>
       </c>
       <c r="B3" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446959</v>
+        <v>447127</v>
       </c>
       <c r="R3" t="n">
-        <v>6804780</v>
+        <v>6804438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893913</v>
+        <v>129893971</v>
       </c>
       <c r="B4" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447127</v>
+        <v>447009</v>
       </c>
       <c r="R4" t="n">
-        <v>6804438</v>
+        <v>6804689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893971</v>
+        <v>129893939</v>
       </c>
       <c r="B5" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447009</v>
+        <v>447133</v>
       </c>
       <c r="R5" t="n">
-        <v>6804689</v>
+        <v>6804362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
         <v>129893972</v>
       </c>
       <c r="B6" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129894024</v>
       </c>
       <c r="B7" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,10 +1269,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893974</v>
+        <v>129893970</v>
       </c>
       <c r="B8" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447014</v>
+        <v>447006</v>
       </c>
       <c r="R8" t="n">
-        <v>6804644</v>
+        <v>6804685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1366,10 +1366,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893970</v>
+        <v>129893974</v>
       </c>
       <c r="B9" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447006</v>
+        <v>447014</v>
       </c>
       <c r="R9" t="n">
-        <v>6804685</v>
+        <v>6804644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B11" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R11" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,11 +1641,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1672,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B12" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,21 +1678,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R12" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,6 +1738,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894023</v>
+        <v>129893953</v>
       </c>
       <c r="B13" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447120</v>
+        <v>447186</v>
       </c>
       <c r="R13" t="n">
-        <v>6804670</v>
+        <v>6804347</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,11 +1840,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1871,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894050</v>
+        <v>129894023</v>
       </c>
       <c r="B14" t="n">
-        <v>78095</v>
+        <v>79088</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,21 +1877,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447251</v>
+        <v>447120</v>
       </c>
       <c r="R14" t="n">
-        <v>6804480</v>
+        <v>6804670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,13 +1939,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B15" t="n">
-        <v>78845</v>
+        <v>78095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R15" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>129894033</v>
       </c>
       <c r="B16" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,45 +2163,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893973</v>
+        <v>129893923</v>
       </c>
       <c r="B17" t="n">
-        <v>78844</v>
+        <v>56930</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447018</v>
+        <v>447079</v>
       </c>
       <c r="R17" t="n">
-        <v>6804657</v>
+        <v>6804592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2263,7 +2271,7 @@
         <v>129894043</v>
       </c>
       <c r="B18" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2357,53 +2365,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893923</v>
+        <v>129893973</v>
       </c>
       <c r="B19" t="n">
-        <v>56930</v>
+        <v>78845</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447079</v>
+        <v>447018</v>
       </c>
       <c r="R19" t="n">
-        <v>6804592</v>
+        <v>6804657</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
         <v>129894042</v>
       </c>
       <c r="B20" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129894039</v>
       </c>
       <c r="B21" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>129893976</v>
       </c>
       <c r="B22" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>129894040</v>
       </c>
       <c r="B23" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,7 +2958,7 @@
         <v>129893956</v>
       </c>
       <c r="B25" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,45 +3052,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B26" t="n">
-        <v>78845</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R26" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,6 +3140,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3149,54 +3159,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R27" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,7 +3238,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3259,7 +3259,7 @@
         <v>129893919</v>
       </c>
       <c r="B28" t="n">
-        <v>79677</v>
+        <v>79678</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
         <v>129894047</v>
       </c>
       <c r="B29" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3458,7 +3458,7 @@
         <v>129893979</v>
       </c>
       <c r="B30" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894029</v>
+        <v>129893935</v>
       </c>
       <c r="B31" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,34 +3563,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447078</v>
+        <v>447017</v>
       </c>
       <c r="R31" t="n">
-        <v>6804574</v>
+        <v>6804662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,11 +3631,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3654,10 +3657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893935</v>
+        <v>129894029</v>
       </c>
       <c r="B32" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3665,42 +3668,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447017</v>
+        <v>447078</v>
       </c>
       <c r="R32" t="n">
-        <v>6804662</v>
+        <v>6804574</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3733,6 +3728,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893920</v>
+        <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>79677</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447249</v>
+        <v>447019</v>
       </c>
       <c r="R33" t="n">
-        <v>6804413</v>
+        <v>6804831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,6 +3830,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3856,10 +3861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893955</v>
+        <v>129894028</v>
       </c>
       <c r="B34" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3867,21 +3872,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447237</v>
+        <v>447038</v>
       </c>
       <c r="R34" t="n">
-        <v>6804433</v>
+        <v>6804585</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,10 +3958,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894026</v>
+        <v>129894036</v>
       </c>
       <c r="B35" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3988,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447019</v>
+        <v>447177</v>
       </c>
       <c r="R35" t="n">
-        <v>6804831</v>
+        <v>6804353</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4024,11 +4029,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4055,10 +4055,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894028</v>
+        <v>129894046</v>
       </c>
       <c r="B36" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4084,16 +4084,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447038</v>
+        <v>447137</v>
       </c>
       <c r="R36" t="n">
-        <v>6804585</v>
+        <v>6804362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,12 +4131,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4152,10 +4161,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894036</v>
+        <v>129894034</v>
       </c>
       <c r="B37" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4187,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447177</v>
+        <v>447146</v>
       </c>
       <c r="R37" t="n">
-        <v>6804353</v>
+        <v>6804328</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4249,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894046</v>
+        <v>129893955</v>
       </c>
       <c r="B38" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4260,37 +4269,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447137</v>
+        <v>447237</v>
       </c>
       <c r="R38" t="n">
-        <v>6804362</v>
+        <v>6804433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,18 +4331,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894034</v>
+        <v>129893920</v>
       </c>
       <c r="B39" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447146</v>
+        <v>447249</v>
       </c>
       <c r="R39" t="n">
-        <v>6804328</v>
+        <v>6804413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4455,7 +4455,7 @@
         <v>129893977</v>
       </c>
       <c r="B40" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>129893983</v>
       </c>
       <c r="B41" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4649,7 +4649,7 @@
         <v>129894027</v>
       </c>
       <c r="B42" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>129893975</v>
       </c>
       <c r="B43" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4843,7 +4843,7 @@
         <v>129893948</v>
       </c>
       <c r="B44" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893933</v>
+        <v>129893980</v>
       </c>
       <c r="B45" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,42 +4948,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447075</v>
+        <v>447136</v>
       </c>
       <c r="R45" t="n">
-        <v>6804732</v>
+        <v>6804407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,10 +5034,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893937</v>
+        <v>129894041</v>
       </c>
       <c r="B46" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,42 +5045,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447059</v>
+        <v>447242</v>
       </c>
       <c r="R46" t="n">
-        <v>6804587</v>
+        <v>6804443</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5147,10 +5131,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893936</v>
+        <v>129894035</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5158,42 +5142,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447012</v>
+        <v>447155</v>
       </c>
       <c r="R47" t="n">
-        <v>6804645</v>
+        <v>6804339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5252,10 +5228,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893918</v>
+        <v>129893969</v>
       </c>
       <c r="B48" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5263,21 +5239,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5287,10 +5263,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447021</v>
+        <v>447006</v>
       </c>
       <c r="R48" t="n">
-        <v>6804646</v>
+        <v>6804728</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893951</v>
+        <v>129893933</v>
       </c>
       <c r="B49" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,34 +5336,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447014</v>
+        <v>447075</v>
       </c>
       <c r="R49" t="n">
-        <v>6804638</v>
+        <v>6804732</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5430,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893980</v>
+        <v>129893937</v>
       </c>
       <c r="B50" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,34 +5441,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447136</v>
+        <v>447059</v>
       </c>
       <c r="R50" t="n">
-        <v>6804407</v>
+        <v>6804587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5535,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894041</v>
+        <v>129893936</v>
       </c>
       <c r="B51" t="n">
-        <v>79087</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,34 +5546,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447242</v>
+        <v>447012</v>
       </c>
       <c r="R51" t="n">
-        <v>6804443</v>
+        <v>6804645</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129894035</v>
+        <v>129893918</v>
       </c>
       <c r="B52" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447155</v>
+        <v>447021</v>
       </c>
       <c r="R52" t="n">
-        <v>6804339</v>
+        <v>6804646</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893969</v>
+        <v>129893951</v>
       </c>
       <c r="B53" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447006</v>
+        <v>447014</v>
       </c>
       <c r="R53" t="n">
-        <v>6804728</v>
+        <v>6804638</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129893924</v>
+        <v>129893932</v>
       </c>
       <c r="B54" t="n">
-        <v>56930</v>
+        <v>57737</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,7 +5867,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>446997</v>
+        <v>447239</v>
       </c>
       <c r="R54" t="n">
-        <v>6804780</v>
+        <v>6804569</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,11 +5913,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5944,7 +5939,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893932</v>
+        <v>129893938</v>
       </c>
       <c r="B55" t="n">
         <v>57737</v>
@@ -5977,7 +5972,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5987,10 +5982,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447239</v>
+        <v>447064</v>
       </c>
       <c r="R55" t="n">
-        <v>6804569</v>
+        <v>6804548</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6049,32 +6044,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893938</v>
+        <v>129893924</v>
       </c>
       <c r="B56" t="n">
-        <v>57737</v>
+        <v>56930</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6082,7 +6077,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6092,10 +6087,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>447064</v>
+        <v>446997</v>
       </c>
       <c r="R56" t="n">
-        <v>6804548</v>
+        <v>6804780</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6128,6 +6123,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6157,7 +6157,7 @@
         <v>129894045</v>
       </c>
       <c r="B57" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129894025</v>
+        <v>129893968</v>
       </c>
       <c r="B58" t="n">
-        <v>79087</v>
+        <v>78845</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,21 +6267,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447101</v>
+        <v>446972</v>
       </c>
       <c r="R58" t="n">
-        <v>6804700</v>
+        <v>6804770</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893968</v>
+        <v>129893967</v>
       </c>
       <c r="B59" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446972</v>
+        <v>447209</v>
       </c>
       <c r="R59" t="n">
-        <v>6804770</v>
+        <v>6804576</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893967</v>
+        <v>129893950</v>
       </c>
       <c r="B60" t="n">
-        <v>78844</v>
+        <v>78846</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6461,21 +6461,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447209</v>
+        <v>447015</v>
       </c>
       <c r="R60" t="n">
-        <v>6804576</v>
+        <v>6804655</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129893950</v>
+        <v>129894025</v>
       </c>
       <c r="B62" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447015</v>
+        <v>447101</v>
       </c>
       <c r="R62" t="n">
-        <v>6804655</v>
+        <v>6804700</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893952</v>
+        <v>129893914</v>
       </c>
       <c r="B63" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447138</v>
+        <v>447244</v>
       </c>
       <c r="R63" t="n">
-        <v>6804405</v>
+        <v>6804447</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129893914</v>
+        <v>129893912</v>
       </c>
       <c r="B64" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447244</v>
+        <v>447082</v>
       </c>
       <c r="R64" t="n">
-        <v>6804447</v>
+        <v>6804551</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893912</v>
+        <v>129893982</v>
       </c>
       <c r="B65" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447082</v>
+        <v>447163</v>
       </c>
       <c r="R65" t="n">
-        <v>6804551</v>
+        <v>6804342</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893982</v>
+        <v>129894038</v>
       </c>
       <c r="B66" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447163</v>
+        <v>447196</v>
       </c>
       <c r="R66" t="n">
-        <v>6804342</v>
+        <v>6804341</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129894038</v>
+        <v>129893952</v>
       </c>
       <c r="B67" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,21 +7148,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447196</v>
+        <v>447138</v>
       </c>
       <c r="R67" t="n">
-        <v>6804341</v>
+        <v>6804405</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129893324</v>
+        <v>129893347</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7350,42 +7350,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447118</v>
+        <v>447114</v>
       </c>
       <c r="R69" t="n">
-        <v>6804529</v>
+        <v>6804581</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7444,10 +7436,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893347</v>
+        <v>129893324</v>
       </c>
       <c r="B70" t="n">
-        <v>78844</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,34 +7447,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447114</v>
+        <v>447118</v>
       </c>
       <c r="R70" t="n">
-        <v>6804581</v>
+        <v>6804529</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7544,7 +7544,7 @@
         <v>129893402</v>
       </c>
       <c r="B71" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129893404</v>
       </c>
       <c r="B72" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>129893403</v>
       </c>
       <c r="B73" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>129893400</v>
       </c>
       <c r="B74" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>129893393</v>
       </c>
       <c r="B75" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>129893356</v>
       </c>
       <c r="B76" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8238,32 +8238,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893368</v>
+        <v>129893306</v>
       </c>
       <c r="B78" t="n">
-        <v>90987</v>
+        <v>79707</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5685</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447279</v>
+        <v>447282</v>
       </c>
       <c r="R78" t="n">
-        <v>6804380</v>
+        <v>6804440</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8317,7 +8317,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8336,7 +8335,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893334</v>
+        <v>129893353</v>
       </c>
       <c r="B79" t="n">
         <v>78845</v>
@@ -8347,21 +8346,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8371,10 +8370,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447287</v>
+        <v>447206</v>
       </c>
       <c r="R79" t="n">
-        <v>6804433</v>
+        <v>6804417</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8433,10 +8432,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893306</v>
+        <v>129893395</v>
       </c>
       <c r="B80" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8444,21 +8443,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8468,7 +8467,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447282</v>
+        <v>447137</v>
       </c>
       <c r="R80" t="n">
         <v>6804440</v>
@@ -8504,6 +8503,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8530,32 +8534,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893353</v>
+        <v>129893368</v>
       </c>
       <c r="B81" t="n">
-        <v>78844</v>
+        <v>90988</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6446</v>
+        <v>5685</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8565,10 +8569,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447206</v>
+        <v>447279</v>
       </c>
       <c r="R81" t="n">
-        <v>6804417</v>
+        <v>6804380</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8609,6 +8613,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8627,10 +8632,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893395</v>
+        <v>129893334</v>
       </c>
       <c r="B82" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8638,21 +8643,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8662,10 +8667,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447137</v>
+        <v>447287</v>
       </c>
       <c r="R82" t="n">
-        <v>6804440</v>
+        <v>6804433</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8698,11 +8703,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8732,7 +8732,7 @@
         <v>129893303</v>
       </c>
       <c r="B83" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8829,7 +8829,7 @@
         <v>129893397</v>
       </c>
       <c r="B84" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8931,7 +8931,7 @@
         <v>129893348</v>
       </c>
       <c r="B85" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>129893305</v>
       </c>
       <c r="B86" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>129893392</v>
       </c>
       <c r="B87" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>129893405</v>
       </c>
       <c r="B88" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>129893307</v>
       </c>
       <c r="B89" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>129893360</v>
       </c>
       <c r="B90" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>129893399</v>
       </c>
       <c r="B91" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>129893351</v>
       </c>
       <c r="B92" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9709,45 +9709,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893309</v>
+        <v>129893316</v>
       </c>
       <c r="B93" t="n">
-        <v>79677</v>
+        <v>56930</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447247</v>
+        <v>447102</v>
       </c>
       <c r="R93" t="n">
-        <v>6804552</v>
+        <v>6804551</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9806,53 +9814,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129893316</v>
+        <v>129893309</v>
       </c>
       <c r="B94" t="n">
-        <v>56930</v>
+        <v>79678</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447102</v>
+        <v>447247</v>
       </c>
       <c r="R94" t="n">
-        <v>6804551</v>
+        <v>6804552</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9914,7 +9914,7 @@
         <v>129893407</v>
       </c>
       <c r="B95" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>129893332</v>
       </c>
       <c r="B97" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893310</v>
+        <v>129893359</v>
       </c>
       <c r="B98" t="n">
-        <v>79677</v>
+        <v>78845</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447280</v>
+        <v>447276</v>
       </c>
       <c r="R98" t="n">
-        <v>6804428</v>
+        <v>6804418</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893359</v>
+        <v>129893350</v>
       </c>
       <c r="B99" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447276</v>
+        <v>447120</v>
       </c>
       <c r="R99" t="n">
-        <v>6804418</v>
+        <v>6804506</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893350</v>
+        <v>129893396</v>
       </c>
       <c r="B100" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447120</v>
+        <v>447170</v>
       </c>
       <c r="R100" t="n">
-        <v>6804506</v>
+        <v>6804344</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,6 +10475,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10501,10 +10506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893396</v>
+        <v>129893310</v>
       </c>
       <c r="B101" t="n">
-        <v>79087</v>
+        <v>79678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10512,21 +10517,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10536,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447170</v>
+        <v>447280</v>
       </c>
       <c r="R101" t="n">
-        <v>6804344</v>
+        <v>6804428</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10572,11 +10577,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10606,7 +10606,7 @@
         <v>129893344</v>
       </c>
       <c r="B102" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>129893357</v>
       </c>
       <c r="B103" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>129893301</v>
       </c>
       <c r="B104" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>129893398</v>
       </c>
       <c r="B105" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>129893346</v>
       </c>
       <c r="B106" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>129893299</v>
       </c>
       <c r="B107" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129893322</v>
+        <v>129893295</v>
       </c>
       <c r="B108" t="n">
-        <v>57737</v>
+        <v>79707</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11196,42 +11196,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447105</v>
+        <v>447085</v>
       </c>
       <c r="R108" t="n">
-        <v>6804584</v>
+        <v>6804671</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11290,10 +11282,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893295</v>
+        <v>129893358</v>
       </c>
       <c r="B109" t="n">
-        <v>79706</v>
+        <v>78845</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11301,21 +11293,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11325,10 +11317,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447085</v>
+        <v>447319</v>
       </c>
       <c r="R109" t="n">
-        <v>6804671</v>
+        <v>6804349</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11387,10 +11379,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893358</v>
+        <v>129893352</v>
       </c>
       <c r="B110" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11422,10 +11414,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447319</v>
+        <v>447146</v>
       </c>
       <c r="R110" t="n">
-        <v>6804349</v>
+        <v>6804415</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11484,10 +11476,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893352</v>
+        <v>129893296</v>
       </c>
       <c r="B111" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11495,21 +11487,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11519,10 +11511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447146</v>
+        <v>447079</v>
       </c>
       <c r="R111" t="n">
-        <v>6804415</v>
+        <v>6804660</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11581,10 +11573,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893296</v>
+        <v>129893322</v>
       </c>
       <c r="B112" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11592,34 +11584,42 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447079</v>
+        <v>447105</v>
       </c>
       <c r="R112" t="n">
-        <v>6804660</v>
+        <v>6804584</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11681,7 +11681,7 @@
         <v>129893300</v>
       </c>
       <c r="B113" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>129893394</v>
       </c>
       <c r="B114" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>129893308</v>
       </c>
       <c r="B115" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11977,7 +11977,7 @@
         <v>129893297</v>
       </c>
       <c r="B116" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129893302</v>
+        <v>129893325</v>
       </c>
       <c r="B118" t="n">
-        <v>79706</v>
+        <v>57737</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12187,34 +12187,42 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447140</v>
+        <v>447201</v>
       </c>
       <c r="R118" t="n">
-        <v>6804436</v>
+        <v>6804314</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12273,10 +12281,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129893354</v>
+        <v>129893302</v>
       </c>
       <c r="B119" t="n">
-        <v>78844</v>
+        <v>79707</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12284,21 +12292,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12308,10 +12316,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447193</v>
+        <v>447140</v>
       </c>
       <c r="R119" t="n">
-        <v>6804389</v>
+        <v>6804436</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12370,10 +12378,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893325</v>
+        <v>129893354</v>
       </c>
       <c r="B120" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12381,42 +12389,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447201</v>
+        <v>447193</v>
       </c>
       <c r="R120" t="n">
-        <v>6804314</v>
+        <v>6804389</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129893401</v>
+        <v>129893333</v>
       </c>
       <c r="B121" t="n">
-        <v>79087</v>
+        <v>78846</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,21 +12486,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447291</v>
+        <v>447284</v>
       </c>
       <c r="R121" t="n">
-        <v>6804354</v>
+        <v>6804412</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12546,11 +12546,6 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12577,10 +12572,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893408</v>
+        <v>129893401</v>
       </c>
       <c r="B122" t="n">
-        <v>79087</v>
+        <v>79088</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12612,10 +12607,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447247</v>
+        <v>447291</v>
       </c>
       <c r="R122" t="n">
-        <v>6804486</v>
+        <v>6804354</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12648,6 +12643,11 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12674,10 +12674,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893304</v>
+        <v>129893408</v>
       </c>
       <c r="B123" t="n">
-        <v>79706</v>
+        <v>79088</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12685,21 +12685,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447208</v>
+        <v>447247</v>
       </c>
       <c r="R123" t="n">
-        <v>6804423</v>
+        <v>6804486</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12771,10 +12771,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129893406</v>
+        <v>129893304</v>
       </c>
       <c r="B124" t="n">
-        <v>79087</v>
+        <v>79707</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12782,21 +12782,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12806,10 +12806,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447282</v>
+        <v>447208</v>
       </c>
       <c r="R124" t="n">
-        <v>6804440</v>
+        <v>6804423</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12842,11 +12842,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12873,10 +12868,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893355</v>
+        <v>129893406</v>
       </c>
       <c r="B125" t="n">
-        <v>78844</v>
+        <v>79088</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12884,21 +12879,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12908,10 +12903,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447175</v>
+        <v>447282</v>
       </c>
       <c r="R125" t="n">
-        <v>6804401</v>
+        <v>6804440</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12944,6 +12939,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12970,7 +12970,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893333</v>
+        <v>129893355</v>
       </c>
       <c r="B126" t="n">
         <v>78845</v>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447284</v>
+        <v>447175</v>
       </c>
       <c r="R126" t="n">
-        <v>6804412</v>
+        <v>6804401</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13070,7 +13070,7 @@
         <v>129893349</v>
       </c>
       <c r="B127" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>129893298</v>
       </c>
       <c r="B128" t="n">
-        <v>79706</v>
+        <v>79707</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>129893345</v>
       </c>
       <c r="B129" t="n">
-        <v>78844</v>
+        <v>78845</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R11" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,6 +1641,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1667,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R12" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,11 +1743,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>78095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R13" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1848,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1968,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894050</v>
+        <v>129893953</v>
       </c>
       <c r="B15" t="n">
-        <v>78095</v>
+        <v>78846</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447251</v>
+        <v>447186</v>
       </c>
       <c r="R15" t="n">
-        <v>6804480</v>
+        <v>6804347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,7 +2048,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -3052,54 +3052,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R26" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,7 +3131,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3149,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R27" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,6 +3237,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893919</v>
+        <v>129894047</v>
       </c>
       <c r="B28" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,21 +3267,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447260</v>
+        <v>447264</v>
       </c>
       <c r="R28" t="n">
-        <v>6804349</v>
+        <v>6804394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,6 +3327,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3353,10 +3358,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894047</v>
+        <v>129893979</v>
       </c>
       <c r="B29" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3364,21 +3369,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3388,10 +3393,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447264</v>
+        <v>447104</v>
       </c>
       <c r="R29" t="n">
-        <v>6804394</v>
+        <v>6804432</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,11 +3429,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3455,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893979</v>
+        <v>129893935</v>
       </c>
       <c r="B30" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,34 +3466,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447104</v>
+        <v>447017</v>
       </c>
       <c r="R30" t="n">
-        <v>6804432</v>
+        <v>6804662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3552,10 +3560,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893935</v>
+        <v>129894029</v>
       </c>
       <c r="B31" t="n">
-        <v>57737</v>
+        <v>79088</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3563,42 +3571,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447017</v>
+        <v>447078</v>
       </c>
       <c r="R31" t="n">
-        <v>6804662</v>
+        <v>6804574</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3631,6 +3631,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3657,10 +3662,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129894029</v>
+        <v>129893919</v>
       </c>
       <c r="B32" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3668,21 +3673,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3692,10 +3697,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447078</v>
+        <v>447260</v>
       </c>
       <c r="R32" t="n">
-        <v>6804574</v>
+        <v>6804349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3728,11 +3733,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894026</v>
+        <v>129893955</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447019</v>
+        <v>447237</v>
       </c>
       <c r="R33" t="n">
-        <v>6804831</v>
+        <v>6804433</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,11 +3830,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3861,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129894028</v>
+        <v>129893920</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3872,21 +3867,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3896,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447038</v>
+        <v>447249</v>
       </c>
       <c r="R34" t="n">
-        <v>6804585</v>
+        <v>6804413</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3958,7 +3953,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894036</v>
+        <v>129894026</v>
       </c>
       <c r="B35" t="n">
         <v>79088</v>
@@ -3993,10 +3988,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447177</v>
+        <v>447019</v>
       </c>
       <c r="R35" t="n">
-        <v>6804353</v>
+        <v>6804831</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4029,6 +4024,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894046</v>
+        <v>129894028</v>
       </c>
       <c r="B36" t="n">
         <v>79088</v>
@@ -4084,19 +4084,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447137</v>
+        <v>447038</v>
       </c>
       <c r="R36" t="n">
-        <v>6804362</v>
+        <v>6804585</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4131,18 +4128,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4161,7 +4152,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894034</v>
+        <v>129894036</v>
       </c>
       <c r="B37" t="n">
         <v>79088</v>
@@ -4196,10 +4187,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447146</v>
+        <v>447177</v>
       </c>
       <c r="R37" t="n">
-        <v>6804328</v>
+        <v>6804353</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4258,10 +4249,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893955</v>
+        <v>129894046</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,34 +4260,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447237</v>
+        <v>447137</v>
       </c>
       <c r="R38" t="n">
-        <v>6804433</v>
+        <v>6804362</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4331,12 +4325,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893920</v>
+        <v>129894034</v>
       </c>
       <c r="B39" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447249</v>
+        <v>447146</v>
       </c>
       <c r="R39" t="n">
-        <v>6804413</v>
+        <v>6804328</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893933</v>
+        <v>129893918</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,42 +5336,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447075</v>
+        <v>447021</v>
       </c>
       <c r="R49" t="n">
-        <v>6804732</v>
+        <v>6804646</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5430,10 +5422,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893937</v>
+        <v>129893951</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,42 +5433,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447059</v>
+        <v>447014</v>
       </c>
       <c r="R50" t="n">
-        <v>6804587</v>
+        <v>6804638</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5535,7 +5519,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893936</v>
+        <v>129893933</v>
       </c>
       <c r="B51" t="n">
         <v>57737</v>
@@ -5578,10 +5562,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447012</v>
+        <v>447075</v>
       </c>
       <c r="R51" t="n">
-        <v>6804645</v>
+        <v>6804732</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5624,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893918</v>
+        <v>129893937</v>
       </c>
       <c r="B52" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,34 +5635,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447021</v>
+        <v>447059</v>
       </c>
       <c r="R52" t="n">
-        <v>6804646</v>
+        <v>6804587</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5729,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893951</v>
+        <v>129893936</v>
       </c>
       <c r="B53" t="n">
-        <v>78846</v>
+        <v>57737</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,34 +5740,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447014</v>
+        <v>447012</v>
       </c>
       <c r="R53" t="n">
-        <v>6804638</v>
+        <v>6804645</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893914</v>
+        <v>129893952</v>
       </c>
       <c r="B63" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447244</v>
+        <v>447138</v>
       </c>
       <c r="R63" t="n">
-        <v>6804447</v>
+        <v>6804405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129893912</v>
+        <v>129893914</v>
       </c>
       <c r="B64" t="n">
         <v>79707</v>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447082</v>
+        <v>447244</v>
       </c>
       <c r="R64" t="n">
-        <v>6804551</v>
+        <v>6804447</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893982</v>
+        <v>129893912</v>
       </c>
       <c r="B65" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447163</v>
+        <v>447082</v>
       </c>
       <c r="R65" t="n">
-        <v>6804342</v>
+        <v>6804551</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129894038</v>
+        <v>129893982</v>
       </c>
       <c r="B66" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447196</v>
+        <v>447163</v>
       </c>
       <c r="R66" t="n">
-        <v>6804341</v>
+        <v>6804342</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893952</v>
+        <v>129894038</v>
       </c>
       <c r="B67" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,21 +7148,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447138</v>
+        <v>447196</v>
       </c>
       <c r="R67" t="n">
-        <v>6804405</v>
+        <v>6804341</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893359</v>
+        <v>129893310</v>
       </c>
       <c r="B98" t="n">
-        <v>78845</v>
+        <v>79678</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447276</v>
+        <v>447280</v>
       </c>
       <c r="R98" t="n">
-        <v>6804418</v>
+        <v>6804428</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,7 +10307,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893350</v>
+        <v>129893359</v>
       </c>
       <c r="B99" t="n">
         <v>78845</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447120</v>
+        <v>447276</v>
       </c>
       <c r="R99" t="n">
-        <v>6804506</v>
+        <v>6804418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893396</v>
+        <v>129893350</v>
       </c>
       <c r="B100" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447170</v>
+        <v>447120</v>
       </c>
       <c r="R100" t="n">
-        <v>6804344</v>
+        <v>6804506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,11 +10475,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10506,10 +10501,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893310</v>
+        <v>129893396</v>
       </c>
       <c r="B101" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10512,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10536,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447280</v>
+        <v>447170</v>
       </c>
       <c r="R101" t="n">
-        <v>6804428</v>
+        <v>6804344</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10577,6 +10572,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B11" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R11" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,11 +1641,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1672,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B12" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,21 +1678,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R12" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,6 +1738,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894050</v>
+        <v>129893953</v>
       </c>
       <c r="B13" t="n">
-        <v>78095</v>
+        <v>78846</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447251</v>
+        <v>447186</v>
       </c>
       <c r="R13" t="n">
-        <v>6804480</v>
+        <v>6804347</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,7 +1848,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B15" t="n">
-        <v>78846</v>
+        <v>78095</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R15" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -3052,45 +3052,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B26" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R26" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3131,6 +3140,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3149,54 +3159,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B27" t="n">
-        <v>8451</v>
+        <v>78846</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R27" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3237,7 +3238,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893955</v>
+        <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>78846</v>
+        <v>79088</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447237</v>
+        <v>447019</v>
       </c>
       <c r="R33" t="n">
-        <v>6804433</v>
+        <v>6804831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,6 +3830,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3856,10 +3861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893920</v>
+        <v>129894028</v>
       </c>
       <c r="B34" t="n">
-        <v>79678</v>
+        <v>79088</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3867,21 +3872,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447249</v>
+        <v>447038</v>
       </c>
       <c r="R34" t="n">
-        <v>6804413</v>
+        <v>6804585</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,7 +3958,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894026</v>
+        <v>129894036</v>
       </c>
       <c r="B35" t="n">
         <v>79088</v>
@@ -3988,10 +3993,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447019</v>
+        <v>447177</v>
       </c>
       <c r="R35" t="n">
-        <v>6804831</v>
+        <v>6804353</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4024,11 +4029,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4055,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894028</v>
+        <v>129894046</v>
       </c>
       <c r="B36" t="n">
         <v>79088</v>
@@ -4084,16 +4084,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447038</v>
+        <v>447137</v>
       </c>
       <c r="R36" t="n">
-        <v>6804585</v>
+        <v>6804362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4128,12 +4131,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4152,7 +4161,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894036</v>
+        <v>129894034</v>
       </c>
       <c r="B37" t="n">
         <v>79088</v>
@@ -4187,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447177</v>
+        <v>447146</v>
       </c>
       <c r="R37" t="n">
-        <v>6804353</v>
+        <v>6804328</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4249,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894046</v>
+        <v>129893955</v>
       </c>
       <c r="B38" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4260,37 +4269,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447137</v>
+        <v>447237</v>
       </c>
       <c r="R38" t="n">
-        <v>6804362</v>
+        <v>6804433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4325,18 +4331,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894034</v>
+        <v>129893920</v>
       </c>
       <c r="B39" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447146</v>
+        <v>447249</v>
       </c>
       <c r="R39" t="n">
-        <v>6804328</v>
+        <v>6804413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5325,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893918</v>
+        <v>129893933</v>
       </c>
       <c r="B49" t="n">
-        <v>79678</v>
+        <v>57737</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,34 +5336,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447021</v>
+        <v>447075</v>
       </c>
       <c r="R49" t="n">
-        <v>6804646</v>
+        <v>6804732</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5422,10 +5430,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893951</v>
+        <v>129893937</v>
       </c>
       <c r="B50" t="n">
-        <v>78846</v>
+        <v>57737</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5433,34 +5441,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447014</v>
+        <v>447059</v>
       </c>
       <c r="R50" t="n">
-        <v>6804638</v>
+        <v>6804587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5519,7 +5535,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893933</v>
+        <v>129893936</v>
       </c>
       <c r="B51" t="n">
         <v>57737</v>
@@ -5562,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447075</v>
+        <v>447012</v>
       </c>
       <c r="R51" t="n">
-        <v>6804732</v>
+        <v>6804645</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5624,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893937</v>
+        <v>129893918</v>
       </c>
       <c r="B52" t="n">
-        <v>57737</v>
+        <v>79678</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5635,42 +5651,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447059</v>
+        <v>447021</v>
       </c>
       <c r="R52" t="n">
-        <v>6804587</v>
+        <v>6804646</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5729,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893936</v>
+        <v>129893951</v>
       </c>
       <c r="B53" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5740,42 +5748,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447012</v>
+        <v>447014</v>
       </c>
       <c r="R53" t="n">
-        <v>6804645</v>
+        <v>6804638</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129893968</v>
+        <v>129893934</v>
       </c>
       <c r="B58" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,34 +6267,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>446972</v>
+        <v>447006</v>
       </c>
       <c r="R58" t="n">
-        <v>6804770</v>
+        <v>6804684</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,10 +6361,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893967</v>
+        <v>129894025</v>
       </c>
       <c r="B59" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6364,21 +6372,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6388,10 +6396,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447209</v>
+        <v>447101</v>
       </c>
       <c r="R59" t="n">
-        <v>6804576</v>
+        <v>6804700</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,10 +6458,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893950</v>
+        <v>129893968</v>
       </c>
       <c r="B60" t="n">
-        <v>78846</v>
+        <v>78845</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6461,21 +6469,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6485,10 +6493,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447015</v>
+        <v>446972</v>
       </c>
       <c r="R60" t="n">
-        <v>6804655</v>
+        <v>6804770</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6547,10 +6555,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893934</v>
+        <v>129893967</v>
       </c>
       <c r="B61" t="n">
-        <v>57737</v>
+        <v>78845</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6558,42 +6566,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447006</v>
+        <v>447209</v>
       </c>
       <c r="R61" t="n">
-        <v>6804684</v>
+        <v>6804576</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6652,10 +6652,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129894025</v>
+        <v>129893950</v>
       </c>
       <c r="B62" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6663,21 +6663,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447101</v>
+        <v>447015</v>
       </c>
       <c r="R62" t="n">
-        <v>6804700</v>
+        <v>6804655</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893952</v>
+        <v>129893921</v>
       </c>
       <c r="B63" t="n">
-        <v>78846</v>
+        <v>57740</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,34 +6760,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447138</v>
+        <v>447004</v>
       </c>
       <c r="R63" t="n">
-        <v>6804405</v>
+        <v>6804712</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7234,10 +7242,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893921</v>
+        <v>129893952</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>78846</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7245,42 +7253,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447004</v>
+        <v>447138</v>
       </c>
       <c r="R68" t="n">
-        <v>6804712</v>
+        <v>6804405</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893393</v>
+        <v>129893315</v>
       </c>
       <c r="B75" t="n">
-        <v>79088</v>
+        <v>57740</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7945,34 +7945,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447110</v>
+        <v>447115</v>
       </c>
       <c r="R75" t="n">
-        <v>6804630</v>
+        <v>6804531</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,11 +8013,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8036,10 +8039,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893356</v>
+        <v>129893393</v>
       </c>
       <c r="B76" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8047,21 +8050,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8071,10 +8074,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447165</v>
+        <v>447110</v>
       </c>
       <c r="R76" t="n">
-        <v>6804365</v>
+        <v>6804630</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8107,6 +8110,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8133,10 +8141,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893315</v>
+        <v>129893356</v>
       </c>
       <c r="B77" t="n">
-        <v>57740</v>
+        <v>78845</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,42 +8152,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447115</v>
+        <v>447165</v>
       </c>
       <c r="R77" t="n">
-        <v>6804531</v>
+        <v>6804365</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8238,32 +8238,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893306</v>
+        <v>129893368</v>
       </c>
       <c r="B78" t="n">
-        <v>79707</v>
+        <v>90988</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447282</v>
+        <v>447279</v>
       </c>
       <c r="R78" t="n">
-        <v>6804440</v>
+        <v>6804380</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8317,6 +8317,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8335,10 +8336,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893353</v>
+        <v>129893306</v>
       </c>
       <c r="B79" t="n">
-        <v>78845</v>
+        <v>79707</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8346,21 +8347,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8370,10 +8371,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447206</v>
+        <v>447282</v>
       </c>
       <c r="R79" t="n">
-        <v>6804417</v>
+        <v>6804440</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8432,10 +8433,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893395</v>
+        <v>129893353</v>
       </c>
       <c r="B80" t="n">
-        <v>79088</v>
+        <v>78845</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8443,21 +8444,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8467,10 +8468,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447137</v>
+        <v>447206</v>
       </c>
       <c r="R80" t="n">
-        <v>6804440</v>
+        <v>6804417</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8503,11 +8504,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8534,32 +8530,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893368</v>
+        <v>129893395</v>
       </c>
       <c r="B81" t="n">
-        <v>90988</v>
+        <v>79088</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5685</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8565,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447279</v>
+        <v>447137</v>
       </c>
       <c r="R81" t="n">
-        <v>6804380</v>
+        <v>6804440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8607,13 +8603,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893310</v>
+        <v>129893359</v>
       </c>
       <c r="B98" t="n">
-        <v>79678</v>
+        <v>78845</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447280</v>
+        <v>447276</v>
       </c>
       <c r="R98" t="n">
-        <v>6804428</v>
+        <v>6804418</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,7 +10307,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893359</v>
+        <v>129893350</v>
       </c>
       <c r="B99" t="n">
         <v>78845</v>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447276</v>
+        <v>447120</v>
       </c>
       <c r="R99" t="n">
-        <v>6804418</v>
+        <v>6804506</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893350</v>
+        <v>129893396</v>
       </c>
       <c r="B100" t="n">
-        <v>78845</v>
+        <v>79088</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447120</v>
+        <v>447170</v>
       </c>
       <c r="R100" t="n">
-        <v>6804506</v>
+        <v>6804344</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,6 +10475,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10501,10 +10506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893396</v>
+        <v>129893310</v>
       </c>
       <c r="B101" t="n">
-        <v>79088</v>
+        <v>79678</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10512,21 +10517,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10536,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447170</v>
+        <v>447280</v>
       </c>
       <c r="R101" t="n">
-        <v>6804344</v>
+        <v>6804428</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10572,11 +10577,6 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD101" t="b">

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129894044</v>
+        <v>129893939</v>
       </c>
       <c r="B2" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>446959</v>
+        <v>447133</v>
       </c>
       <c r="R2" t="n">
-        <v>6804780</v>
+        <v>6804362</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,7 +783,7 @@
         <v>129893913</v>
       </c>
       <c r="B3" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +880,7 @@
         <v>129893971</v>
       </c>
       <c r="B4" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893939</v>
+        <v>129894044</v>
       </c>
       <c r="B5" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,42 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447133</v>
+        <v>446959</v>
       </c>
       <c r="R5" t="n">
-        <v>6804362</v>
+        <v>6804780</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,7 +1074,7 @@
         <v>129893972</v>
       </c>
       <c r="B6" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,7 +1175,7 @@
         <v>129894024</v>
       </c>
       <c r="B7" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1272,7 +1272,7 @@
         <v>129893970</v>
       </c>
       <c r="B8" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>129893974</v>
       </c>
       <c r="B9" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B11" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R11" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,6 +1641,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1667,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B12" t="n">
-        <v>79088</v>
+        <v>78847</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R12" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,11 +1743,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B13" t="n">
-        <v>78846</v>
+        <v>78096</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R13" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1848,6 +1848,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1869,7 +1870,7 @@
         <v>129894023</v>
       </c>
       <c r="B14" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,10 +1969,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129894050</v>
+        <v>129893953</v>
       </c>
       <c r="B15" t="n">
-        <v>78095</v>
+        <v>78847</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1979,21 +1980,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2003,10 +2004,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447251</v>
+        <v>447186</v>
       </c>
       <c r="R15" t="n">
-        <v>6804480</v>
+        <v>6804347</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2047,7 +2048,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>129894033</v>
       </c>
       <c r="B16" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,53 +2163,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893923</v>
+        <v>129893973</v>
       </c>
       <c r="B17" t="n">
-        <v>56930</v>
+        <v>78846</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447079</v>
+        <v>447018</v>
       </c>
       <c r="R17" t="n">
-        <v>6804592</v>
+        <v>6804657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2271,7 +2263,7 @@
         <v>129894043</v>
       </c>
       <c r="B18" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2365,45 +2357,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893973</v>
+        <v>129893923</v>
       </c>
       <c r="B19" t="n">
-        <v>78845</v>
+        <v>56930</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447018</v>
+        <v>447079</v>
       </c>
       <c r="R19" t="n">
-        <v>6804657</v>
+        <v>6804592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
         <v>129894042</v>
       </c>
       <c r="B20" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129894039</v>
       </c>
       <c r="B21" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,45 +2656,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893976</v>
+        <v>129893945</v>
       </c>
       <c r="B22" t="n">
-        <v>78845</v>
+        <v>56933</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447071</v>
+        <v>447140</v>
       </c>
       <c r="R22" t="n">
-        <v>6804595</v>
+        <v>6804358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2753,10 +2761,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894040</v>
+        <v>129893976</v>
       </c>
       <c r="B23" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2764,21 +2772,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2788,10 +2796,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447244</v>
+        <v>447071</v>
       </c>
       <c r="R23" t="n">
-        <v>6804361</v>
+        <v>6804595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2850,53 +2858,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893945</v>
+        <v>129894040</v>
       </c>
       <c r="B24" t="n">
-        <v>56933</v>
+        <v>79089</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447140</v>
+        <v>447244</v>
       </c>
       <c r="R24" t="n">
-        <v>6804358</v>
+        <v>6804361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2958,7 +2958,7 @@
         <v>129893956</v>
       </c>
       <c r="B25" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3052,54 +3052,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>78847</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R26" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,7 +3131,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3149,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B27" t="n">
-        <v>78846</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R27" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,6 +3237,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894047</v>
+        <v>129893935</v>
       </c>
       <c r="B28" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,34 +3267,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447264</v>
+        <v>447017</v>
       </c>
       <c r="R28" t="n">
-        <v>6804394</v>
+        <v>6804662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,11 +3335,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3358,10 +3361,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893979</v>
+        <v>129894047</v>
       </c>
       <c r="B29" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3369,21 +3372,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3393,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447104</v>
+        <v>447264</v>
       </c>
       <c r="R29" t="n">
-        <v>6804432</v>
+        <v>6804394</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3429,6 +3432,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3463,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893935</v>
+        <v>129894029</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,42 +3474,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447017</v>
+        <v>447078</v>
       </c>
       <c r="R30" t="n">
-        <v>6804662</v>
+        <v>6804574</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3534,6 +3534,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3560,10 +3565,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894029</v>
+        <v>129893979</v>
       </c>
       <c r="B31" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3571,21 +3576,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3595,10 +3600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447078</v>
+        <v>447104</v>
       </c>
       <c r="R31" t="n">
-        <v>6804574</v>
+        <v>6804432</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3631,11 +3636,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3665,7 +3665,7 @@
         <v>129893919</v>
       </c>
       <c r="B32" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3762,7 +3762,7 @@
         <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>129894028</v>
       </c>
       <c r="B34" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129894036</v>
       </c>
       <c r="B35" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>129894046</v>
       </c>
       <c r="B36" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>129894034</v>
       </c>
       <c r="B37" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4258,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129893955</v>
+        <v>129893920</v>
       </c>
       <c r="B38" t="n">
-        <v>78846</v>
+        <v>79679</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4269,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4293,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447237</v>
+        <v>447249</v>
       </c>
       <c r="R38" t="n">
-        <v>6804433</v>
+        <v>6804413</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4355,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129893920</v>
+        <v>129893955</v>
       </c>
       <c r="B39" t="n">
-        <v>79678</v>
+        <v>78847</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4366,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4390,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447249</v>
+        <v>447237</v>
       </c>
       <c r="R39" t="n">
-        <v>6804413</v>
+        <v>6804433</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4455,7 +4455,7 @@
         <v>129893977</v>
       </c>
       <c r="B40" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         <v>129893983</v>
       </c>
       <c r="B41" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894027</v>
+        <v>129893975</v>
       </c>
       <c r="B42" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446979</v>
+        <v>447017</v>
       </c>
       <c r="R42" t="n">
-        <v>6804787</v>
+        <v>6804644</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129893975</v>
+        <v>129894027</v>
       </c>
       <c r="B43" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447017</v>
+        <v>446979</v>
       </c>
       <c r="R43" t="n">
-        <v>6804644</v>
+        <v>6804787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4843,7 +4843,7 @@
         <v>129893948</v>
       </c>
       <c r="B44" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893980</v>
+        <v>129893936</v>
       </c>
       <c r="B45" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,34 +4948,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447136</v>
+        <v>447012</v>
       </c>
       <c r="R45" t="n">
-        <v>6804407</v>
+        <v>6804645</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894041</v>
+        <v>129893937</v>
       </c>
       <c r="B46" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5045,34 +5053,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447242</v>
+        <v>447059</v>
       </c>
       <c r="R46" t="n">
-        <v>6804443</v>
+        <v>6804587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129894035</v>
+        <v>129893933</v>
       </c>
       <c r="B47" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,34 +5158,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447155</v>
+        <v>447075</v>
       </c>
       <c r="R47" t="n">
-        <v>6804339</v>
+        <v>6804732</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,10 +5252,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893969</v>
+        <v>129893980</v>
       </c>
       <c r="B48" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5263,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447006</v>
+        <v>447136</v>
       </c>
       <c r="R48" t="n">
-        <v>6804728</v>
+        <v>6804407</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893933</v>
+        <v>129893969</v>
       </c>
       <c r="B49" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,42 +5360,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447075</v>
+        <v>447006</v>
       </c>
       <c r="R49" t="n">
-        <v>6804732</v>
+        <v>6804728</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5430,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893937</v>
+        <v>129894041</v>
       </c>
       <c r="B50" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,42 +5457,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447059</v>
+        <v>447242</v>
       </c>
       <c r="R50" t="n">
-        <v>6804587</v>
+        <v>6804443</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5535,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893936</v>
+        <v>129894035</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,42 +5554,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447012</v>
+        <v>447155</v>
       </c>
       <c r="R51" t="n">
-        <v>6804645</v>
+        <v>6804339</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893918</v>
+        <v>129893951</v>
       </c>
       <c r="B52" t="n">
-        <v>79678</v>
+        <v>78847</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447021</v>
+        <v>447014</v>
       </c>
       <c r="R52" t="n">
-        <v>6804646</v>
+        <v>6804638</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893951</v>
+        <v>129893918</v>
       </c>
       <c r="B53" t="n">
-        <v>78846</v>
+        <v>79679</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447014</v>
+        <v>447021</v>
       </c>
       <c r="R53" t="n">
-        <v>6804638</v>
+        <v>6804646</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6157,7 +6157,7 @@
         <v>129894045</v>
       </c>
       <c r="B57" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>129894025</v>
       </c>
       <c r="B59" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6461,7 +6461,7 @@
         <v>129893968</v>
       </c>
       <c r="B60" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>129893967</v>
       </c>
       <c r="B61" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>129893950</v>
       </c>
       <c r="B62" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893921</v>
+        <v>129893914</v>
       </c>
       <c r="B63" t="n">
-        <v>57740</v>
+        <v>79708</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,42 +6760,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447004</v>
+        <v>447244</v>
       </c>
       <c r="R63" t="n">
-        <v>6804712</v>
+        <v>6804447</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6854,10 +6846,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129893914</v>
+        <v>129893912</v>
       </c>
       <c r="B64" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6889,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447244</v>
+        <v>447082</v>
       </c>
       <c r="R64" t="n">
-        <v>6804447</v>
+        <v>6804551</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6951,10 +6943,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893912</v>
+        <v>129893982</v>
       </c>
       <c r="B65" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6962,21 +6954,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6986,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447082</v>
+        <v>447163</v>
       </c>
       <c r="R65" t="n">
-        <v>6804551</v>
+        <v>6804342</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7048,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893982</v>
+        <v>129894038</v>
       </c>
       <c r="B66" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7059,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7083,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447163</v>
+        <v>447196</v>
       </c>
       <c r="R66" t="n">
-        <v>6804342</v>
+        <v>6804341</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7145,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129894038</v>
+        <v>129893952</v>
       </c>
       <c r="B67" t="n">
-        <v>79088</v>
+        <v>78847</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7156,21 +7148,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7180,10 +7172,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447196</v>
+        <v>447138</v>
       </c>
       <c r="R67" t="n">
-        <v>6804341</v>
+        <v>6804405</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7242,10 +7234,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893952</v>
+        <v>129893921</v>
       </c>
       <c r="B68" t="n">
-        <v>78846</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7253,34 +7245,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447138</v>
+        <v>447004</v>
       </c>
       <c r="R68" t="n">
-        <v>6804405</v>
+        <v>6804712</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129893347</v>
+        <v>129893324</v>
       </c>
       <c r="B69" t="n">
-        <v>78845</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7350,34 +7350,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447114</v>
+        <v>447118</v>
       </c>
       <c r="R69" t="n">
-        <v>6804581</v>
+        <v>6804529</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7436,10 +7444,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893324</v>
+        <v>129893347</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>78846</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7447,42 +7455,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447118</v>
+        <v>447114</v>
       </c>
       <c r="R70" t="n">
-        <v>6804529</v>
+        <v>6804581</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7544,7 +7544,7 @@
         <v>129893402</v>
       </c>
       <c r="B71" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129893404</v>
       </c>
       <c r="B72" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>129893403</v>
       </c>
       <c r="B73" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>129893400</v>
       </c>
       <c r="B74" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8042,7 +8042,7 @@
         <v>129893393</v>
       </c>
       <c r="B76" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>129893356</v>
       </c>
       <c r="B77" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>129893368</v>
       </c>
       <c r="B78" t="n">
-        <v>90988</v>
+        <v>91005</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893306</v>
+        <v>129893334</v>
       </c>
       <c r="B79" t="n">
-        <v>79707</v>
+        <v>78847</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447282</v>
+        <v>447287</v>
       </c>
       <c r="R79" t="n">
-        <v>6804440</v>
+        <v>6804433</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8433,10 +8433,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893353</v>
+        <v>129893306</v>
       </c>
       <c r="B80" t="n">
-        <v>78845</v>
+        <v>79708</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8444,21 +8444,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8468,10 +8468,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447206</v>
+        <v>447282</v>
       </c>
       <c r="R80" t="n">
-        <v>6804417</v>
+        <v>6804440</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8530,10 +8530,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893395</v>
+        <v>129893353</v>
       </c>
       <c r="B81" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8541,21 +8541,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8565,10 +8565,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447137</v>
+        <v>447206</v>
       </c>
       <c r="R81" t="n">
-        <v>6804440</v>
+        <v>6804417</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8601,11 +8601,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8632,10 +8627,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893334</v>
+        <v>129893395</v>
       </c>
       <c r="B82" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8643,21 +8638,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8667,10 +8662,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447287</v>
+        <v>447137</v>
       </c>
       <c r="R82" t="n">
-        <v>6804433</v>
+        <v>6804440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8703,6 +8698,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8729,10 +8729,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893303</v>
+        <v>129893305</v>
       </c>
       <c r="B83" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447143</v>
+        <v>447170</v>
       </c>
       <c r="R83" t="n">
-        <v>6804414</v>
+        <v>6804401</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8826,10 +8826,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893397</v>
+        <v>129893303</v>
       </c>
       <c r="B84" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8837,21 +8837,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447191</v>
+        <v>447143</v>
       </c>
       <c r="R84" t="n">
-        <v>6804284</v>
+        <v>6804414</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8897,11 +8897,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8928,10 +8923,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893348</v>
+        <v>129893397</v>
       </c>
       <c r="B85" t="n">
-        <v>78845</v>
+        <v>79089</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8939,21 +8934,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8963,10 +8958,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447138</v>
+        <v>447191</v>
       </c>
       <c r="R85" t="n">
-        <v>6804553</v>
+        <v>6804284</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8999,6 +8994,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9025,10 +9025,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893305</v>
+        <v>129893348</v>
       </c>
       <c r="B86" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9036,21 +9036,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447170</v>
+        <v>447138</v>
       </c>
       <c r="R86" t="n">
-        <v>6804401</v>
+        <v>6804553</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9125,7 +9125,7 @@
         <v>129893392</v>
       </c>
       <c r="B87" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>129893405</v>
       </c>
       <c r="B88" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>129893307</v>
       </c>
       <c r="B89" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>129893360</v>
       </c>
       <c r="B90" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>129893399</v>
       </c>
       <c r="B91" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9612,45 +9612,53 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893351</v>
+        <v>129893316</v>
       </c>
       <c r="B92" t="n">
-        <v>78845</v>
+        <v>56930</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447129</v>
+        <v>447102</v>
       </c>
       <c r="R92" t="n">
-        <v>6804505</v>
+        <v>6804551</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9709,53 +9717,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893316</v>
+        <v>129893309</v>
       </c>
       <c r="B93" t="n">
-        <v>56930</v>
+        <v>79679</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447102</v>
+        <v>447247</v>
       </c>
       <c r="R93" t="n">
-        <v>6804551</v>
+        <v>6804552</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9814,10 +9814,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129893309</v>
+        <v>129893351</v>
       </c>
       <c r="B94" t="n">
-        <v>79678</v>
+        <v>78846</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9825,21 +9825,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447247</v>
+        <v>447129</v>
       </c>
       <c r="R94" t="n">
-        <v>6804552</v>
+        <v>6804505</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893407</v>
+        <v>129893323</v>
       </c>
       <c r="B95" t="n">
-        <v>79088</v>
+        <v>57737</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,34 +9922,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447258</v>
+        <v>447139</v>
       </c>
       <c r="R95" t="n">
-        <v>6804469</v>
+        <v>6804556</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10008,10 +10016,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129893323</v>
+        <v>129893407</v>
       </c>
       <c r="B96" t="n">
-        <v>57737</v>
+        <v>79089</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10019,42 +10027,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447139</v>
+        <v>447258</v>
       </c>
       <c r="R96" t="n">
-        <v>6804556</v>
+        <v>6804469</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10116,7 +10116,7 @@
         <v>129893332</v>
       </c>
       <c r="B97" t="n">
-        <v>78846</v>
+        <v>78847</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10213,7 +10213,7 @@
         <v>129893359</v>
       </c>
       <c r="B98" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10310,7 +10310,7 @@
         <v>129893350</v>
       </c>
       <c r="B99" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10407,7 +10407,7 @@
         <v>129893396</v>
       </c>
       <c r="B100" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>129893310</v>
       </c>
       <c r="B101" t="n">
-        <v>79678</v>
+        <v>79679</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10606,7 +10606,7 @@
         <v>129893344</v>
       </c>
       <c r="B102" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>129893357</v>
       </c>
       <c r="B103" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>129893301</v>
       </c>
       <c r="B104" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129893398</v>
+        <v>129893346</v>
       </c>
       <c r="B105" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447189</v>
+        <v>447088</v>
       </c>
       <c r="R105" t="n">
-        <v>6804301</v>
+        <v>6804609</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893346</v>
+        <v>129893299</v>
       </c>
       <c r="B106" t="n">
-        <v>78845</v>
+        <v>79708</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447088</v>
+        <v>447141</v>
       </c>
       <c r="R106" t="n">
-        <v>6804609</v>
+        <v>6804483</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893299</v>
+        <v>129893398</v>
       </c>
       <c r="B107" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447141</v>
+        <v>447189</v>
       </c>
       <c r="R107" t="n">
-        <v>6804483</v>
+        <v>6804301</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11185,10 +11185,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129893295</v>
+        <v>129893322</v>
       </c>
       <c r="B108" t="n">
-        <v>79707</v>
+        <v>57737</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11196,34 +11196,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>447085</v>
+        <v>447105</v>
       </c>
       <c r="R108" t="n">
-        <v>6804671</v>
+        <v>6804584</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11282,10 +11290,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893358</v>
+        <v>129893295</v>
       </c>
       <c r="B109" t="n">
-        <v>78845</v>
+        <v>79708</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11293,21 +11301,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11317,10 +11325,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447319</v>
+        <v>447085</v>
       </c>
       <c r="R109" t="n">
-        <v>6804349</v>
+        <v>6804671</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11379,10 +11387,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893352</v>
+        <v>129893358</v>
       </c>
       <c r="B110" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11414,10 +11422,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447146</v>
+        <v>447319</v>
       </c>
       <c r="R110" t="n">
-        <v>6804415</v>
+        <v>6804349</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11476,10 +11484,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893296</v>
+        <v>129893352</v>
       </c>
       <c r="B111" t="n">
-        <v>79707</v>
+        <v>78846</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,21 +11495,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11511,10 +11519,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447079</v>
+        <v>447146</v>
       </c>
       <c r="R111" t="n">
-        <v>6804660</v>
+        <v>6804415</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11573,10 +11581,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893322</v>
+        <v>129893296</v>
       </c>
       <c r="B112" t="n">
-        <v>57737</v>
+        <v>79708</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11584,42 +11592,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447105</v>
+        <v>447079</v>
       </c>
       <c r="R112" t="n">
-        <v>6804584</v>
+        <v>6804660</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893300</v>
+        <v>129893314</v>
       </c>
       <c r="B113" t="n">
-        <v>79707</v>
+        <v>57740</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,34 +11689,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447121</v>
+        <v>447227</v>
       </c>
       <c r="R113" t="n">
-        <v>6804435</v>
+        <v>6804586</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11775,10 +11783,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893394</v>
+        <v>129893300</v>
       </c>
       <c r="B114" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11786,21 +11794,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -11810,10 +11818,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447128</v>
+        <v>447121</v>
       </c>
       <c r="R114" t="n">
-        <v>6804516</v>
+        <v>6804435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11846,11 +11854,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -11877,10 +11880,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893308</v>
+        <v>129893394</v>
       </c>
       <c r="B115" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11888,21 +11891,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11912,10 +11915,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447248</v>
+        <v>447128</v>
       </c>
       <c r="R115" t="n">
-        <v>6804484</v>
+        <v>6804516</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11948,6 +11951,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11974,10 +11982,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893297</v>
+        <v>129893308</v>
       </c>
       <c r="B116" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -12009,10 +12017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447104</v>
+        <v>447248</v>
       </c>
       <c r="R116" t="n">
-        <v>6804519</v>
+        <v>6804484</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12071,10 +12079,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893314</v>
+        <v>129893297</v>
       </c>
       <c r="B117" t="n">
-        <v>57740</v>
+        <v>79708</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12082,42 +12090,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447227</v>
+        <v>447104</v>
       </c>
       <c r="R117" t="n">
-        <v>6804586</v>
+        <v>6804519</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12284,7 +12284,7 @@
         <v>129893302</v>
       </c>
       <c r="B119" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12381,7 +12381,7 @@
         <v>129893354</v>
       </c>
       <c r="B120" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12475,10 +12475,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129893333</v>
+        <v>129893401</v>
       </c>
       <c r="B121" t="n">
-        <v>78846</v>
+        <v>79089</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12486,21 +12486,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447284</v>
+        <v>447291</v>
       </c>
       <c r="R121" t="n">
-        <v>6804412</v>
+        <v>6804354</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12546,6 +12546,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12572,10 +12577,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893401</v>
+        <v>129893408</v>
       </c>
       <c r="B122" t="n">
-        <v>79088</v>
+        <v>79089</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12607,10 +12612,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447291</v>
+        <v>447247</v>
       </c>
       <c r="R122" t="n">
-        <v>6804354</v>
+        <v>6804486</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12643,11 +12648,6 @@
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -12674,10 +12674,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893408</v>
+        <v>129893304</v>
       </c>
       <c r="B123" t="n">
-        <v>79088</v>
+        <v>79708</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12685,21 +12685,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447247</v>
+        <v>447208</v>
       </c>
       <c r="R123" t="n">
-        <v>6804486</v>
+        <v>6804423</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12771,10 +12771,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129893304</v>
+        <v>129893406</v>
       </c>
       <c r="B124" t="n">
-        <v>79707</v>
+        <v>79089</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12782,21 +12782,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12806,10 +12806,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447208</v>
+        <v>447282</v>
       </c>
       <c r="R124" t="n">
-        <v>6804423</v>
+        <v>6804440</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12842,6 +12842,11 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12868,10 +12873,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893406</v>
+        <v>129893355</v>
       </c>
       <c r="B125" t="n">
-        <v>79088</v>
+        <v>78846</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12879,21 +12884,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12903,10 +12908,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447282</v>
+        <v>447175</v>
       </c>
       <c r="R125" t="n">
-        <v>6804440</v>
+        <v>6804401</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12939,11 +12944,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12970,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893355</v>
+        <v>129893333</v>
       </c>
       <c r="B126" t="n">
-        <v>78845</v>
+        <v>78847</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447175</v>
+        <v>447284</v>
       </c>
       <c r="R126" t="n">
-        <v>6804401</v>
+        <v>6804412</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13070,7 +13070,7 @@
         <v>129893349</v>
       </c>
       <c r="B127" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>129893298</v>
       </c>
       <c r="B128" t="n">
-        <v>79707</v>
+        <v>79708</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>129893345</v>
       </c>
       <c r="B129" t="n">
-        <v>78845</v>
+        <v>78846</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894044</v>
+        <v>129893971</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446959</v>
+        <v>447009</v>
       </c>
       <c r="R3" t="n">
-        <v>6804780</v>
+        <v>6804689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893971</v>
+        <v>129894044</v>
       </c>
       <c r="B4" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447009</v>
+        <v>446959</v>
       </c>
       <c r="R4" t="n">
-        <v>6804689</v>
+        <v>6804780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1269,45 +1269,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893974</v>
+        <v>129893963</v>
       </c>
       <c r="B8" t="n">
-        <v>78852</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447014</v>
+        <v>447084</v>
       </c>
       <c r="R8" t="n">
-        <v>6804644</v>
+        <v>6804507</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1348,6 +1357,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1366,7 +1376,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129893970</v>
+        <v>129893974</v>
       </c>
       <c r="B9" t="n">
         <v>78852</v>
@@ -1401,10 +1411,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>447006</v>
+        <v>447014</v>
       </c>
       <c r="R9" t="n">
-        <v>6804685</v>
+        <v>6804644</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1463,54 +1473,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893963</v>
+        <v>129893970</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>78852</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447084</v>
+        <v>447006</v>
       </c>
       <c r="R10" t="n">
-        <v>6804507</v>
+        <v>6804685</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1552,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -3256,7 +3256,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894029</v>
+        <v>129894047</v>
       </c>
       <c r="B28" t="n">
         <v>79095</v>
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447078</v>
+        <v>447264</v>
       </c>
       <c r="R28" t="n">
-        <v>6804574</v>
+        <v>6804394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3331,7 +3331,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3358,10 +3358,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893979</v>
+        <v>129893919</v>
       </c>
       <c r="B29" t="n">
-        <v>78852</v>
+        <v>79685</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3369,21 +3369,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447104</v>
+        <v>447260</v>
       </c>
       <c r="R29" t="n">
-        <v>6804432</v>
+        <v>6804349</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3455,10 +3455,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894047</v>
+        <v>129893935</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,34 +3466,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447264</v>
+        <v>447017</v>
       </c>
       <c r="R30" t="n">
-        <v>6804394</v>
+        <v>6804662</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3526,11 +3534,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3557,10 +3560,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893935</v>
+        <v>129894029</v>
       </c>
       <c r="B31" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3568,42 +3571,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447017</v>
+        <v>447078</v>
       </c>
       <c r="R31" t="n">
-        <v>6804662</v>
+        <v>6804574</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3636,6 +3631,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3662,10 +3662,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893919</v>
+        <v>129893979</v>
       </c>
       <c r="B32" t="n">
-        <v>79685</v>
+        <v>78852</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447260</v>
+        <v>447104</v>
       </c>
       <c r="R32" t="n">
-        <v>6804349</v>
+        <v>6804432</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893975</v>
+        <v>129893948</v>
       </c>
       <c r="B41" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>447017</v>
+        <v>446971</v>
       </c>
       <c r="R41" t="n">
-        <v>6804644</v>
+        <v>6804769</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129894027</v>
+        <v>129893975</v>
       </c>
       <c r="B42" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446979</v>
+        <v>447017</v>
       </c>
       <c r="R42" t="n">
-        <v>6804787</v>
+        <v>6804644</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129893983</v>
+        <v>129894027</v>
       </c>
       <c r="B43" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447195</v>
+        <v>446979</v>
       </c>
       <c r="R43" t="n">
-        <v>6804348</v>
+        <v>6804787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4840,10 +4840,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893948</v>
+        <v>129893983</v>
       </c>
       <c r="B44" t="n">
-        <v>78853</v>
+        <v>78852</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4851,21 +4851,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>446971</v>
+        <v>447195</v>
       </c>
       <c r="R44" t="n">
-        <v>6804769</v>
+        <v>6804348</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -8534,32 +8534,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893368</v>
+        <v>129893334</v>
       </c>
       <c r="B81" t="n">
-        <v>91021</v>
+        <v>78853</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8569,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447279</v>
+        <v>447287</v>
       </c>
       <c r="R81" t="n">
-        <v>6804380</v>
+        <v>6804433</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8613,7 +8613,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8632,32 +8631,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893334</v>
+        <v>129893368</v>
       </c>
       <c r="B82" t="n">
-        <v>78853</v>
+        <v>91021</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>5685</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8667,10 +8666,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447287</v>
+        <v>447279</v>
       </c>
       <c r="R82" t="n">
-        <v>6804433</v>
+        <v>6804380</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8711,6 +8710,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8826,10 +8826,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893397</v>
+        <v>129893348</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8837,21 +8837,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8861,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447191</v>
+        <v>447138</v>
       </c>
       <c r="R84" t="n">
-        <v>6804284</v>
+        <v>6804553</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8897,11 +8897,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8928,10 +8923,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893348</v>
+        <v>129893397</v>
       </c>
       <c r="B85" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8939,21 +8934,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8963,10 +8958,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447138</v>
+        <v>447191</v>
       </c>
       <c r="R85" t="n">
-        <v>6804553</v>
+        <v>6804284</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8999,6 +8994,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893407</v>
+        <v>129893332</v>
       </c>
       <c r="B95" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,21 +9922,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447258</v>
+        <v>447086</v>
       </c>
       <c r="R95" t="n">
-        <v>6804469</v>
+        <v>6804674</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129893332</v>
+        <v>129893407</v>
       </c>
       <c r="B97" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,21 +10124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10148,10 +10148,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447086</v>
+        <v>447258</v>
       </c>
       <c r="R97" t="n">
-        <v>6804674</v>
+        <v>6804469</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893310</v>
+        <v>129893350</v>
       </c>
       <c r="B98" t="n">
-        <v>79685</v>
+        <v>78852</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447280</v>
+        <v>447120</v>
       </c>
       <c r="R98" t="n">
-        <v>6804428</v>
+        <v>6804506</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10307,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893396</v>
+        <v>129893310</v>
       </c>
       <c r="B99" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10318,21 +10318,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10342,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447170</v>
+        <v>447280</v>
       </c>
       <c r="R99" t="n">
-        <v>6804344</v>
+        <v>6804428</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10378,11 +10378,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10409,10 +10404,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893359</v>
+        <v>129893396</v>
       </c>
       <c r="B100" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10420,21 +10415,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10444,10 +10439,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447276</v>
+        <v>447170</v>
       </c>
       <c r="R100" t="n">
-        <v>6804418</v>
+        <v>6804344</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10480,6 +10475,11 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10506,7 +10506,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893350</v>
+        <v>129893359</v>
       </c>
       <c r="B101" t="n">
         <v>78852</v>
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447120</v>
+        <v>447276</v>
       </c>
       <c r="R101" t="n">
-        <v>6804506</v>
+        <v>6804418</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129893398</v>
+        <v>129893346</v>
       </c>
       <c r="B105" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447189</v>
+        <v>447088</v>
       </c>
       <c r="R105" t="n">
-        <v>6804301</v>
+        <v>6804609</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893299</v>
+        <v>129893398</v>
       </c>
       <c r="B106" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447141</v>
+        <v>447189</v>
       </c>
       <c r="R106" t="n">
-        <v>6804483</v>
+        <v>6804301</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893346</v>
+        <v>129893299</v>
       </c>
       <c r="B107" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447088</v>
+        <v>447141</v>
       </c>
       <c r="R107" t="n">
-        <v>6804609</v>
+        <v>6804483</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893314</v>
+        <v>129893308</v>
       </c>
       <c r="B113" t="n">
-        <v>57741</v>
+        <v>79714</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,42 +11689,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447227</v>
+        <v>447248</v>
       </c>
       <c r="R113" t="n">
-        <v>6804586</v>
+        <v>6804484</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11783,7 +11775,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893308</v>
+        <v>129893300</v>
       </c>
       <c r="B114" t="n">
         <v>79714</v>
@@ -11818,10 +11810,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447248</v>
+        <v>447121</v>
       </c>
       <c r="R114" t="n">
-        <v>6804484</v>
+        <v>6804435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11880,10 +11872,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893300</v>
+        <v>129893314</v>
       </c>
       <c r="B115" t="n">
-        <v>79714</v>
+        <v>57741</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11891,34 +11883,42 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447121</v>
+        <v>447227</v>
       </c>
       <c r="R115" t="n">
-        <v>6804435</v>
+        <v>6804586</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12868,10 +12868,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893333</v>
+        <v>129893401</v>
       </c>
       <c r="B125" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12879,21 +12879,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447284</v>
+        <v>447291</v>
       </c>
       <c r="R125" t="n">
-        <v>6804412</v>
+        <v>6804354</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12939,6 +12939,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12965,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893401</v>
+        <v>129893333</v>
       </c>
       <c r="B126" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12976,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13000,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447291</v>
+        <v>447284</v>
       </c>
       <c r="R126" t="n">
-        <v>6804354</v>
+        <v>6804412</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13036,11 +13041,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -780,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129893971</v>
+        <v>129894044</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +791,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447009</v>
+        <v>446959</v>
       </c>
       <c r="R3" t="n">
-        <v>6804689</v>
+        <v>6804780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894044</v>
+        <v>129893971</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446959</v>
+        <v>447009</v>
       </c>
       <c r="R4" t="n">
-        <v>6804780</v>
+        <v>6804689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -2163,53 +2163,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893923</v>
+        <v>129894043</v>
       </c>
       <c r="B17" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447079</v>
+        <v>447247</v>
       </c>
       <c r="R17" t="n">
-        <v>6804592</v>
+        <v>6804534</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,45 +2260,53 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894043</v>
+        <v>129893923</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>56931</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447247</v>
+        <v>447079</v>
       </c>
       <c r="R18" t="n">
-        <v>6804534</v>
+        <v>6804592</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129894028</v>
+        <v>129893955</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447038</v>
+        <v>447237</v>
       </c>
       <c r="R33" t="n">
-        <v>6804585</v>
+        <v>6804433</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3856,10 +3856,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893955</v>
+        <v>129893920</v>
       </c>
       <c r="B34" t="n">
-        <v>78853</v>
+        <v>79685</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3867,21 +3867,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,10 +3891,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447237</v>
+        <v>447249</v>
       </c>
       <c r="R34" t="n">
-        <v>6804433</v>
+        <v>6804413</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,10 +3953,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129893920</v>
+        <v>129894046</v>
       </c>
       <c r="B35" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3964,34 +3964,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447249</v>
+        <v>447137</v>
       </c>
       <c r="R35" t="n">
-        <v>6804413</v>
+        <v>6804362</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4026,12 +4029,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4050,7 +4059,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894046</v>
+        <v>129894034</v>
       </c>
       <c r="B36" t="n">
         <v>79095</v>
@@ -4079,19 +4088,16 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447137</v>
+        <v>447146</v>
       </c>
       <c r="R36" t="n">
-        <v>6804362</v>
+        <v>6804328</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4126,18 +4132,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4156,7 +4156,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894034</v>
+        <v>129894028</v>
       </c>
       <c r="B37" t="n">
         <v>79095</v>
@@ -4191,10 +4191,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447146</v>
+        <v>447038</v>
       </c>
       <c r="R37" t="n">
-        <v>6804328</v>
+        <v>6804585</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894035</v>
+        <v>129893933</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,34 +4948,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447155</v>
+        <v>447075</v>
       </c>
       <c r="R45" t="n">
-        <v>6804339</v>
+        <v>6804732</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,10 +5042,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893969</v>
+        <v>129893937</v>
       </c>
       <c r="B46" t="n">
-        <v>78852</v>
+        <v>57738</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5045,34 +5053,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447006</v>
+        <v>447059</v>
       </c>
       <c r="R46" t="n">
-        <v>6804728</v>
+        <v>6804587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,10 +5147,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893980</v>
+        <v>129893936</v>
       </c>
       <c r="B47" t="n">
-        <v>78852</v>
+        <v>57738</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,34 +5158,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447136</v>
+        <v>447012</v>
       </c>
       <c r="R47" t="n">
-        <v>6804407</v>
+        <v>6804645</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5228,7 +5252,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894041</v>
+        <v>129894035</v>
       </c>
       <c r="B48" t="n">
         <v>79095</v>
@@ -5263,10 +5287,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447242</v>
+        <v>447155</v>
       </c>
       <c r="R48" t="n">
-        <v>6804443</v>
+        <v>6804339</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5325,10 +5349,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893933</v>
+        <v>129893969</v>
       </c>
       <c r="B49" t="n">
-        <v>57738</v>
+        <v>78852</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5336,42 +5360,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447075</v>
+        <v>447006</v>
       </c>
       <c r="R49" t="n">
-        <v>6804732</v>
+        <v>6804728</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5430,10 +5446,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893937</v>
+        <v>129893980</v>
       </c>
       <c r="B50" t="n">
-        <v>57738</v>
+        <v>78852</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5441,42 +5457,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447059</v>
+        <v>447136</v>
       </c>
       <c r="R50" t="n">
-        <v>6804587</v>
+        <v>6804407</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5535,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893936</v>
+        <v>129894041</v>
       </c>
       <c r="B51" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5546,42 +5554,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447012</v>
+        <v>447242</v>
       </c>
       <c r="R51" t="n">
-        <v>6804645</v>
+        <v>6804443</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893393</v>
+        <v>129893315</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7945,34 +7945,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447110</v>
+        <v>447115</v>
       </c>
       <c r="R75" t="n">
-        <v>6804630</v>
+        <v>6804531</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8005,11 +8013,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8036,10 +8039,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893356</v>
+        <v>129893393</v>
       </c>
       <c r="B76" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8047,21 +8050,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8071,10 +8074,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447165</v>
+        <v>447110</v>
       </c>
       <c r="R76" t="n">
-        <v>6804365</v>
+        <v>6804630</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8107,6 +8110,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8133,10 +8141,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893315</v>
+        <v>129893356</v>
       </c>
       <c r="B77" t="n">
-        <v>57741</v>
+        <v>78852</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8144,42 +8152,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447115</v>
+        <v>447165</v>
       </c>
       <c r="R77" t="n">
-        <v>6804531</v>
+        <v>6804365</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8238,32 +8238,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893353</v>
+        <v>129893368</v>
       </c>
       <c r="B78" t="n">
-        <v>78852</v>
+        <v>91021</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>5685</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447206</v>
+        <v>447279</v>
       </c>
       <c r="R78" t="n">
-        <v>6804417</v>
+        <v>6804380</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8317,6 +8317,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8335,10 +8336,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893306</v>
+        <v>129893353</v>
       </c>
       <c r="B79" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8346,21 +8347,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8370,10 +8371,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447282</v>
+        <v>447206</v>
       </c>
       <c r="R79" t="n">
-        <v>6804440</v>
+        <v>6804417</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8432,10 +8433,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893395</v>
+        <v>129893306</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8443,21 +8444,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8467,7 +8468,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447137</v>
+        <v>447282</v>
       </c>
       <c r="R80" t="n">
         <v>6804440</v>
@@ -8503,11 +8504,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8534,10 +8530,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893334</v>
+        <v>129893395</v>
       </c>
       <c r="B81" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8545,21 +8541,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8569,10 +8565,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447287</v>
+        <v>447137</v>
       </c>
       <c r="R81" t="n">
-        <v>6804433</v>
+        <v>6804440</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8605,6 +8601,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8631,32 +8632,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893368</v>
+        <v>129893334</v>
       </c>
       <c r="B82" t="n">
-        <v>91021</v>
+        <v>78853</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8666,10 +8667,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447279</v>
+        <v>447287</v>
       </c>
       <c r="R82" t="n">
-        <v>6804380</v>
+        <v>6804433</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8710,7 +8711,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893332</v>
+        <v>129893407</v>
       </c>
       <c r="B95" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,21 +9922,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9946,10 +9946,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447086</v>
+        <v>447258</v>
       </c>
       <c r="R95" t="n">
-        <v>6804674</v>
+        <v>6804469</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10113,10 +10113,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129893407</v>
+        <v>129893332</v>
       </c>
       <c r="B97" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10124,21 +10124,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10148,10 +10148,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>447258</v>
+        <v>447086</v>
       </c>
       <c r="R97" t="n">
-        <v>6804469</v>
+        <v>6804674</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10894,10 +10894,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129893346</v>
+        <v>129893398</v>
       </c>
       <c r="B105" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10905,21 +10905,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10929,10 +10929,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>447088</v>
+        <v>447189</v>
       </c>
       <c r="R105" t="n">
-        <v>6804609</v>
+        <v>6804301</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893398</v>
+        <v>129893299</v>
       </c>
       <c r="B106" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447189</v>
+        <v>447141</v>
       </c>
       <c r="R106" t="n">
-        <v>6804301</v>
+        <v>6804483</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893299</v>
+        <v>129893346</v>
       </c>
       <c r="B107" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447141</v>
+        <v>447088</v>
       </c>
       <c r="R107" t="n">
-        <v>6804483</v>
+        <v>6804609</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893308</v>
+        <v>129893314</v>
       </c>
       <c r="B113" t="n">
-        <v>79714</v>
+        <v>57741</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,34 +11689,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447248</v>
+        <v>447227</v>
       </c>
       <c r="R113" t="n">
-        <v>6804484</v>
+        <v>6804586</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11775,7 +11783,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893300</v>
+        <v>129893308</v>
       </c>
       <c r="B114" t="n">
         <v>79714</v>
@@ -11810,10 +11818,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447121</v>
+        <v>447248</v>
       </c>
       <c r="R114" t="n">
-        <v>6804435</v>
+        <v>6804484</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11872,10 +11880,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893314</v>
+        <v>129893300</v>
       </c>
       <c r="B115" t="n">
-        <v>57741</v>
+        <v>79714</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11883,42 +11891,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447227</v>
+        <v>447121</v>
       </c>
       <c r="R115" t="n">
-        <v>6804586</v>
+        <v>6804435</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12868,10 +12868,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893401</v>
+        <v>129893333</v>
       </c>
       <c r="B125" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12879,21 +12879,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12903,10 +12903,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447291</v>
+        <v>447284</v>
       </c>
       <c r="R125" t="n">
-        <v>6804354</v>
+        <v>6804412</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12939,11 +12939,6 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12970,10 +12965,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893333</v>
+        <v>129893401</v>
       </c>
       <c r="B126" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12981,21 +12976,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13005,10 +13000,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447284</v>
+        <v>447291</v>
       </c>
       <c r="R126" t="n">
-        <v>6804412</v>
+        <v>6804354</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13041,6 +13036,11 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD126" t="b">

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893939</v>
+        <v>129893913</v>
       </c>
       <c r="B2" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447133</v>
+        <v>447127</v>
       </c>
       <c r="R2" t="n">
-        <v>6804362</v>
+        <v>6804438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -780,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129894044</v>
+        <v>129893971</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -791,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -815,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>446959</v>
+        <v>447009</v>
       </c>
       <c r="R3" t="n">
-        <v>6804780</v>
+        <v>6804689</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129893971</v>
+        <v>129894044</v>
       </c>
       <c r="B4" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -888,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -912,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>447009</v>
+        <v>446959</v>
       </c>
       <c r="R4" t="n">
-        <v>6804689</v>
+        <v>6804780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129893913</v>
+        <v>129893939</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -985,34 +977,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>447127</v>
+        <v>447133</v>
       </c>
       <c r="R5" t="n">
-        <v>6804438</v>
+        <v>6804362</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1269,54 +1269,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129893963</v>
+        <v>129893970</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>78852</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>447084</v>
+        <v>447006</v>
       </c>
       <c r="R8" t="n">
-        <v>6804507</v>
+        <v>6804685</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1357,7 +1348,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1473,45 +1463,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129893970</v>
+        <v>129893963</v>
       </c>
       <c r="B10" t="n">
-        <v>78852</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>447006</v>
+        <v>447084</v>
       </c>
       <c r="R10" t="n">
-        <v>6804685</v>
+        <v>6804507</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,6 +1551,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B11" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R11" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,11 +1641,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1672,10 +1667,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B12" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1683,21 +1678,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1707,10 +1702,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R12" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,6 +1738,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894050</v>
+        <v>129894023</v>
       </c>
       <c r="B13" t="n">
-        <v>78102</v>
+        <v>79095</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447251</v>
+        <v>447120</v>
       </c>
       <c r="R13" t="n">
-        <v>6804480</v>
+        <v>6804670</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,13 +1842,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1867,10 +1871,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894023</v>
+        <v>129894050</v>
       </c>
       <c r="B14" t="n">
-        <v>79095</v>
+        <v>78102</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1878,21 +1882,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1902,10 +1906,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447120</v>
+        <v>447251</v>
       </c>
       <c r="R14" t="n">
-        <v>6804670</v>
+        <v>6804480</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,17 +1944,13 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2163,10 +2163,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129894043</v>
+        <v>129893973</v>
       </c>
       <c r="B17" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2174,21 +2174,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2198,10 +2198,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447247</v>
+        <v>447018</v>
       </c>
       <c r="R17" t="n">
-        <v>6804534</v>
+        <v>6804657</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,53 +2260,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129893923</v>
+        <v>129894043</v>
       </c>
       <c r="B18" t="n">
-        <v>56931</v>
+        <v>79095</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447079</v>
+        <v>447247</v>
       </c>
       <c r="R18" t="n">
-        <v>6804592</v>
+        <v>6804534</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2365,45 +2357,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893973</v>
+        <v>129893923</v>
       </c>
       <c r="B19" t="n">
-        <v>78852</v>
+        <v>56931</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447018</v>
+        <v>447079</v>
       </c>
       <c r="R19" t="n">
-        <v>6804657</v>
+        <v>6804592</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2462,7 +2462,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129894039</v>
+        <v>129894042</v>
       </c>
       <c r="B20" t="n">
         <v>79095</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>447226</v>
+        <v>447262</v>
       </c>
       <c r="R20" t="n">
-        <v>6804354</v>
+        <v>6804466</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129894042</v>
+        <v>129894039</v>
       </c>
       <c r="B21" t="n">
         <v>79095</v>
@@ -2594,10 +2594,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>447262</v>
+        <v>447226</v>
       </c>
       <c r="R21" t="n">
-        <v>6804466</v>
+        <v>6804354</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2656,45 +2656,53 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893976</v>
+        <v>129893945</v>
       </c>
       <c r="B22" t="n">
-        <v>78852</v>
+        <v>56934</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>102613</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447071</v>
+        <v>447140</v>
       </c>
       <c r="R22" t="n">
-        <v>6804595</v>
+        <v>6804358</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2850,53 +2858,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893945</v>
+        <v>129893976</v>
       </c>
       <c r="B24" t="n">
-        <v>56934</v>
+        <v>78852</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102613</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447140</v>
+        <v>447071</v>
       </c>
       <c r="R24" t="n">
-        <v>6804358</v>
+        <v>6804595</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129894047</v>
+        <v>129893935</v>
       </c>
       <c r="B28" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,34 +3267,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447264</v>
+        <v>447017</v>
       </c>
       <c r="R28" t="n">
-        <v>6804394</v>
+        <v>6804662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,11 +3335,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3358,10 +3361,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129893919</v>
+        <v>129894047</v>
       </c>
       <c r="B29" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3369,21 +3372,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3393,10 +3396,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447260</v>
+        <v>447264</v>
       </c>
       <c r="R29" t="n">
-        <v>6804349</v>
+        <v>6804394</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3429,6 +3432,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3455,10 +3463,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129893935</v>
+        <v>129894029</v>
       </c>
       <c r="B30" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3466,42 +3474,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447017</v>
+        <v>447078</v>
       </c>
       <c r="R30" t="n">
-        <v>6804662</v>
+        <v>6804574</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3534,6 +3534,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3560,10 +3565,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129894029</v>
+        <v>129893979</v>
       </c>
       <c r="B31" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3571,21 +3576,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3595,10 +3600,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447078</v>
+        <v>447104</v>
       </c>
       <c r="R31" t="n">
-        <v>6804574</v>
+        <v>6804432</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3631,11 +3636,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3662,10 +3662,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893979</v>
+        <v>129893919</v>
       </c>
       <c r="B32" t="n">
-        <v>78852</v>
+        <v>79685</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3673,21 +3673,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3697,10 +3697,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447104</v>
+        <v>447260</v>
       </c>
       <c r="R32" t="n">
-        <v>6804432</v>
+        <v>6804349</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3759,10 +3759,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129893955</v>
+        <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3770,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3794,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>447237</v>
+        <v>447019</v>
       </c>
       <c r="R33" t="n">
-        <v>6804433</v>
+        <v>6804831</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3830,6 +3830,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3856,10 +3861,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129893920</v>
+        <v>129894028</v>
       </c>
       <c r="B34" t="n">
-        <v>79685</v>
+        <v>79095</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3867,21 +3872,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3891,10 +3896,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>447249</v>
+        <v>447038</v>
       </c>
       <c r="R34" t="n">
-        <v>6804413</v>
+        <v>6804585</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3953,7 +3958,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129894046</v>
+        <v>129894036</v>
       </c>
       <c r="B35" t="n">
         <v>79095</v>
@@ -3982,19 +3987,16 @@
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>447137</v>
+        <v>447177</v>
       </c>
       <c r="R35" t="n">
-        <v>6804362</v>
+        <v>6804353</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4029,18 +4031,12 @@
           <t>2025-11-28</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m.</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4059,7 +4055,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129894034</v>
+        <v>129894046</v>
       </c>
       <c r="B36" t="n">
         <v>79095</v>
@@ -4088,16 +4084,19 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>447146</v>
+        <v>447137</v>
       </c>
       <c r="R36" t="n">
-        <v>6804328</v>
+        <v>6804362</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4132,12 +4131,18 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m.</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4156,7 +4161,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129894028</v>
+        <v>129894034</v>
       </c>
       <c r="B37" t="n">
         <v>79095</v>
@@ -4191,10 +4196,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>447038</v>
+        <v>447146</v>
       </c>
       <c r="R37" t="n">
-        <v>6804585</v>
+        <v>6804328</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4253,10 +4258,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129894036</v>
+        <v>129893955</v>
       </c>
       <c r="B38" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4264,21 +4269,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4288,10 +4293,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>447177</v>
+        <v>447237</v>
       </c>
       <c r="R38" t="n">
-        <v>6804353</v>
+        <v>6804433</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4350,10 +4355,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129894026</v>
+        <v>129893920</v>
       </c>
       <c r="B39" t="n">
-        <v>79095</v>
+        <v>79685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4361,21 +4366,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4385,10 +4390,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>447019</v>
+        <v>447249</v>
       </c>
       <c r="R39" t="n">
-        <v>6804831</v>
+        <v>6804413</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4421,11 +4426,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129893948</v>
+        <v>129894027</v>
       </c>
       <c r="B41" t="n">
-        <v>78853</v>
+        <v>79095</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446971</v>
+        <v>446979</v>
       </c>
       <c r="R41" t="n">
-        <v>6804769</v>
+        <v>6804787</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893975</v>
+        <v>129893948</v>
       </c>
       <c r="B42" t="n">
-        <v>78852</v>
+        <v>78853</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>447017</v>
+        <v>446971</v>
       </c>
       <c r="R42" t="n">
-        <v>6804644</v>
+        <v>6804769</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129894027</v>
+        <v>129893983</v>
       </c>
       <c r="B43" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>446979</v>
+        <v>447195</v>
       </c>
       <c r="R43" t="n">
-        <v>6804787</v>
+        <v>6804348</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4840,7 +4840,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129893983</v>
+        <v>129893975</v>
       </c>
       <c r="B44" t="n">
         <v>78852</v>
@@ -4875,10 +4875,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>447195</v>
+        <v>447017</v>
       </c>
       <c r="R44" t="n">
-        <v>6804348</v>
+        <v>6804644</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129893933</v>
+        <v>129894041</v>
       </c>
       <c r="B45" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,42 +4948,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447075</v>
+        <v>447242</v>
       </c>
       <c r="R45" t="n">
-        <v>6804732</v>
+        <v>6804443</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5042,10 +5034,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129893937</v>
+        <v>129894035</v>
       </c>
       <c r="B46" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5053,42 +5045,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447059</v>
+        <v>447155</v>
       </c>
       <c r="R46" t="n">
-        <v>6804587</v>
+        <v>6804339</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5147,7 +5131,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893936</v>
+        <v>129893933</v>
       </c>
       <c r="B47" t="n">
         <v>57738</v>
@@ -5190,10 +5174,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447012</v>
+        <v>447075</v>
       </c>
       <c r="R47" t="n">
-        <v>6804645</v>
+        <v>6804732</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5252,10 +5236,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129894035</v>
+        <v>129893937</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5263,34 +5247,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447155</v>
+        <v>447059</v>
       </c>
       <c r="R48" t="n">
-        <v>6804339</v>
+        <v>6804587</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5349,10 +5341,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893969</v>
+        <v>129893936</v>
       </c>
       <c r="B49" t="n">
-        <v>78852</v>
+        <v>57738</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5360,34 +5352,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447006</v>
+        <v>447012</v>
       </c>
       <c r="R49" t="n">
-        <v>6804728</v>
+        <v>6804645</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5543,10 +5543,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129894041</v>
+        <v>129893969</v>
       </c>
       <c r="B51" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,21 +5554,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447242</v>
+        <v>447006</v>
       </c>
       <c r="R51" t="n">
-        <v>6804443</v>
+        <v>6804728</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6353,7 +6353,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893967</v>
+        <v>129893968</v>
       </c>
       <c r="B59" t="n">
         <v>78852</v>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>447209</v>
+        <v>446972</v>
       </c>
       <c r="R59" t="n">
-        <v>6804576</v>
+        <v>6804770</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,7 +6450,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893968</v>
+        <v>129893967</v>
       </c>
       <c r="B60" t="n">
         <v>78852</v>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>446972</v>
+        <v>447209</v>
       </c>
       <c r="R60" t="n">
-        <v>6804770</v>
+        <v>6804576</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6547,10 +6547,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893950</v>
+        <v>129893934</v>
       </c>
       <c r="B61" t="n">
-        <v>78853</v>
+        <v>57738</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6558,34 +6558,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447015</v>
+        <v>447006</v>
       </c>
       <c r="R61" t="n">
-        <v>6804655</v>
+        <v>6804684</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6644,10 +6652,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129893934</v>
+        <v>129893950</v>
       </c>
       <c r="B62" t="n">
-        <v>57738</v>
+        <v>78853</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6655,42 +6663,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447006</v>
+        <v>447015</v>
       </c>
       <c r="R62" t="n">
-        <v>6804684</v>
+        <v>6804655</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893914</v>
+        <v>129893952</v>
       </c>
       <c r="B63" t="n">
-        <v>79714</v>
+        <v>78853</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447244</v>
+        <v>447138</v>
       </c>
       <c r="R63" t="n">
-        <v>6804447</v>
+        <v>6804405</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893912</v>
+        <v>129893914</v>
       </c>
       <c r="B65" t="n">
         <v>79714</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447082</v>
+        <v>447244</v>
       </c>
       <c r="R65" t="n">
-        <v>6804551</v>
+        <v>6804447</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893982</v>
+        <v>129893912</v>
       </c>
       <c r="B66" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447163</v>
+        <v>447082</v>
       </c>
       <c r="R66" t="n">
-        <v>6804342</v>
+        <v>6804551</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893921</v>
+        <v>129893982</v>
       </c>
       <c r="B67" t="n">
-        <v>57741</v>
+        <v>78852</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,42 +7148,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447004</v>
+        <v>447163</v>
       </c>
       <c r="R67" t="n">
-        <v>6804712</v>
+        <v>6804342</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7242,10 +7234,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893952</v>
+        <v>129893921</v>
       </c>
       <c r="B68" t="n">
-        <v>78853</v>
+        <v>57741</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7253,34 +7245,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447138</v>
+        <v>447004</v>
       </c>
       <c r="R68" t="n">
-        <v>6804405</v>
+        <v>6804712</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7541,7 +7541,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129893404</v>
+        <v>129893402</v>
       </c>
       <c r="B71" t="n">
         <v>79095</v>
@@ -7576,10 +7576,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>447286</v>
+        <v>447287</v>
       </c>
       <c r="R71" t="n">
-        <v>6804416</v>
+        <v>6804380</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7638,7 +7638,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129893402</v>
+        <v>129893404</v>
       </c>
       <c r="B72" t="n">
         <v>79095</v>
@@ -7673,10 +7673,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>447287</v>
+        <v>447286</v>
       </c>
       <c r="R72" t="n">
-        <v>6804380</v>
+        <v>6804416</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7934,10 +7934,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129893315</v>
+        <v>129893393</v>
       </c>
       <c r="B75" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7945,42 +7945,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>447115</v>
+        <v>447110</v>
       </c>
       <c r="R75" t="n">
-        <v>6804531</v>
+        <v>6804630</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8013,6 +8005,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8039,10 +8036,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129893393</v>
+        <v>129893356</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8050,21 +8047,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8074,10 +8071,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>447110</v>
+        <v>447165</v>
       </c>
       <c r="R76" t="n">
-        <v>6804630</v>
+        <v>6804365</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8110,11 +8107,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8141,10 +8133,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129893356</v>
+        <v>129893315</v>
       </c>
       <c r="B77" t="n">
-        <v>78852</v>
+        <v>57741</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8152,34 +8144,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>447165</v>
+        <v>447115</v>
       </c>
       <c r="R77" t="n">
-        <v>6804365</v>
+        <v>6804531</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8241,7 +8241,7 @@
         <v>129893368</v>
       </c>
       <c r="B78" t="n">
-        <v>91021</v>
+        <v>91023</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8336,10 +8336,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893353</v>
+        <v>129893395</v>
       </c>
       <c r="B79" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8347,21 +8347,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8371,10 +8371,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447206</v>
+        <v>447137</v>
       </c>
       <c r="R79" t="n">
-        <v>6804417</v>
+        <v>6804440</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8407,6 +8407,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8530,10 +8535,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129893395</v>
+        <v>129893353</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8541,21 +8546,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8565,10 +8570,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>447137</v>
+        <v>447206</v>
       </c>
       <c r="R81" t="n">
-        <v>6804440</v>
+        <v>6804417</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8601,11 +8606,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8729,10 +8729,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893305</v>
+        <v>129893397</v>
       </c>
       <c r="B83" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447170</v>
+        <v>447191</v>
       </c>
       <c r="R83" t="n">
-        <v>6804401</v>
+        <v>6804284</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8800,6 +8800,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8826,10 +8831,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893348</v>
+        <v>129893303</v>
       </c>
       <c r="B84" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8837,21 +8842,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8861,10 +8866,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447138</v>
+        <v>447143</v>
       </c>
       <c r="R84" t="n">
-        <v>6804553</v>
+        <v>6804414</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8923,10 +8928,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>129893397</v>
+        <v>129893348</v>
       </c>
       <c r="B85" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8934,21 +8939,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8958,10 +8963,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>447191</v>
+        <v>447138</v>
       </c>
       <c r="R85" t="n">
-        <v>6804284</v>
+        <v>6804553</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8994,11 +8999,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9025,7 +9025,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129893303</v>
+        <v>129893305</v>
       </c>
       <c r="B86" t="n">
         <v>79714</v>
@@ -9060,10 +9060,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>447143</v>
+        <v>447170</v>
       </c>
       <c r="R86" t="n">
-        <v>6804414</v>
+        <v>6804401</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9224,10 +9224,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>129893360</v>
+        <v>129893405</v>
       </c>
       <c r="B88" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9235,21 +9235,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9259,10 +9259,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>447286</v>
+        <v>447280</v>
       </c>
       <c r="R88" t="n">
-        <v>6804433</v>
+        <v>6804429</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893405</v>
+        <v>129893307</v>
       </c>
       <c r="B90" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9429,21 +9429,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447280</v>
+        <v>447271</v>
       </c>
       <c r="R90" t="n">
-        <v>6804429</v>
+        <v>6804458</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9515,10 +9515,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893307</v>
+        <v>129893360</v>
       </c>
       <c r="B91" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9526,21 +9526,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447271</v>
+        <v>447286</v>
       </c>
       <c r="R91" t="n">
-        <v>6804458</v>
+        <v>6804433</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9709,45 +9709,53 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129893309</v>
+        <v>129893316</v>
       </c>
       <c r="B93" t="n">
-        <v>79685</v>
+        <v>56931</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>447247</v>
+        <v>447102</v>
       </c>
       <c r="R93" t="n">
-        <v>6804552</v>
+        <v>6804551</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9806,53 +9814,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129893316</v>
+        <v>129893309</v>
       </c>
       <c r="B94" t="n">
-        <v>56931</v>
+        <v>79685</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447102</v>
+        <v>447247</v>
       </c>
       <c r="R94" t="n">
-        <v>6804551</v>
+        <v>6804552</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9911,10 +9911,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129893407</v>
+        <v>129893323</v>
       </c>
       <c r="B95" t="n">
-        <v>79095</v>
+        <v>57738</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9922,34 +9922,42 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>447258</v>
+        <v>447139</v>
       </c>
       <c r="R95" t="n">
-        <v>6804469</v>
+        <v>6804556</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10008,10 +10016,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129893323</v>
+        <v>129893407</v>
       </c>
       <c r="B96" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10019,42 +10027,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>447139</v>
+        <v>447258</v>
       </c>
       <c r="R96" t="n">
-        <v>6804556</v>
+        <v>6804469</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893350</v>
+        <v>129893396</v>
       </c>
       <c r="B98" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447120</v>
+        <v>447170</v>
       </c>
       <c r="R98" t="n">
-        <v>6804506</v>
+        <v>6804344</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10281,6 +10281,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10307,10 +10312,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893310</v>
+        <v>129893359</v>
       </c>
       <c r="B99" t="n">
-        <v>79685</v>
+        <v>78852</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10318,21 +10323,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10342,10 +10347,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447280</v>
+        <v>447276</v>
       </c>
       <c r="R99" t="n">
-        <v>6804428</v>
+        <v>6804418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10404,10 +10409,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129893396</v>
+        <v>129893350</v>
       </c>
       <c r="B100" t="n">
-        <v>79095</v>
+        <v>78852</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10415,21 +10420,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10439,10 +10444,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>447170</v>
+        <v>447120</v>
       </c>
       <c r="R100" t="n">
-        <v>6804344</v>
+        <v>6804506</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10475,11 +10480,6 @@
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10506,10 +10506,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893359</v>
+        <v>129893310</v>
       </c>
       <c r="B101" t="n">
-        <v>78852</v>
+        <v>79685</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10517,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10541,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447276</v>
+        <v>447280</v>
       </c>
       <c r="R101" t="n">
-        <v>6804418</v>
+        <v>6804428</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10603,10 +10603,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129893301</v>
+        <v>129893344</v>
       </c>
       <c r="B102" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10614,21 +10614,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10638,10 +10638,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>447134</v>
+        <v>447173</v>
       </c>
       <c r="R102" t="n">
-        <v>6804438</v>
+        <v>6804600</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10797,10 +10797,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>129893344</v>
+        <v>129893301</v>
       </c>
       <c r="B104" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10808,21 +10808,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10832,10 +10832,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>447173</v>
+        <v>447134</v>
       </c>
       <c r="R104" t="n">
-        <v>6804600</v>
+        <v>6804438</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10991,10 +10991,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>129893299</v>
+        <v>129893346</v>
       </c>
       <c r="B106" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11002,21 +11002,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11026,10 +11026,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>447141</v>
+        <v>447088</v>
       </c>
       <c r="R106" t="n">
-        <v>6804483</v>
+        <v>6804609</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11088,10 +11088,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129893346</v>
+        <v>129893299</v>
       </c>
       <c r="B107" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11099,21 +11099,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11123,10 +11123,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>447088</v>
+        <v>447141</v>
       </c>
       <c r="R107" t="n">
-        <v>6804609</v>
+        <v>6804483</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11282,7 +11282,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129893352</v>
+        <v>129893358</v>
       </c>
       <c r="B109" t="n">
         <v>78852</v>
@@ -11317,10 +11317,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>447146</v>
+        <v>447319</v>
       </c>
       <c r="R109" t="n">
-        <v>6804415</v>
+        <v>6804349</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11379,10 +11379,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893296</v>
+        <v>129893352</v>
       </c>
       <c r="B110" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11390,21 +11390,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11414,10 +11414,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447079</v>
+        <v>447146</v>
       </c>
       <c r="R110" t="n">
-        <v>6804660</v>
+        <v>6804415</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11476,10 +11476,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893358</v>
+        <v>129893296</v>
       </c>
       <c r="B111" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,21 +11487,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11511,10 +11511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447319</v>
+        <v>447079</v>
       </c>
       <c r="R111" t="n">
-        <v>6804349</v>
+        <v>6804660</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893314</v>
+        <v>129893300</v>
       </c>
       <c r="B113" t="n">
-        <v>57741</v>
+        <v>79714</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,42 +11689,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447227</v>
+        <v>447121</v>
       </c>
       <c r="R113" t="n">
-        <v>6804586</v>
+        <v>6804435</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11880,7 +11872,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893300</v>
+        <v>129893297</v>
       </c>
       <c r="B115" t="n">
         <v>79714</v>
@@ -11915,10 +11907,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447121</v>
+        <v>447104</v>
       </c>
       <c r="R115" t="n">
-        <v>6804435</v>
+        <v>6804519</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12079,10 +12071,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893297</v>
+        <v>129893314</v>
       </c>
       <c r="B117" t="n">
-        <v>79714</v>
+        <v>57741</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12090,34 +12082,42 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447104</v>
+        <v>447227</v>
       </c>
       <c r="R117" t="n">
-        <v>6804519</v>
+        <v>6804586</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12176,10 +12176,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129893325</v>
+        <v>129893302</v>
       </c>
       <c r="B118" t="n">
-        <v>57738</v>
+        <v>79714</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12187,42 +12187,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>447201</v>
+        <v>447140</v>
       </c>
       <c r="R118" t="n">
-        <v>6804314</v>
+        <v>6804436</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12378,10 +12370,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893302</v>
+        <v>129893325</v>
       </c>
       <c r="B120" t="n">
-        <v>79714</v>
+        <v>57738</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12389,34 +12381,42 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447140</v>
+        <v>447201</v>
       </c>
       <c r="R120" t="n">
-        <v>6804436</v>
+        <v>6804314</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12475,7 +12475,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>129893408</v>
+        <v>129893401</v>
       </c>
       <c r="B121" t="n">
         <v>79095</v>
@@ -12510,10 +12510,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>447247</v>
+        <v>447291</v>
       </c>
       <c r="R121" t="n">
-        <v>6804486</v>
+        <v>6804354</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12546,6 +12546,11 @@
       <c r="AA121" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -12572,10 +12577,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129893304</v>
+        <v>129893408</v>
       </c>
       <c r="B122" t="n">
-        <v>79714</v>
+        <v>79095</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12583,21 +12588,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12607,10 +12612,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>447208</v>
+        <v>447247</v>
       </c>
       <c r="R122" t="n">
-        <v>6804423</v>
+        <v>6804486</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12669,10 +12674,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893355</v>
+        <v>129893406</v>
       </c>
       <c r="B123" t="n">
-        <v>78852</v>
+        <v>79095</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12680,21 +12685,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12704,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447175</v>
+        <v>447282</v>
       </c>
       <c r="R123" t="n">
-        <v>6804401</v>
+        <v>6804440</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12740,6 +12745,11 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12766,10 +12776,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129893406</v>
+        <v>129893304</v>
       </c>
       <c r="B124" t="n">
-        <v>79095</v>
+        <v>79714</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12777,21 +12787,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12801,10 +12811,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447282</v>
+        <v>447208</v>
       </c>
       <c r="R124" t="n">
-        <v>6804440</v>
+        <v>6804423</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12837,11 +12847,6 @@
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -12868,10 +12873,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893333</v>
+        <v>129893355</v>
       </c>
       <c r="B125" t="n">
-        <v>78853</v>
+        <v>78852</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12879,21 +12884,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12903,10 +12908,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447284</v>
+        <v>447175</v>
       </c>
       <c r="R125" t="n">
-        <v>6804412</v>
+        <v>6804401</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12965,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893401</v>
+        <v>129893333</v>
       </c>
       <c r="B126" t="n">
-        <v>79095</v>
+        <v>78853</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12976,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13000,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447291</v>
+        <v>447284</v>
       </c>
       <c r="R126" t="n">
-        <v>6804354</v>
+        <v>6804412</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13036,11 +13041,6 @@
       <c r="AA126" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 30 m</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13067,10 +13067,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>129893298</v>
+        <v>129893349</v>
       </c>
       <c r="B127" t="n">
-        <v>79714</v>
+        <v>78852</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13078,21 +13078,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13102,7 +13102,7 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>447137</v>
+        <v>447138</v>
       </c>
       <c r="R127" t="n">
         <v>6804511</v>
@@ -13164,10 +13164,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>129893349</v>
+        <v>129893298</v>
       </c>
       <c r="B128" t="n">
-        <v>78852</v>
+        <v>79714</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13175,21 +13175,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>447138</v>
+        <v>447137</v>
       </c>
       <c r="R128" t="n">
         <v>6804511</v>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY129"/>
+  <dimension ref="A1:AY130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129893913</v>
+        <v>129894044</v>
       </c>
       <c r="B2" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>447127</v>
+        <v>446959</v>
       </c>
       <c r="R2" t="n">
-        <v>6804438</v>
+        <v>6804780</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129893971</v>
+        <v>129893913</v>
       </c>
       <c r="B3" t="n">
-        <v>78852</v>
+        <v>79799</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>447009</v>
+        <v>447127</v>
       </c>
       <c r="R3" t="n">
-        <v>6804689</v>
+        <v>6804438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129894044</v>
+        <v>129893971</v>
       </c>
       <c r="B4" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>446959</v>
+        <v>447009</v>
       </c>
       <c r="R4" t="n">
-        <v>6804780</v>
+        <v>6804689</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +969,7 @@
         <v>129893939</v>
       </c>
       <c r="B5" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,10 +1071,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129894024</v>
+        <v>129893972</v>
       </c>
       <c r="B6" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1082,34 +1082,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>447139</v>
+        <v>447014</v>
       </c>
       <c r="R6" t="n">
-        <v>6804619</v>
+        <v>6804654</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1150,6 +1153,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1168,10 +1172,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129893972</v>
+        <v>129894024</v>
       </c>
       <c r="B7" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1179,37 +1183,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>447014</v>
+        <v>447139</v>
       </c>
       <c r="R7" t="n">
-        <v>6804654</v>
+        <v>6804619</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,7 +1251,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>129893970</v>
       </c>
       <c r="B8" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>129893974</v>
       </c>
       <c r="B9" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,10 +1570,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129893949</v>
+        <v>129894030</v>
       </c>
       <c r="B11" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1581,21 +1581,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1605,10 +1605,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>447021</v>
+        <v>447081</v>
       </c>
       <c r="R11" t="n">
-        <v>6804675</v>
+        <v>6804503</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1641,6 +1641,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1667,10 +1672,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129894030</v>
+        <v>129893949</v>
       </c>
       <c r="B12" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1678,21 +1683,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1702,10 +1707,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>447081</v>
+        <v>447021</v>
       </c>
       <c r="R12" t="n">
-        <v>6804503</v>
+        <v>6804675</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1738,11 +1743,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1769,10 +1769,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129894023</v>
+        <v>129893953</v>
       </c>
       <c r="B13" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1780,21 +1780,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1804,10 +1804,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>447120</v>
+        <v>447186</v>
       </c>
       <c r="R13" t="n">
-        <v>6804670</v>
+        <v>6804347</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1840,11 +1840,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1871,10 +1866,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129894050</v>
+        <v>129894023</v>
       </c>
       <c r="B14" t="n">
-        <v>78102</v>
+        <v>79180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1882,21 +1877,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1906,10 +1901,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>447251</v>
+        <v>447120</v>
       </c>
       <c r="R14" t="n">
-        <v>6804480</v>
+        <v>6804670</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1944,13 +1939,17 @@
           <t>2025-11-28</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1968,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129893953</v>
+        <v>129894050</v>
       </c>
       <c r="B15" t="n">
-        <v>78853</v>
+        <v>78187</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1980,21 +1979,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6487</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2004,10 +2003,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>447186</v>
+        <v>447251</v>
       </c>
       <c r="R15" t="n">
-        <v>6804347</v>
+        <v>6804480</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,6 +2047,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2069,7 +2069,7 @@
         <v>129894033</v>
       </c>
       <c r="B16" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2163,45 +2163,53 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129893973</v>
+        <v>129893923</v>
       </c>
       <c r="B17" t="n">
-        <v>78852</v>
+        <v>57016</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>447018</v>
+        <v>447079</v>
       </c>
       <c r="R17" t="n">
-        <v>6804657</v>
+        <v>6804592</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2260,10 +2268,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129894043</v>
+        <v>129893973</v>
       </c>
       <c r="B18" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2271,21 +2279,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2295,10 +2303,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>447247</v>
+        <v>447018</v>
       </c>
       <c r="R18" t="n">
-        <v>6804534</v>
+        <v>6804657</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2357,53 +2365,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129893923</v>
+        <v>129894043</v>
       </c>
       <c r="B19" t="n">
-        <v>56931</v>
+        <v>79180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>447079</v>
+        <v>447247</v>
       </c>
       <c r="R19" t="n">
-        <v>6804592</v>
+        <v>6804534</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2465,7 +2465,7 @@
         <v>129894042</v>
       </c>
       <c r="B20" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2562,7 +2562,7 @@
         <v>129894039</v>
       </c>
       <c r="B21" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2656,53 +2656,45 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129893945</v>
+        <v>129893956</v>
       </c>
       <c r="B22" t="n">
-        <v>56934</v>
+        <v>78938</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102613</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>447140</v>
+        <v>447248</v>
       </c>
       <c r="R22" t="n">
-        <v>6804358</v>
+        <v>6804447</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2761,10 +2753,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129894040</v>
+        <v>129893976</v>
       </c>
       <c r="B23" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,21 +2764,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2796,10 +2788,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>447244</v>
+        <v>447071</v>
       </c>
       <c r="R23" t="n">
-        <v>6804361</v>
+        <v>6804595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2858,10 +2850,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129893976</v>
+        <v>129894040</v>
       </c>
       <c r="B24" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2869,21 +2861,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2893,10 +2885,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>447071</v>
+        <v>447244</v>
       </c>
       <c r="R24" t="n">
-        <v>6804595</v>
+        <v>6804361</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2955,45 +2947,53 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129893956</v>
+        <v>129893945</v>
       </c>
       <c r="B25" t="n">
-        <v>78853</v>
+        <v>57019</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>102613</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>447248</v>
+        <v>447140</v>
       </c>
       <c r="R25" t="n">
-        <v>6804447</v>
+        <v>6804358</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3052,54 +3052,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129893964</v>
+        <v>129893954</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>78938</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>447241</v>
+        <v>447247</v>
       </c>
       <c r="R26" t="n">
-        <v>6804440</v>
+        <v>6804420</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3140,7 +3131,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3159,45 +3149,54 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129893954</v>
+        <v>129893964</v>
       </c>
       <c r="B27" t="n">
-        <v>78853</v>
+        <v>8451</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>447247</v>
+        <v>447241</v>
       </c>
       <c r="R27" t="n">
-        <v>6804420</v>
+        <v>6804440</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3238,6 +3237,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3256,10 +3256,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129893935</v>
+        <v>129894047</v>
       </c>
       <c r="B28" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3267,42 +3267,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>447017</v>
+        <v>447264</v>
       </c>
       <c r="R28" t="n">
-        <v>6804662</v>
+        <v>6804394</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3335,6 +3327,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3361,10 +3358,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129894047</v>
+        <v>129893919</v>
       </c>
       <c r="B29" t="n">
-        <v>79095</v>
+        <v>79770</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3372,21 +3369,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3396,10 +3393,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>447264</v>
+        <v>447260</v>
       </c>
       <c r="R29" t="n">
-        <v>6804394</v>
+        <v>6804349</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3432,11 +3429,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gott om garnlav inom en radie av 30m</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3463,10 +3455,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129894029</v>
+        <v>129893979</v>
       </c>
       <c r="B30" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3474,21 +3466,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3498,10 +3490,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>447078</v>
+        <v>447104</v>
       </c>
       <c r="R30" t="n">
-        <v>6804574</v>
+        <v>6804432</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3534,11 +3526,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3565,10 +3552,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129893979</v>
+        <v>129893935</v>
       </c>
       <c r="B31" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3576,34 +3563,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>447104</v>
+        <v>447017</v>
       </c>
       <c r="R31" t="n">
-        <v>6804432</v>
+        <v>6804662</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3662,10 +3657,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129893919</v>
+        <v>129894029</v>
       </c>
       <c r="B32" t="n">
-        <v>79685</v>
+        <v>79180</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3673,21 +3668,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3697,10 +3692,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>447260</v>
+        <v>447078</v>
       </c>
       <c r="R32" t="n">
-        <v>6804349</v>
+        <v>6804574</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3733,6 +3728,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav inom en radie av 40m</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3762,7 +3762,7 @@
         <v>129894026</v>
       </c>
       <c r="B33" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3864,7 +3864,7 @@
         <v>129894028</v>
       </c>
       <c r="B34" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>129894036</v>
       </c>
       <c r="B35" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4058,7 +4058,7 @@
         <v>129894046</v>
       </c>
       <c r="B36" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4164,7 +4164,7 @@
         <v>129894034</v>
       </c>
       <c r="B37" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>129893955</v>
       </c>
       <c r="B38" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>129893920</v>
       </c>
       <c r="B39" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>129893977</v>
       </c>
       <c r="B40" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4549,10 +4549,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129894027</v>
+        <v>129893948</v>
       </c>
       <c r="B41" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4560,21 +4560,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4584,10 +4584,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>446979</v>
+        <v>446971</v>
       </c>
       <c r="R41" t="n">
-        <v>6804787</v>
+        <v>6804769</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4646,10 +4646,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129893948</v>
+        <v>129893983</v>
       </c>
       <c r="B42" t="n">
-        <v>78853</v>
+        <v>78937</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4657,21 +4657,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4681,10 +4681,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>446971</v>
+        <v>447195</v>
       </c>
       <c r="R42" t="n">
-        <v>6804769</v>
+        <v>6804348</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4743,10 +4743,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129893983</v>
+        <v>129894027</v>
       </c>
       <c r="B43" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4754,21 +4754,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4778,10 +4778,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>447195</v>
+        <v>446979</v>
       </c>
       <c r="R43" t="n">
-        <v>6804348</v>
+        <v>6804787</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4843,7 +4843,7 @@
         <v>129893975</v>
       </c>
       <c r="B44" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4937,10 +4937,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129894041</v>
+        <v>129893980</v>
       </c>
       <c r="B45" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4948,21 +4948,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4972,10 +4972,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>447242</v>
+        <v>447136</v>
       </c>
       <c r="R45" t="n">
-        <v>6804443</v>
+        <v>6804407</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5034,10 +5034,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129894035</v>
+        <v>129894041</v>
       </c>
       <c r="B46" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5069,10 +5069,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>447155</v>
+        <v>447242</v>
       </c>
       <c r="R46" t="n">
-        <v>6804339</v>
+        <v>6804443</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5131,10 +5131,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129893933</v>
+        <v>129894035</v>
       </c>
       <c r="B47" t="n">
-        <v>57738</v>
+        <v>79180</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5142,42 +5142,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>447075</v>
+        <v>447155</v>
       </c>
       <c r="R47" t="n">
-        <v>6804732</v>
+        <v>6804339</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5236,10 +5228,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129893937</v>
+        <v>129893918</v>
       </c>
       <c r="B48" t="n">
-        <v>57738</v>
+        <v>79770</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5247,42 +5239,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>447059</v>
+        <v>447021</v>
       </c>
       <c r="R48" t="n">
-        <v>6804587</v>
+        <v>6804646</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5341,10 +5325,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129893936</v>
+        <v>129893933</v>
       </c>
       <c r="B49" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5384,10 +5368,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>447012</v>
+        <v>447075</v>
       </c>
       <c r="R49" t="n">
-        <v>6804645</v>
+        <v>6804732</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5446,10 +5430,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129893980</v>
+        <v>129893937</v>
       </c>
       <c r="B50" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5457,34 +5441,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>447136</v>
+        <v>447059</v>
       </c>
       <c r="R50" t="n">
-        <v>6804407</v>
+        <v>6804587</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5543,10 +5535,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129893969</v>
+        <v>129893936</v>
       </c>
       <c r="B51" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5554,34 +5546,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>447006</v>
+        <v>447012</v>
       </c>
       <c r="R51" t="n">
-        <v>6804728</v>
+        <v>6804645</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5640,10 +5640,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129893918</v>
+        <v>129893951</v>
       </c>
       <c r="B52" t="n">
-        <v>79685</v>
+        <v>78938</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5651,21 +5651,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5675,10 +5675,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>447021</v>
+        <v>447014</v>
       </c>
       <c r="R52" t="n">
-        <v>6804646</v>
+        <v>6804638</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5737,10 +5737,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129893951</v>
+        <v>129893969</v>
       </c>
       <c r="B53" t="n">
-        <v>78853</v>
+        <v>78937</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5748,21 +5748,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5772,10 +5772,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>447014</v>
+        <v>447006</v>
       </c>
       <c r="R53" t="n">
-        <v>6804638</v>
+        <v>6804728</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5834,32 +5834,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129893932</v>
+        <v>129893924</v>
       </c>
       <c r="B54" t="n">
-        <v>57738</v>
+        <v>57016</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5867,7 +5867,7 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
@@ -5877,10 +5877,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>447239</v>
+        <v>446997</v>
       </c>
       <c r="R54" t="n">
-        <v>6804569</v>
+        <v>6804780</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5913,6 +5913,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5939,10 +5944,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129893938</v>
+        <v>129893932</v>
       </c>
       <c r="B55" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5972,7 +5977,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>447064</v>
+        <v>447239</v>
       </c>
       <c r="R55" t="n">
-        <v>6804548</v>
+        <v>6804569</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6044,32 +6049,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129893924</v>
+        <v>129893938</v>
       </c>
       <c r="B56" t="n">
-        <v>56931</v>
+        <v>57823</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6077,7 +6082,7 @@
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
@@ -6087,10 +6092,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>446997</v>
+        <v>447064</v>
       </c>
       <c r="R56" t="n">
-        <v>6804780</v>
+        <v>6804548</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6123,11 +6128,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ivägskrämd</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6157,7 +6157,7 @@
         <v>129894045</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129894025</v>
+        <v>129893950</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>78938</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6267,21 +6267,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6291,10 +6291,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>447101</v>
+        <v>447015</v>
       </c>
       <c r="R58" t="n">
-        <v>6804700</v>
+        <v>6804655</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6353,10 +6353,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129893968</v>
+        <v>129894025</v>
       </c>
       <c r="B59" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6364,21 +6364,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6388,10 +6388,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>446972</v>
+        <v>447101</v>
       </c>
       <c r="R59" t="n">
-        <v>6804770</v>
+        <v>6804700</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6450,10 +6450,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129893967</v>
+        <v>129893968</v>
       </c>
       <c r="B60" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6485,10 +6485,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>447209</v>
+        <v>446972</v>
       </c>
       <c r="R60" t="n">
-        <v>6804576</v>
+        <v>6804770</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6547,10 +6547,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129893934</v>
+        <v>129893967</v>
       </c>
       <c r="B61" t="n">
-        <v>57738</v>
+        <v>78937</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6558,42 +6558,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>447006</v>
+        <v>447209</v>
       </c>
       <c r="R61" t="n">
-        <v>6804684</v>
+        <v>6804576</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6652,10 +6644,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129893950</v>
+        <v>129893934</v>
       </c>
       <c r="B62" t="n">
-        <v>78853</v>
+        <v>57823</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6663,34 +6655,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>447015</v>
+        <v>447006</v>
       </c>
       <c r="R62" t="n">
-        <v>6804655</v>
+        <v>6804684</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6749,10 +6749,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129893952</v>
+        <v>129893914</v>
       </c>
       <c r="B63" t="n">
-        <v>78853</v>
+        <v>79799</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6760,21 +6760,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>447138</v>
+        <v>447244</v>
       </c>
       <c r="R63" t="n">
-        <v>6804405</v>
+        <v>6804447</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129894038</v>
+        <v>129893912</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>447196</v>
+        <v>447082</v>
       </c>
       <c r="R64" t="n">
-        <v>6804341</v>
+        <v>6804551</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129893914</v>
+        <v>129893952</v>
       </c>
       <c r="B65" t="n">
-        <v>79714</v>
+        <v>78938</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>447244</v>
+        <v>447138</v>
       </c>
       <c r="R65" t="n">
-        <v>6804447</v>
+        <v>6804405</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129893912</v>
+        <v>129893982</v>
       </c>
       <c r="B66" t="n">
-        <v>79714</v>
+        <v>78937</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>447082</v>
+        <v>447163</v>
       </c>
       <c r="R66" t="n">
-        <v>6804551</v>
+        <v>6804342</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129893982</v>
+        <v>129893921</v>
       </c>
       <c r="B67" t="n">
-        <v>78852</v>
+        <v>57826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7148,34 +7148,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>447163</v>
+        <v>447004</v>
       </c>
       <c r="R67" t="n">
-        <v>6804342</v>
+        <v>6804712</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7234,10 +7242,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129893921</v>
+        <v>129894038</v>
       </c>
       <c r="B68" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7245,42 +7253,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Jöllmyren, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>447004</v>
+        <v>447196</v>
       </c>
       <c r="R68" t="n">
-        <v>6804712</v>
+        <v>6804341</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7339,10 +7339,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129893324</v>
+        <v>129893347</v>
       </c>
       <c r="B69" t="n">
-        <v>57738</v>
+        <v>78937</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7350,42 +7350,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>447118</v>
+        <v>447114</v>
       </c>
       <c r="R69" t="n">
-        <v>6804529</v>
+        <v>6804581</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7444,10 +7436,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129893347</v>
+        <v>129893324</v>
       </c>
       <c r="B70" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7455,34 +7447,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>447114</v>
+        <v>447118</v>
       </c>
       <c r="R70" t="n">
-        <v>6804581</v>
+        <v>6804529</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7544,7 +7544,7 @@
         <v>129893402</v>
       </c>
       <c r="B71" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7641,7 +7641,7 @@
         <v>129893404</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>129893403</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>129893400</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7937,7 +7937,7 @@
         <v>129893393</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>129893356</v>
       </c>
       <c r="B76" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8136,7 +8136,7 @@
         <v>129893315</v>
       </c>
       <c r="B77" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8238,32 +8238,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129893368</v>
+        <v>129893334</v>
       </c>
       <c r="B78" t="n">
-        <v>91023</v>
+        <v>78938</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5685</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8273,10 +8273,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>447279</v>
+        <v>447287</v>
       </c>
       <c r="R78" t="n">
-        <v>6804380</v>
+        <v>6804433</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8317,7 +8317,6 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8336,10 +8335,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129893395</v>
+        <v>129893306</v>
       </c>
       <c r="B79" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8347,21 +8346,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8371,7 +8370,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>447137</v>
+        <v>447282</v>
       </c>
       <c r="R79" t="n">
         <v>6804440</v>
@@ -8407,11 +8406,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8438,32 +8432,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129893306</v>
+        <v>129893368</v>
       </c>
       <c r="B80" t="n">
-        <v>79714</v>
+        <v>91110</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>5685</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8473,10 +8467,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>447282</v>
+        <v>447279</v>
       </c>
       <c r="R80" t="n">
-        <v>6804440</v>
+        <v>6804380</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8517,6 +8511,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8538,7 +8533,7 @@
         <v>129893353</v>
       </c>
       <c r="B81" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8632,10 +8627,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129893334</v>
+        <v>129893395</v>
       </c>
       <c r="B82" t="n">
-        <v>78853</v>
+        <v>79180</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8643,21 +8638,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8667,10 +8662,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>447287</v>
+        <v>447137</v>
       </c>
       <c r="R82" t="n">
-        <v>6804433</v>
+        <v>6804440</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8703,6 +8698,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8729,10 +8729,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>129893397</v>
+        <v>129893303</v>
       </c>
       <c r="B83" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8740,21 +8740,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8764,10 +8764,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>447191</v>
+        <v>447143</v>
       </c>
       <c r="R83" t="n">
-        <v>6804284</v>
+        <v>6804414</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8800,11 +8800,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8831,10 +8826,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>129893303</v>
+        <v>129893397</v>
       </c>
       <c r="B84" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8842,21 +8837,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8866,10 +8861,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>447143</v>
+        <v>447191</v>
       </c>
       <c r="R84" t="n">
-        <v>6804414</v>
+        <v>6804284</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8902,6 +8897,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8931,7 +8931,7 @@
         <v>129893348</v>
       </c>
       <c r="B85" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>129893305</v>
       </c>
       <c r="B86" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9125,7 +9125,7 @@
         <v>129893392</v>
       </c>
       <c r="B87" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>129893405</v>
       </c>
       <c r="B88" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9321,10 +9321,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129893399</v>
+        <v>129893307</v>
       </c>
       <c r="B89" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9332,21 +9332,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9356,10 +9356,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>447206</v>
+        <v>447271</v>
       </c>
       <c r="R89" t="n">
-        <v>6804317</v>
+        <v>6804458</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9418,10 +9418,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129893307</v>
+        <v>129893360</v>
       </c>
       <c r="B90" t="n">
-        <v>79714</v>
+        <v>78937</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9429,21 +9429,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9453,10 +9453,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>447271</v>
+        <v>447286</v>
       </c>
       <c r="R90" t="n">
-        <v>6804458</v>
+        <v>6804433</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9515,10 +9515,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129893360</v>
+        <v>129893399</v>
       </c>
       <c r="B91" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9526,21 +9526,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9550,10 +9550,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>447286</v>
+        <v>447206</v>
       </c>
       <c r="R91" t="n">
-        <v>6804433</v>
+        <v>6804317</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9612,10 +9612,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129893351</v>
+        <v>129893309</v>
       </c>
       <c r="B92" t="n">
-        <v>78852</v>
+        <v>79770</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9623,21 +9623,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9647,10 +9647,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>447129</v>
+        <v>447247</v>
       </c>
       <c r="R92" t="n">
-        <v>6804505</v>
+        <v>6804552</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9712,7 +9712,7 @@
         <v>129893316</v>
       </c>
       <c r="B93" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9814,10 +9814,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129893309</v>
+        <v>129893351</v>
       </c>
       <c r="B94" t="n">
-        <v>79685</v>
+        <v>78937</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9825,21 +9825,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9849,10 +9849,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>447247</v>
+        <v>447129</v>
       </c>
       <c r="R94" t="n">
-        <v>6804552</v>
+        <v>6804505</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9914,7 +9914,7 @@
         <v>129893323</v>
       </c>
       <c r="B95" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>129893407</v>
       </c>
       <c r="B96" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10116,7 +10116,7 @@
         <v>129893332</v>
       </c>
       <c r="B97" t="n">
-        <v>78853</v>
+        <v>78938</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10210,10 +10210,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129893396</v>
+        <v>129893359</v>
       </c>
       <c r="B98" t="n">
-        <v>79095</v>
+        <v>78937</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10221,21 +10221,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10245,10 +10245,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>447170</v>
+        <v>447276</v>
       </c>
       <c r="R98" t="n">
-        <v>6804344</v>
+        <v>6804418</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10281,11 +10281,6 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10312,10 +10307,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129893359</v>
+        <v>129893310</v>
       </c>
       <c r="B99" t="n">
-        <v>78852</v>
+        <v>79770</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10323,21 +10318,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10347,10 +10342,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>447276</v>
+        <v>447280</v>
       </c>
       <c r="R99" t="n">
-        <v>6804418</v>
+        <v>6804428</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10412,7 +10407,7 @@
         <v>129893350</v>
       </c>
       <c r="B100" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10506,10 +10501,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129893310</v>
+        <v>129893396</v>
       </c>
       <c r="B101" t="n">
-        <v>79685</v>
+        <v>79180</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10517,21 +10512,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10541,10 +10536,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>447280</v>
+        <v>447170</v>
       </c>
       <c r="R101" t="n">
-        <v>6804428</v>
+        <v>6804344</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10577,6 +10572,11 @@
       <c r="AA101" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10606,7 +10606,7 @@
         <v>129893344</v>
       </c>
       <c r="B102" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>129893357</v>
       </c>
       <c r="B103" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>129893301</v>
       </c>
       <c r="B104" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>129893398</v>
       </c>
       <c r="B105" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10994,7 +10994,7 @@
         <v>129893346</v>
       </c>
       <c r="B106" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>129893299</v>
       </c>
       <c r="B107" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>129893295</v>
       </c>
       <c r="B108" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>129893358</v>
       </c>
       <c r="B109" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11379,10 +11379,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>129893352</v>
+        <v>129893322</v>
       </c>
       <c r="B110" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11390,34 +11390,42 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>447146</v>
+        <v>447105</v>
       </c>
       <c r="R110" t="n">
-        <v>6804415</v>
+        <v>6804584</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11476,10 +11484,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129893296</v>
+        <v>129893352</v>
       </c>
       <c r="B111" t="n">
-        <v>79714</v>
+        <v>78937</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11487,21 +11495,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11511,10 +11519,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>447079</v>
+        <v>447146</v>
       </c>
       <c r="R111" t="n">
-        <v>6804660</v>
+        <v>6804415</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11573,10 +11581,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129893322</v>
+        <v>129893296</v>
       </c>
       <c r="B112" t="n">
-        <v>57738</v>
+        <v>79799</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11584,42 +11592,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>447105</v>
+        <v>447079</v>
       </c>
       <c r="R112" t="n">
-        <v>6804584</v>
+        <v>6804660</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11678,10 +11678,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>129893300</v>
+        <v>129893314</v>
       </c>
       <c r="B113" t="n">
-        <v>79714</v>
+        <v>57826</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11689,34 +11689,42 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>447121</v>
+        <v>447227</v>
       </c>
       <c r="R113" t="n">
-        <v>6804435</v>
+        <v>6804586</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11775,10 +11783,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129893308</v>
+        <v>129893300</v>
       </c>
       <c r="B114" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11810,10 +11818,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>447248</v>
+        <v>447121</v>
       </c>
       <c r="R114" t="n">
-        <v>6804484</v>
+        <v>6804435</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11872,10 +11880,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129893297</v>
+        <v>129893394</v>
       </c>
       <c r="B115" t="n">
-        <v>79714</v>
+        <v>79180</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11883,21 +11891,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11907,10 +11915,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>447104</v>
+        <v>447128</v>
       </c>
       <c r="R115" t="n">
-        <v>6804519</v>
+        <v>6804516</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11943,6 +11951,11 @@
       <c r="AA115" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -11969,10 +11982,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129893394</v>
+        <v>129893308</v>
       </c>
       <c r="B116" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11980,21 +11993,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12004,10 +12017,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>447128</v>
+        <v>447248</v>
       </c>
       <c r="R116" t="n">
-        <v>6804516</v>
+        <v>6804484</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12040,11 +12053,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12071,10 +12079,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129893314</v>
+        <v>129893297</v>
       </c>
       <c r="B117" t="n">
-        <v>57741</v>
+        <v>79799</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12082,42 +12090,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>447227</v>
+        <v>447104</v>
       </c>
       <c r="R117" t="n">
-        <v>6804586</v>
+        <v>6804519</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12179,7 +12179,7 @@
         <v>129893302</v>
       </c>
       <c r="B118" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12273,10 +12273,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>129893354</v>
+        <v>129893325</v>
       </c>
       <c r="B119" t="n">
-        <v>78852</v>
+        <v>57823</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12284,34 +12284,42 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>447193</v>
+        <v>447201</v>
       </c>
       <c r="R119" t="n">
-        <v>6804389</v>
+        <v>6804314</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12370,10 +12378,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>129893325</v>
+        <v>129893354</v>
       </c>
       <c r="B120" t="n">
-        <v>57738</v>
+        <v>78937</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12381,42 +12389,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="K120" t="inlineStr"/>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
           <t>Jöllmyr, Dlr</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>447201</v>
+        <v>447193</v>
       </c>
       <c r="R120" t="n">
-        <v>6804314</v>
+        <v>6804389</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12478,7 +12478,7 @@
         <v>129893401</v>
       </c>
       <c r="B121" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12580,7 +12580,7 @@
         <v>129893408</v>
       </c>
       <c r="B122" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12674,10 +12674,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129893406</v>
+        <v>129893304</v>
       </c>
       <c r="B123" t="n">
-        <v>79095</v>
+        <v>79799</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12685,21 +12685,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12709,10 +12709,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>447282</v>
+        <v>447208</v>
       </c>
       <c r="R123" t="n">
-        <v>6804440</v>
+        <v>6804423</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12745,11 +12745,6 @@
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-11-28</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -12776,10 +12771,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129893304</v>
+        <v>129893333</v>
       </c>
       <c r="B124" t="n">
-        <v>79714</v>
+        <v>78938</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12787,21 +12782,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12811,10 +12806,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>447208</v>
+        <v>447284</v>
       </c>
       <c r="R124" t="n">
-        <v>6804423</v>
+        <v>6804412</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12873,10 +12868,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129893355</v>
+        <v>129893406</v>
       </c>
       <c r="B125" t="n">
-        <v>78852</v>
+        <v>79180</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12884,21 +12879,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12908,10 +12903,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>447175</v>
+        <v>447282</v>
       </c>
       <c r="R125" t="n">
-        <v>6804401</v>
+        <v>6804440</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12944,6 +12939,11 @@
       <c r="AA125" t="inlineStr">
         <is>
           <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Rikligt inom en radie av 20 m</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -12970,10 +12970,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>129893333</v>
+        <v>129893355</v>
       </c>
       <c r="B126" t="n">
-        <v>78853</v>
+        <v>78937</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12981,21 +12981,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13005,10 +13005,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>447284</v>
+        <v>447175</v>
       </c>
       <c r="R126" t="n">
-        <v>6804412</v>
+        <v>6804401</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13070,7 +13070,7 @@
         <v>129893349</v>
       </c>
       <c r="B127" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13167,7 +13167,7 @@
         <v>129893298</v>
       </c>
       <c r="B128" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>129893345</v>
       </c>
       <c r="B129" t="n">
-        <v>78852</v>
+        <v>78937</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13355,6 +13355,111 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129893985</v>
+      </c>
+      <c r="B130" t="n">
+        <v>57826</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>nyligen använt bo</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Jöllmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>447006</v>
+      </c>
+      <c r="R130" t="n">
+        <v>6804699</v>
+      </c>
+      <c r="S130" t="n">
+        <v>10</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Eva Löfqvist</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -13361,7 +13361,7 @@
         <v>129893985</v>
       </c>
       <c r="B130" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -13361,7 +13361,7 @@
         <v>129893985</v>
       </c>
       <c r="B130" t="n">
-        <v>57852</v>
+        <v>57854</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -13361,7 +13361,7 @@
         <v>129893985</v>
       </c>
       <c r="B130" t="n">
-        <v>57854</v>
+        <v>57862</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55982-2025 artfynd.xlsx
+++ b/artfynd/A 55982-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY136"/>
+  <dimension ref="A1:AZ136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893368</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893392</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -974,6 +989,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893393</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893394</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1178,6 +1203,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893395</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1280,6 +1310,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893396</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1382,6 +1417,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893397</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1479,6 +1519,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893398</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1576,6 +1621,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893399</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893400</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1780,6 +1835,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893401</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1877,6 +1937,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893402</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1974,6 +2039,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893403</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2071,6 +2141,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893404</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2168,6 +2243,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893405</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2270,6 +2350,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893406</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2367,6 +2452,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893407</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2464,6 +2554,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893408</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2566,6 +2661,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894023</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2663,6 +2763,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894024</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2760,6 +2865,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894025</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2862,6 +2972,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894026</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2959,6 +3074,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894027</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3056,6 +3176,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894028</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3158,6 +3283,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894029</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3260,6 +3390,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894030</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3362,6 +3497,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894031</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3459,6 +3599,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894033</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3556,6 +3701,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894034</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3653,6 +3803,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894035</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3750,6 +3905,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894036</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3847,6 +4007,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894038</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3944,6 +4109,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894039</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4041,6 +4211,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894040</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4138,6 +4313,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894041</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4235,6 +4415,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894042</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4332,6 +4517,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894043</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4429,6 +4619,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894044</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4531,6 +4726,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894045</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4637,6 +4837,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894046</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4739,6 +4944,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894047</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4836,6 +5046,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893343</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4933,6 +5148,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893344</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5030,6 +5250,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893345</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5127,6 +5352,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893346</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5224,6 +5454,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893347</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5321,6 +5556,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893348</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5418,6 +5658,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893349</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5515,6 +5760,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893350</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5612,6 +5862,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893351</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5709,6 +5964,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893352</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5806,6 +6066,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893353</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5903,6 +6168,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893354</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6000,6 +6270,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893355</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6097,6 +6372,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893356</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6194,6 +6474,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893357</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6291,6 +6576,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893358</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6388,6 +6678,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893359</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6485,6 +6780,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893360</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6582,6 +6882,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893967</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6679,6 +6984,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893968</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6776,6 +7086,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893969</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6873,6 +7188,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893970</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6970,6 +7290,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893971</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7071,6 +7396,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893972</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7168,6 +7498,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893973</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7265,6 +7600,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893974</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7362,6 +7702,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893975</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7459,6 +7804,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893976</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7556,6 +7906,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893977</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7653,6 +8008,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893978</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7750,6 +8110,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893979</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7847,6 +8212,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893980</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7944,6 +8314,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893981</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8041,6 +8416,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893982</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8138,6 +8518,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893983</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8235,6 +8620,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893295</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8332,6 +8722,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893296</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8429,6 +8824,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893297</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8526,6 +8926,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893298</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8623,6 +9028,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893299</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8720,6 +9130,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893300</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8817,6 +9232,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893301</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8914,6 +9334,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893302</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9011,6 +9436,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893303</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9108,6 +9538,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893304</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9205,6 +9640,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893305</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9302,6 +9742,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893306</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9399,6 +9844,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893307</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9496,6 +9946,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893308</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9593,6 +10048,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893912</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9690,6 +10150,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893913</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9787,6 +10252,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893914</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9885,6 +10355,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129894050</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -9990,6 +10465,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893322</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10095,6 +10575,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893323</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10200,6 +10685,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893324</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10305,6 +10795,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893325</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10410,6 +10905,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893932</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10515,6 +11015,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893933</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10620,6 +11125,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893934</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10725,6 +11235,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893935</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10830,6 +11345,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893936</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -10935,6 +11455,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893937</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11040,6 +11565,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893938</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11145,6 +11675,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893939</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11250,6 +11785,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893940</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11355,6 +11895,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893942</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11460,6 +12005,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893314</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11565,6 +12115,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893315</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11670,6 +12225,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893921</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11775,6 +12335,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893985</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11880,6 +12445,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893316</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -11985,6 +12555,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893923</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12095,6 +12670,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893924</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12200,6 +12780,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893945</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12307,6 +12892,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893963</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12414,6 +13004,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893964</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12511,6 +13106,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893332</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12608,6 +13208,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893333</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12705,6 +13310,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893334</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12802,6 +13412,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893948</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12899,6 +13514,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893949</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -12996,6 +13616,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893950</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13093,6 +13718,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893951</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13190,6 +13820,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893952</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13287,6 +13922,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893953</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13384,6 +14024,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893954</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13481,6 +14126,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893955</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13578,6 +14228,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893956</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13675,6 +14330,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893309</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13772,6 +14432,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893310</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -13869,6 +14534,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893918</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -13966,6 +14636,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893919</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14063,8 +14738,150 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129893920</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>